--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -666,7 +666,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -671,7 +671,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="15" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -56170,18 +56170,18 @@
       </c>
       <c r="J896" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="K896" s="5" t="n">
-        <v>6412737</v>
+        <v>7736825</v>
       </c>
       <c r="L896" s="5" t="n">
-        <v>19374</v>
+        <v>23374</v>
       </c>
       <c r="M896" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>90 天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N896" s="3" t="inlineStr">
@@ -56232,18 +56232,18 @@
       </c>
       <c r="J897" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K897" s="5" t="n">
-        <v>8237450</v>
+        <v>8737700</v>
       </c>
       <c r="L897" s="5" t="n">
-        <v>18224</v>
+        <v>19331</v>
       </c>
       <c r="M897" s="3" t="inlineStr">
         <is>
-          <t>90天現金優惠付款計劃</t>
+          <t>90 天現金優惠付款計劃</t>
         </is>
       </c>
       <c r="N897" s="3" t="inlineStr">
@@ -65284,14 +65284,14 @@
       </c>
       <c r="J1043" s="3" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="K1043" s="5" t="n">
-        <v>7246980</v>
+        <v>7687080</v>
       </c>
       <c r="L1043" s="5" t="n">
-        <v>16069</v>
+        <v>17045</v>
       </c>
       <c r="M1043" s="3" t="inlineStr">
         <is>

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -24,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,12 +126,6 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
@@ -217,7 +211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -282,13 +276,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -16156,38 +16147,30 @@
       </c>
       <c r="F251" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H251" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="H251" s="5" t="n">
+        <v>15651000</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>26172</v>
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K251" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L251" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K251" s="5" t="n">
+        <v>15651000</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>26172</v>
       </c>
       <c r="M251" s="3" t="inlineStr">
         <is>
@@ -16196,7 +16179,7 @@
       </c>
       <c r="N251" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -56170,7 +56153,7 @@
       </c>
       <c r="J896" s="3" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="K896" s="5" t="n">
@@ -56232,7 +56215,7 @@
       </c>
       <c r="J897" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="K897" s="5" t="n">
@@ -65284,7 +65267,7 @@
       </c>
       <c r="J1043" s="3" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="K1043" s="5" t="n">
@@ -68844,7 +68827,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -68854,7 +68837,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>246</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -68963,12 +68946,12 @@
 (21年-09月-20日)</t>
         </is>
       </c>
-      <c r="I5" s="22" t="inlineStr">
+      <c r="I5" s="20" t="inlineStr">
         <is>
           <t>H | 598呎 (3房)
-招标单位
--
-(在售)</t>
+$1565万
+$26,172/呎
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -74931,7 +74914,7 @@
 (21年-07月-26日)</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 452呎 (2房)
 $1334万
@@ -74939,7 +74922,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="G20" s="24" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 331呎 (1房)
 $1038万
@@ -76268,7 +76251,7 @@
 (22年-01月-20日)</t>
         </is>
       </c>
-      <c r="J35" s="23" t="inlineStr">
+      <c r="J35" s="22" t="inlineStr">
         <is>
           <t>J | 451呎 (2房)
 $1174万

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -66561,7 +66561,7 @@
           <t>A | 643呎 (3房)
 $1531万
 $23,806/呎
-(24年-12月-12日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -66569,7 +66569,7 @@
           <t>B | 443呎 (2房)
 $913万
 $20,614/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -66577,7 +66577,7 @@
           <t>C | 438呎 (2房)
 $932万
 $21,281/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -66585,7 +66585,7 @@
           <t>D | 445呎 (2房)
 $959万
 $21,548/呎
-(25年-09月-10日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -66593,7 +66593,7 @@
           <t>E | 426呎 (2房)
 $930万
 $21,822/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -66601,7 +66601,7 @@
           <t>F | 448呎 (2房)
 $974万
 $21,743/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -66609,7 +66609,7 @@
           <t>G | 778呎 (3房)
 $2420万
 $31,105/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -66617,7 +66617,7 @@
           <t>H | 642呎 (3房)
 $1450万
 $22,586/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -66632,7 +66632,7 @@
           <t>A | 643呎 (3房)
 $2012万
 $31,289/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -66640,7 +66640,7 @@
           <t>B | 443呎 (2房)
 $1236万
 $27,894/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -66648,7 +66648,7 @@
           <t>C | 438呎 (2房)
 $927万
 $21,160/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -66656,7 +66656,7 @@
           <t>D | 445呎 (2房)
 $954万
 $21,427/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -66664,7 +66664,7 @@
           <t>E | 426呎 (2房)
 $924万
 $21,700/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -66672,7 +66672,7 @@
           <t>F | 448呎 (2房)
 $969万
 $21,623/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -66680,7 +66680,7 @@
           <t>G | 765呎 (3房)
 $1912万
 $24,999/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -66688,7 +66688,7 @@
           <t>H | 644呎 (3房)
 $1467万
 $22,784/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -66703,7 +66703,7 @@
           <t>A | 643呎 (3房)
 $1515万
 $23,557/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -66711,7 +66711,7 @@
           <t>B | 443呎 (2房)
 $903万
 $20,375/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -66719,7 +66719,7 @@
           <t>C | 438呎 (2房)
 $922万
 $21,041/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -66727,7 +66727,7 @@
           <t>D | 445呎 (2房)
 $948万
 $21,306/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -66735,7 +66735,7 @@
           <t>E | 426呎 (2房)
 $933万
 $21,899/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -66743,7 +66743,7 @@
           <t>F | 448呎 (2房)
 $963万
 $21,502/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -66751,7 +66751,7 @@
           <t>G | 765呎 (3房)
 $1907万
 $24,929/呎
-(26年-01月-04日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -66759,7 +66759,7 @@
           <t>H | 644呎 (3房)
 $1441万
 $22,380/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -66774,7 +66774,7 @@
           <t>A | 643呎 (3房)
 $1991万
 $30,958/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -66782,7 +66782,7 @@
           <t>B | 443呎 (2房)
 $897万
 $20,255/呎
-(26年-03月-17日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -66790,7 +66790,7 @@
           <t>C | 438呎 (2房)
 $921万
 $21,025/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -66798,7 +66798,7 @@
           <t>D | 445呎 (2房)
 $943万
 $21,184/呎
-(25年-09月-17日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -66806,7 +66806,7 @@
           <t>E | 426呎 (2房)
 $914万
 $21,453/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -66814,7 +66814,7 @@
           <t>F | 448呎 (2房)
 $958万
 $21,384/呎
-(24年-12月-04日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -66822,7 +66822,7 @@
           <t>G | 765呎 (3房)
 $1902万
 $24,861/呎
-(26年-01月-15日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -66830,7 +66830,7 @@
           <t>H | 644呎 (3房)
 $1437万
 $22,314/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -66845,7 +66845,7 @@
           <t>A | 643呎 (3房)
 $1499万
 $23,306/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -66853,7 +66853,7 @@
           <t>B | 443呎 (2房)
 $892万
 $20,140/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -66861,7 +66861,7 @@
           <t>C | 438呎 (2房)
 $920万
 $21,007/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -66869,7 +66869,7 @@
           <t>D | 445呎 (2房)
 $937万
 $21,063/呎
-(25年-11月-12日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -66877,7 +66877,7 @@
           <t>E | 426呎 (2房)
 $909万
 $21,331/呎
-(24年-04月-28日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -66885,7 +66885,7 @@
           <t>F | 448呎 (2房)
 $952万
 $21,261/呎
-(24年-12月-09日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -66893,7 +66893,7 @@
           <t>G | 765呎 (3房)
 $1897万
 $24,792/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -66901,7 +66901,7 @@
           <t>H | 644呎 (3房)
 $1433万
 $22,247/呎
-(24年-03月-04日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -66916,7 +66916,7 @@
           <t>A | 643呎 (3房)
 $1491万
 $23,182/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -66924,7 +66924,7 @@
           <t>B | 443呎 (2房)
 $887万
 $20,018/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -66932,7 +66932,7 @@
           <t>C | 438呎 (2房)
 $919万
 $20,989/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -66940,7 +66940,7 @@
           <t>D | 445呎 (2房)
 $932万
 $20,942/呎
-(25年-10月-19日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -66948,7 +66948,7 @@
           <t>E | 426呎 (2房)
 $904万
 $21,209/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -66956,7 +66956,7 @@
           <t>F | 448呎 (2房)
 $947万
 $21,141/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -66964,7 +66964,7 @@
           <t>G | 765呎 (3房)
 $1910万
 $24,974/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -66972,7 +66972,7 @@
           <t>H | 644呎 (3房)
 $1428万
 $22,180/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -66987,7 +66987,7 @@
           <t>A | 643呎 (3房)
 $1483万
 $23,058/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -66995,7 +66995,7 @@
           <t>B | 444呎 (2房)
 $1147万
 $25,829/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -67003,7 +67003,7 @@
           <t>C | 438呎 (2房)
 $918万
 $20,970/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -67011,7 +67011,7 @@
           <t>D | 445呎 (2房)
 $926万
 $20,820/呎
-(25年-09月-09日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -67019,7 +67019,7 @@
           <t>E | 426呎 (2房)
 $898万
 $21,085/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -67027,7 +67027,7 @@
           <t>F | 448呎 (2房)
 $942万
 $21,022/呎
-(25年-01月-16日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -67035,7 +67035,7 @@
           <t>G | 765呎 (3房)
 $1886万
 $24,654/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -67043,7 +67043,7 @@
           <t>H | 644呎 (3房)
 $1424万
 $22,115/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -67058,7 +67058,7 @@
           <t>A | 643呎 (3房)
 $1504万
 $23,393/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -67066,7 +67066,7 @@
           <t>B | 444呎 (2房)
 $1200万
 $27,023/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -67074,7 +67074,7 @@
           <t>C | 438呎 (2房)
 $1207万
 $27,562/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -67082,7 +67082,7 @@
           <t>D | 445呎 (2房)
 $926万
 $20,820/呎
-(25年-10月-02日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -67090,7 +67090,7 @@
           <t>E | 426呎 (2房)
 $898万
 $21,085/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -67098,7 +67098,7 @@
           <t>F | 448呎 (2房)
 $1301万
 $29,045/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -67106,7 +67106,7 @@
           <t>G | 765呎 (3房)
 $1886万
 $24,654/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -67114,7 +67114,7 @@
           <t>H | 644呎 (3房)
 $1424万
 $22,115/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67129,7 +67129,7 @@
           <t>A | 643呎 (3房)
 $1466万
 $22,807/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -67137,7 +67137,7 @@
           <t>B | 443呎 (2房)
 $1186万
 $26,761/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -67145,7 +67145,7 @@
           <t>C | 438呎 (2房)
 $1140万
 $26,037/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -67153,7 +67153,7 @@
           <t>D | 445呎 (2房)
 $916万
 $20,580/呎
-(24年-12月-11日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -67161,7 +67161,7 @@
           <t>E | 426呎 (2房)
 $888万
 $20,843/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -67169,7 +67169,7 @@
           <t>F | 448呎 (2房)
 $931万
 $20,781/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -67177,7 +67177,7 @@
           <t>G | 765呎 (3房)
 $1906万
 $24,919/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -67185,7 +67185,7 @@
           <t>H | 644呎 (3房)
 $1416万
 $21,983/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67200,7 +67200,7 @@
           <t>A | 643呎 (3房)
 $1458万
 $22,683/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -67208,7 +67208,7 @@
           <t>B | 444呎 (2房)
 $1178万
 $26,541/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -67216,7 +67216,7 @@
           <t>C | 438呎 (2房)
 $925万
 $21,116/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -67224,7 +67224,7 @@
           <t>D | 445呎 (2房)
 $910万
 $20,458/呎
-(25年-01月-23日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -67232,7 +67232,7 @@
           <t>E | 426呎 (2房)
 $883万
 $20,718/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -67240,7 +67240,7 @@
           <t>F | 448呎 (2房)
 $926万
 $20,658/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -67248,7 +67248,7 @@
           <t>G | 765呎 (3房)
 $1870万
 $24,447/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -67256,7 +67256,7 @@
           <t>H | 644呎 (3房)
 $1412万
 $21,918/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67271,7 +67271,7 @@
           <t>A | 643呎 (3房)
 $1450万
 $22,557/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -67279,7 +67279,7 @@
           <t>B | 444呎 (2房)
 $1159万
 $26,110/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -67287,7 +67287,7 @@
           <t>C | 438呎 (2房)
 $1179万
 $26,916/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -67295,7 +67295,7 @@
           <t>D | 445呎 (2房)
 $905万
 $20,337/呎
-(25年-06月-29日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -67303,7 +67303,7 @@
           <t>E | 426呎 (2房)
 $877万
 $20,596/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -67311,7 +67311,7 @@
           <t>F | 448呎 (2房)
 $934万
 $20,853/呎
-(24年-07月-23日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -67319,7 +67319,7 @@
           <t>G | 765呎 (3房)
 $1865万
 $24,379/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -67327,7 +67327,7 @@
           <t>H | 644呎 (3房)
 $1407万
 $21,851/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67342,7 +67342,7 @@
           <t>A | 643呎 (3房)
 $1785万
 $27,760/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -67350,7 +67350,7 @@
           <t>B | 444呎 (2房)
 $1101万
 $24,802/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -67358,7 +67358,7 @@
           <t>C | 438呎 (2房)
 $1172万
 $26,756/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -67366,7 +67366,7 @@
           <t>D | 445呎 (2房)
 $900万
 $20,216/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -67374,7 +67374,7 @@
           <t>E | 426呎 (2房)
 $872万
 $20,474/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -67382,7 +67382,7 @@
           <t>F | 448呎 (2房)
 $915万
 $20,420/呎
-(24年-05月-08日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -67390,7 +67390,7 @@
           <t>G | 765呎 (3房)
 $1860万
 $24,310/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -67398,7 +67398,7 @@
           <t>H | 644呎 (3房)
 $1403万
 $21,786/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67413,7 +67413,7 @@
           <t>A | 643呎 (3房)
 $1775万
 $27,607/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -67421,7 +67421,7 @@
           <t>B | 444呎 (2房)
 $1094万
 $24,649/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -67429,7 +67429,7 @@
           <t>C | 438呎 (2房)
 $1165万
 $26,594/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -67437,7 +67437,7 @@
           <t>D | 444呎 (2房)
 $1140万
 $25,676/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -67445,7 +67445,7 @@
           <t>E | 426呎 (2房)
 $1141万
 $26,777/呎
-(21年-09月-06日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -67453,7 +67453,7 @@
           <t>F | 448呎 (2房)
 $909万
 $20,299/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -67461,7 +67461,7 @@
           <t>G | 765呎 (3房)
 $2074万
 $27,118/呎
-(23年-08月-17日)</t>
+(23年-08月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -67469,7 +67469,7 @@
           <t>H | 644呎 (3房)
 $1399万
 $21,720/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67484,7 +67484,7 @@
           <t>A | 643呎 (3房)
 $1765万
 $27,453/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -67492,7 +67492,7 @@
           <t>B | 444呎 (2房)
 $1088万
 $24,495/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -67500,7 +67500,7 @@
           <t>C | 438呎 (2房)
 $1106万
 $25,263/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -67508,7 +67508,7 @@
           <t>D | 444呎 (2房)
 $1186万
 $26,700/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -67516,7 +67516,7 @@
           <t>E | 426呎 (2房)
 $1173万
 $27,528/呎
-(21年-08月-10日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -67524,7 +67524,7 @@
           <t>F | 448呎 (2房)
 $904万
 $20,179/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -67532,7 +67532,7 @@
           <t>G | 765呎 (3房)
 $2263万
 $29,583/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -67540,7 +67540,7 @@
           <t>H | 644呎 (3房)
 $1395万
 $21,657/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -67555,7 +67555,7 @@
           <t>A | 643呎 (3房)
 $1755万
 $27,297/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -67563,7 +67563,7 @@
           <t>B | 444呎 (2房)
 $1108万
 $24,959/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -67571,7 +67571,7 @@
           <t>C | 438呎 (2房)
 $1163万
 $26,562/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -67579,7 +67579,7 @@
           <t>D | 445呎 (2房)
 $1178万
 $26,481/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -67587,7 +67587,7 @@
           <t>E | 426呎 (2房)
 $1166万
 $27,362/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -67595,7 +67595,7 @@
           <t>F | 448呎 (2房)
 $899万
 $20,058/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -67603,7 +67603,7 @@
           <t>G | 765呎 (3房)
 $2108万
 $27,556/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -67611,7 +67611,7 @@
           <t>H | 644呎 (3房)
 $1390万
 $21,590/呎
-(24年-01月-18日)</t>
+(24年-01月)</t>
         </is>
       </c>
     </row>
@@ -67626,7 +67626,7 @@
           <t>A | 643呎 (3房)
 $1826万
 $28,398/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -67634,7 +67634,7 @@
           <t>B | 443呎 (2房)
 $1065万
 $24,034/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -67642,7 +67642,7 @@
           <t>C | 438呎 (2房)
 $1144万
 $26,107/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -67650,7 +67650,7 @@
           <t>D | 445呎 (2房)
 $1119万
 $25,155/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -67658,7 +67658,7 @@
           <t>E | 426呎 (2房)
 $1159万
 $27,197/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -67666,7 +67666,7 @@
           <t>F | 447呎 (2房)
 $1180万
 $26,389/呎
-(21年-08月-18日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -67674,7 +67674,7 @@
           <t>G | 765呎 (3房)
 $2193万
 $28,668/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -67682,7 +67682,7 @@
           <t>H | 644呎 (3房)
 $1386万
 $21,526/呎
-(24年-02月-07日)</t>
+(24年-02月)</t>
         </is>
       </c>
     </row>
@@ -67697,7 +67697,7 @@
           <t>A | 643呎 (3房)
 $1826万
 $28,398/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -67705,7 +67705,7 @@
           <t>B | 443呎 (2房)
 $1052万
 $23,758/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -67713,7 +67713,7 @@
           <t>C | 438呎 (2房)
 $1144万
 $26,107/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -67721,7 +67721,7 @@
           <t>D | 445呎 (2房)
 $1119万
 $25,155/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -67729,7 +67729,7 @@
           <t>E | 426呎 (2房)
 $1135万
 $26,653/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -67737,7 +67737,7 @@
           <t>F | 447呎 (2房)
 $1180万
 $26,389/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -67745,7 +67745,7 @@
           <t>G | 765呎 (3房)
 $2193万
 $28,668/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -67753,7 +67753,7 @@
           <t>H | 644呎 (3房)
 $1881万
 $29,207/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -67768,7 +67768,7 @@
           <t>A | 643呎 (3房)
 $1426万
 $22,180/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -67776,7 +67776,7 @@
           <t>B | 444呎 (2房)
 $1087万
 $24,486/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -67784,7 +67784,7 @@
           <t>C | 438呎 (2房)
 $1092万
 $24,932/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -67792,7 +67792,7 @@
           <t>D | 445呎 (2房)
 $1118万
 $25,135/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -67800,7 +67800,7 @@
           <t>E | 426呎 (2房)
 $1121万
 $26,324/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -67808,7 +67808,7 @@
           <t>F | 447呎 (2房)
 $1165万
 $26,072/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -67816,7 +67816,7 @@
           <t>G | 765呎 (3房)
 $2168万
 $28,344/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -67824,7 +67824,7 @@
           <t>H | 644呎 (3房)
 $1550万
 $24,071/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -67839,7 +67839,7 @@
           <t>A | 643呎 (3房)
 $1716万
 $26,680/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -67847,7 +67847,7 @@
           <t>B | 443呎 (2房)
 $1033万
 $23,309/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -67855,7 +67855,7 @@
           <t>C | 438呎 (2房)
 $1089万
 $24,854/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -67863,7 +67863,7 @@
           <t>D | 444呎 (2房)
 $1150万
 $25,892/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -67871,7 +67871,7 @@
           <t>E | 426呎 (2房)
 $1114万
 $26,162/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -67879,7 +67879,7 @@
           <t>F | 448呎 (2房)
 $1212万
 $27,049/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -67887,7 +67887,7 @@
           <t>G | 765呎 (3房)
 $2061万
 $26,937/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -67895,7 +67895,7 @@
           <t>H | 643呎 (3房)
 $1767万
 $27,487/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -67910,7 +67910,7 @@
           <t>A | 643呎 (3房)
 $1731万
 $26,919/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -67918,7 +67918,7 @@
           <t>B | 444呎 (2房)
 $1073万
 $24,176/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -67926,7 +67926,7 @@
           <t>C | 438呎 (2房)
 $1082万
 $24,696/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -67934,7 +67934,7 @@
           <t>D | 444呎 (2房)
 $1092万
 $24,595/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -67942,7 +67942,7 @@
           <t>E | 426呎 (2房)
 $1059万
 $24,850/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -67950,7 +67950,7 @@
           <t>F | 447呎 (2房)
 $1204万
 $26,942/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -67958,7 +67958,7 @@
           <t>G | 765呎 (3房)
 $2049万
 $26,783/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -67966,7 +67966,7 @@
           <t>H | 644呎 (3房)
 $1432万
 $22,239/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -67981,7 +67981,7 @@
           <t>A | 643呎 (3房)
 $1645万
 $25,580/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -67989,7 +67989,7 @@
           <t>B | 443呎 (2房)
 $1019万
 $23,009/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -67997,7 +67997,7 @@
           <t>C | 438呎 (2房)
 $1027万
 $23,457/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -68005,7 +68005,7 @@
           <t>D | 445呎 (2房)
 $1135万
 $25,512/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -68013,7 +68013,7 @@
           <t>E | 426呎 (2房)
 $1101万
 $25,836/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -68021,7 +68021,7 @@
           <t>F | 447呎 (2房)
 $1157万
 $25,888/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -68029,7 +68029,7 @@
           <t>G | 765呎 (3房)
 $2037万
 $26,627/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -68037,7 +68037,7 @@
           <t>H | 644呎 (3房)
 $1828万
 $28,384/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68052,7 +68052,7 @@
           <t>A | 643呎 (3房)
 $1660万
 $25,821/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -68060,7 +68060,7 @@
           <t>B | 443呎 (2房)
 $1059万
 $23,914/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -68068,7 +68068,7 @@
           <t>C | 438呎 (2房)
 $1068万
 $24,384/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -68076,7 +68076,7 @@
           <t>D | 444呎 (2房)
 $1078万
 $24,284/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -68084,7 +68084,7 @@
           <t>E | 426呎 (2房)
 $1045万
 $24,538/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -68092,7 +68092,7 @@
           <t>F | 448呎 (2房)
 $1190万
 $26,551/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -68100,7 +68100,7 @@
           <t>G | 765呎 (3房)
 $1804万
 $23,588/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -68108,7 +68108,7 @@
           <t>H | 643呎 (3房)
 $1720万
 $26,751/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68123,7 +68123,7 @@
           <t>A | 643呎 (3房)
 $1505万
 $23,406/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -68131,7 +68131,7 @@
           <t>B | 443呎 (2房)
 $1053万
 $23,761/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -68139,7 +68139,7 @@
           <t>C | 438呎 (2房)
 $1061万
 $24,226/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -68147,7 +68147,7 @@
           <t>D | 444呎 (2房)
 $1071万
 $24,131/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -68155,7 +68155,7 @@
           <t>E | 426呎 (2房)
 $1087万
 $25,507/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -68163,7 +68163,7 @@
           <t>F | 447呎 (2房)
 $1143万
 $25,568/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -68171,7 +68171,7 @@
           <t>G | 765呎 (3房)
 $1799万
 $23,518/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -68179,7 +68179,7 @@
           <t>H | 643呎 (3房)
 $1642万
 $25,543/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68194,7 +68194,7 @@
           <t>A | 643呎 (3房)
 $1479万
 $23,006/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -68202,7 +68202,7 @@
           <t>B | 443呎 (2房)
 $1046万
 $23,600/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -68210,7 +68210,7 @@
           <t>C | 438呎 (2房)
 $1019万
 $23,272/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -68218,7 +68218,7 @@
           <t>D | 445呎 (2房)
 $1114万
 $25,027/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -68226,7 +68226,7 @@
           <t>E | 426呎 (2房)
 $1080万
 $25,345/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -68234,7 +68234,7 @@
           <t>F | 447呎 (2房)
 $1123万
 $25,116/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -68242,7 +68242,7 @@
           <t>G | 765呎 (3房)
 $1991万
 $26,027/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -68250,7 +68250,7 @@
           <t>H | 643呎 (3房)
 $1709万
 $26,572/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68265,7 +68265,7 @@
           <t>A | 643呎 (3房)
 $1548万
 $24,070/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -68273,7 +68273,7 @@
           <t>B | 444呎 (2房)
 $999万
 $22,507/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -68281,7 +68281,7 @@
           <t>C | 438呎 (2房)
 $1008万
 $23,007/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -68289,7 +68289,7 @@
           <t>D | 444呎 (2房)
 $1114万
 $25,083/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -68297,7 +68297,7 @@
           <t>E | 426呎 (2房)
 $1080万
 $25,345/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -68305,7 +68305,7 @@
           <t>F | 447呎 (2房)
 $1136万
 $25,407/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -68313,7 +68313,7 @@
           <t>G | 765呎 (3房)
 $1925万
 $25,165/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -68321,7 +68321,7 @@
           <t>H | 643呎 (3房)
 $1690万
 $26,281/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68336,7 +68336,7 @@
           <t>A | 643呎 (3房)
 $1460万
 $22,706/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -68344,7 +68344,7 @@
           <t>B | 443呎 (2房)
 $1032万
 $23,287/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -68352,7 +68352,7 @@
           <t>C | 438呎 (2房)
 $1041万
 $23,758/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -68360,7 +68360,7 @@
           <t>D | 444呎 (2房)
 $1051万
 $23,667/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -68368,7 +68368,7 @@
           <t>E | 426呎 (2房)
 $1019万
 $23,913/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -68376,7 +68376,7 @@
           <t>F | 447呎 (2房)
 $1108万
 $24,796/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -68384,7 +68384,7 @@
           <t>G | 765呎 (3房)
 $1879万
 $24,567/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -68392,7 +68392,7 @@
           <t>H | 643呎 (3房)
 $1669万
 $25,955/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68407,7 +68407,7 @@
           <t>A | 643呎 (3房)
 $1450万
 $22,557/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -68415,7 +68415,7 @@
           <t>B | 443呎 (2房)
 $979万
 $22,106/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -68423,7 +68423,7 @@
           <t>C | 438呎 (2房)
 $1034万
 $23,598/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -68431,7 +68431,7 @@
           <t>D | 444呎 (2房)
 $1044万
 $23,511/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -68439,7 +68439,7 @@
           <t>E | 426呎 (2房)
 $1059万
 $24,854/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -68447,7 +68447,7 @@
           <t>F | 447呎 (2房)
 $1101万
 $24,638/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -68455,7 +68455,7 @@
           <t>G | 765呎 (3房)
 $1868万
 $24,413/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -68463,7 +68463,7 @@
           <t>H | 643呎 (3房)
 $1658万
 $25,788/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68478,7 +68478,7 @@
           <t>A | 643呎 (3房)
 $1507万
 $23,443/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -68486,7 +68486,7 @@
           <t>B | 444呎 (2房)
 $973万
 $21,908/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -68494,7 +68494,7 @@
           <t>C | 438呎 (2房)
 $1027万
 $23,443/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -68502,7 +68502,7 @@
           <t>D | 444呎 (2房)
 $1085万
 $24,437/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -68510,7 +68510,7 @@
           <t>E | 426呎 (2房)
 $1005万
 $23,601/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -68518,7 +68518,7 @@
           <t>F | 447呎 (2房)
 $1145万
 $25,611/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -68526,7 +68526,7 @@
           <t>G | 765呎 (3房)
 $1856万
 $24,259/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -68534,7 +68534,7 @@
           <t>H | 644呎 (3房)
 $1575万
 $24,453/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -68549,7 +68549,7 @@
           <t>A | 643呎 (3房)
 $1431万
 $22,257/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -68557,7 +68557,7 @@
           <t>B | 443呎 (2房)
 $966万
 $21,806/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -68565,7 +68565,7 @@
           <t>C | 438呎 (2房)
 $812万
 $18,527/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -68573,7 +68573,7 @@
           <t>D | 445呎 (2房)
 $1030万
 $23,151/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -68581,7 +68581,7 @@
           <t>E | 426呎 (2房)
 $999万
 $23,444/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -68589,7 +68589,7 @@
           <t>F | 447呎 (2房)
 $1087万
 $24,320/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -68597,7 +68597,7 @@
           <t>G | 765呎 (3房)
 $1844万
 $24,105/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -68605,7 +68605,7 @@
           <t>H | 644呎 (3房)
 $1221万
 $18,958/呎
-(23年-12月-07日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -68620,7 +68620,7 @@
           <t>A | 643呎 (3房)
 $1487万
 $23,129/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -68628,7 +68628,7 @@
           <t>B | 443呎 (2房)
 $948万
 $21,406/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -68636,7 +68636,7 @@
           <t>C | 438呎 (2房)
 $1000万
 $22,831/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -68644,7 +68644,7 @@
           <t>D | 445呎 (2房)
 $1059万
 $23,791/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -68652,7 +68652,7 @@
           <t>E | 426呎 (2房)
 $981万
 $23,028/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -68660,7 +68660,7 @@
           <t>F | 448呎 (2房)
 $1117万
 $24,942/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -68668,7 +68668,7 @@
           <t>G | 765呎 (3房)
 $1832万
 $23,950/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -68676,7 +68676,7 @@
           <t>H | 644呎 (3房)
 $1195万
 $18,557/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -68691,7 +68691,7 @@
           <t>A | 643呎 (3房)
 $1396万
 $21,708/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -68699,7 +68699,7 @@
           <t>B | 443呎 (2房)
 $960万
 $21,679/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -68707,7 +68707,7 @@
           <t>C | 438呎 (2房)
 $972万
 $22,187/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -68715,7 +68715,7 @@
           <t>D | 445呎 (2房)
 $1028万
 $23,092/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -68723,7 +68723,7 @@
           <t>E | 426呎 (2房)
 $996万
 $23,387/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -68731,7 +68731,7 @@
           <t>F | 447呎 (2房)
 $1049万
 $23,472/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -68739,7 +68739,7 @@
           <t>G | 765呎 (3房)
 $1884万
 $24,626/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -68747,7 +68747,7 @@
           <t>H | 644呎 (3房)
 $1174万
 $18,234/呎
-(23年-12月-21日)</t>
+(23年-12月)</t>
         </is>
       </c>
     </row>
@@ -68909,7 +68909,7 @@
           <t>A | 1484呎 (4+房)
 $5095万
 $34,335/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -68919,7 +68919,7 @@
           <t>D | 329呎 (1房)
 $862万
 $26,204/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -68927,7 +68927,7 @@
           <t>E | 330呎 (1房)
 $647万
 $19,597/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -68935,7 +68935,7 @@
           <t>F | 330呎 (1房)
 $684万
 $20,715/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -68943,7 +68943,7 @@
           <t>G | 338呎 (1房)
 $975万
 $28,840/呎
-(21年-09月-20日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -68951,7 +68951,7 @@
           <t>H | 598呎 (3房)
 $1565万
 $26,172/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
     </row>
@@ -68966,7 +68966,7 @@
           <t>A | 454呎 (2房)
 $1188万
 $26,163/呎
-(22年-09月-22日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -68974,7 +68974,7 @@
           <t>B | 564呎 (2房)
 $1227万
 $21,761/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -68982,7 +68982,7 @@
           <t>C | 460呎 (2房)
 $954万
 $20,750/呎
-(26年-03月-22日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -68990,7 +68990,7 @@
           <t>D | 330呎 (1房)
 $860万
 $26,055/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -68998,7 +68998,7 @@
           <t>E | 330呎 (1房)
 $643万
 $19,485/呎
-(25年-10月-07日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -69006,7 +69006,7 @@
           <t>F | 330呎 (1房)
 $946万
 $28,676/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -69014,7 +69014,7 @@
           <t>G | 338呎 (1房)
 $696万
 $20,595/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -69022,7 +69022,7 @@
           <t>H | 597呎 (3房)
 $1405万
 $23,538/呎
-(26年-04月-27日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>
@@ -69037,7 +69037,7 @@
           <t>A | 454呎 (2房)
 $1209万
 $26,639/呎
-(22年-09月-19日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -69045,7 +69045,7 @@
           <t>B | 564呎 (2房)
 $1221万
 $21,644/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -69053,7 +69053,7 @@
           <t>C | 460呎 (2房)
 $1228万
 $26,704/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -69061,7 +69061,7 @@
           <t>D | 330呎 (1房)
 $894万
 $27,103/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -69069,7 +69069,7 @@
           <t>E | 330呎 (1房)
 $922万
 $27,942/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -69077,7 +69077,7 @@
           <t>F | 330呎 (1房)
 $676万
 $20,479/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -69085,7 +69085,7 @@
           <t>G | 338呎 (1房)
 $703万
 $20,793/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -69093,7 +69093,7 @@
           <t>H | 597呎 (3房)
 $1398万
 $23,412/呎
-(24年-08月-29日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -69108,7 +69108,7 @@
           <t>A | 454呎 (2房)
 $1174万
 $25,852/呎
-(23年-03月-16日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -69116,7 +69116,7 @@
           <t>B | 564呎 (2房)
 $1222万
 $21,672/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -69124,7 +69124,7 @@
           <t>C | 460呎 (2房)
 $1278万
 $27,778/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -69132,7 +69132,7 @@
           <t>D | 330呎 (1房)
 $889万
 $26,945/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -69140,7 +69140,7 @@
           <t>E | 330呎 (1房)
 $917万
 $27,779/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -69148,7 +69148,7 @@
           <t>F | 330呎 (1房)
 $672万
 $20,361/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -69156,7 +69156,7 @@
           <t>G | 338呎 (1房)
 $958万
 $28,346/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -69164,7 +69164,7 @@
           <t>H | 597呎 (3房)
 $1474万
 $24,683/呎
-(25年-09月-29日)</t>
+(25年-09月)</t>
         </is>
       </c>
     </row>
@@ -69179,7 +69179,7 @@
           <t>A | 454呎 (2房)
 $1167万
 $25,698/呎
-(23年-03月-16日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -69187,7 +69187,7 @@
           <t>B | 564呎 (2房)
 $1234万
 $21,888/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -69195,7 +69195,7 @@
           <t>C | 460呎 (2房)
 $1270万
 $27,615/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -69203,7 +69203,7 @@
           <t>D | 330呎 (1房)
 $884万
 $26,788/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -69211,7 +69211,7 @@
           <t>E | 330呎 (1房)
 $881万
 $26,703/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -69219,7 +69219,7 @@
           <t>F | 330呎 (1房)
 $678万
 $20,552/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -69227,7 +69227,7 @@
           <t>G | 338呎 (1房)
 $684万
 $20,240/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -69235,7 +69235,7 @@
           <t>H | 597呎 (3房)
 $1382万
 $23,157/呎
-(25年-01月-14日)</t>
+(25年-01月)</t>
         </is>
       </c>
     </row>
@@ -69250,7 +69250,7 @@
           <t>A | 454呎 (2房)
 $1160万
 $25,544/呎
-(22年-05月-30日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -69258,7 +69258,7 @@
           <t>B | 564呎 (2房)
 $1190万
 $21,105/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -69266,7 +69266,7 @@
           <t>C | 460呎 (2房)
 $1263万
 $27,454/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -69274,7 +69274,7 @@
           <t>D | 330呎 (1房)
 $879万
 $26,630/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -69282,7 +69282,7 @@
           <t>E | 330呎 (1房)
 $866万
 $26,242/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -69290,7 +69290,7 @@
           <t>F | 330呎 (1房)
 $631万
 $19,115/呎
-(25年-08月-14日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -69298,7 +69298,7 @@
           <t>G | 338呎 (1房)
 $680万
 $20,121/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -69306,7 +69306,7 @@
           <t>H | 597呎 (3房)
 $1375万
 $23,030/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -69321,7 +69321,7 @@
           <t>A | 454呎 (2房)
 $1181万
 $26,009/呎
-(22年-09月-29日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -69329,7 +69329,7 @@
           <t>B | 564呎 (2房)
 $1184万
 $20,988/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -69337,7 +69337,7 @@
           <t>C | 460呎 (2房)
 $1256万
 $27,293/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -69345,7 +69345,7 @@
           <t>D | 330呎 (1房)
 $874万
 $26,476/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -69353,7 +69353,7 @@
           <t>E | 330呎 (1房)
 $861万
 $26,088/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -69361,7 +69361,7 @@
           <t>F | 330呎 (1房)
 $627万
 $19,000/呎
-(25年-08月-24日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -69369,7 +69369,7 @@
           <t>G | 338呎 (1房)
 $676万
 $20,003/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -69377,7 +69377,7 @@
           <t>H | 597呎 (3房)
 $1367万
 $22,905/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -69392,7 +69392,7 @@
           <t>A | 454呎 (2房)
 $1251万
 $27,546/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -69400,7 +69400,7 @@
           <t>B | 564呎 (2房)
 $1184万
 $20,988/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -69408,7 +69408,7 @@
           <t>C | 460呎 (2房)
 $1200万
 $26,087/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -69416,7 +69416,7 @@
           <t>D | 330呎 (1房)
 $874万
 $26,476/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -69424,7 +69424,7 @@
           <t>E | 330呎 (1房)
 $861万
 $26,088/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -69432,7 +69432,7 @@
           <t>F | 330呎 (1房)
 $901万
 $27,294/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -69440,7 +69440,7 @@
           <t>G | 338呎 (1房)
 $941万
 $27,849/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -69448,7 +69448,7 @@
           <t>H | 597呎 (3房)
 $1387万
 $23,235/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -69463,7 +69463,7 @@
           <t>A | 454呎 (2房)
 $1144万
 $25,189/呎
-(22年-09月-22日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -69471,7 +69471,7 @@
           <t>B | 564呎 (2房)
 $1189万
 $21,083/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -69479,7 +69479,7 @@
           <t>C | 460呎 (2房)
 $1241万
 $26,970/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -69487,7 +69487,7 @@
           <t>D | 330呎 (1房)
 $825万
 $25,006/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -69495,7 +69495,7 @@
           <t>E | 330呎 (1房)
 $890万
 $26,970/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -69503,7 +69503,7 @@
           <t>F | 330呎 (1房)
 $607万
 $18,403/呎
-(25年-08月-19日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -69511,7 +69511,7 @@
           <t>G | 338呎 (1房)
 $930万
 $27,521/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -69519,7 +69519,7 @@
           <t>H | 597呎 (3房)
 $1372万
 $22,977/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -69534,7 +69534,7 @@
           <t>A | 454呎 (2房)
 $1140万
 $25,115/呎
-(22年-05月-29日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -69542,7 +69542,7 @@
           <t>B | 564呎 (2房)
 $1164万
 $20,640/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -69550,7 +69550,7 @@
           <t>C | 460呎 (2房)
 $938万
 $20,398/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -69558,7 +69558,7 @@
           <t>D | 330呎 (1房)
 $820万
 $24,855/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -69566,7 +69566,7 @@
           <t>E | 330呎 (1房)
 $885万
 $26,809/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -69574,7 +69574,7 @@
           <t>F | 330呎 (1房)
 $885万
 $26,809/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -69582,7 +69582,7 @@
           <t>G | 338呎 (1房)
 $925万
 $27,358/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -69590,7 +69590,7 @@
           <t>H | 597呎 (3房)
 $1364万
 $22,848/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -69605,7 +69605,7 @@
           <t>A | 454呎 (2房)
 $1164万
 $25,648/呎
-(22年-09月-12日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -69613,7 +69613,7 @@
           <t>B | 564呎 (2房)
 $1158万
 $20,525/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -69621,7 +69621,7 @@
           <t>C | 460呎 (2房)
 $1226万
 $26,648/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -69629,7 +69629,7 @@
           <t>D | 330呎 (1房)
 $853万
 $25,848/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -69637,7 +69637,7 @@
           <t>E | 330呎 (1房)
 $840万
 $25,470/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -69645,7 +69645,7 @@
           <t>F | 330呎 (1房)
 $879万
 $26,645/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -69653,7 +69653,7 @@
           <t>G | 338呎 (1房)
 $919万
 $27,189/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -69661,7 +69661,7 @@
           <t>H | 598呎 (3房)
 $1664万
 $27,828/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -69676,7 +69676,7 @@
           <t>A | 454呎 (2房)
 $1174万
 $25,870/呎
-(22年-06月-09日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -69684,7 +69684,7 @@
           <t>B | 564呎 (2房)
 $1169万
 $20,730/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -69692,7 +69692,7 @@
           <t>C | 460呎 (2房)
 $1164万
 $25,315/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -69700,7 +69700,7 @@
           <t>D | 330呎 (1房)
 $810万
 $24,555/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -69708,7 +69708,7 @@
           <t>E | 330呎 (1房)
 $874万
 $26,485/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -69716,7 +69716,7 @@
           <t>F | 330呎 (1房)
 $874万
 $26,485/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -69724,7 +69724,7 @@
           <t>G | 338呎 (1房)
 $895万
 $26,485/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -69732,7 +69732,7 @@
           <t>H | 597呎 (3房)
 $1330万
 $22,270/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -69747,7 +69747,7 @@
           <t>A | 454呎 (2房)
 $1130万
 $24,888/呎
-(22年-05月-24日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -69755,7 +69755,7 @@
           <t>B | 564呎 (2房)
 $1145万
 $20,294/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -69763,7 +69763,7 @@
           <t>C | 460呎 (2房)
 $922万
 $20,033/呎
-(26年-03月-23日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -69771,7 +69771,7 @@
           <t>D | 330呎 (1房)
 $805万
 $24,406/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -69779,7 +69779,7 @@
           <t>E | 330呎 (1房)
 $869万
 $26,324/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -69787,7 +69787,7 @@
           <t>F | 330呎 (1房)
 $869万
 $26,324/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -69795,7 +69795,7 @@
           <t>G | 338呎 (1房)
 $622万
 $18,396/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -69803,7 +69803,7 @@
           <t>H | 597呎 (3房)
 $1322万
 $22,142/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -69818,7 +69818,7 @@
           <t>A | 454呎 (2房)
 $1127万
 $24,815/呎
-(22年-06月-05日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -69826,7 +69826,7 @@
           <t>B | 564呎 (2房)
 $1138万
 $20,179/呎
-(24年-03月-02日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -69834,7 +69834,7 @@
           <t>C | 460呎 (2房)
 $1204万
 $26,163/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -69842,7 +69842,7 @@
           <t>D | 330呎 (1房)
 $837万
 $25,376/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -69850,7 +69850,7 @@
           <t>E | 330呎 (1房)
 $863万
 $26,161/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -69858,7 +69858,7 @@
           <t>F | 330呎 (1房)
 $863万
 $26,161/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -69866,7 +69866,7 @@
           <t>G | 338呎 (1房)
 $884万
 $26,163/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -69874,7 +69874,7 @@
           <t>H | 598呎 (3房)
 $1636万
 $27,356/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
     </row>
@@ -69889,7 +69889,7 @@
           <t>A | 454呎 (2房)
 $1178万
 $25,941/呎
-(21年-12月-13日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -69897,7 +69897,7 @@
           <t>B | 564呎 (2房)
 $1149万
 $20,378/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -69905,7 +69905,7 @@
           <t>C | 460呎 (2房)
 $1196万
 $26,002/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -69913,7 +69913,7 @@
           <t>D | 330呎 (1房)
 $832万
 $25,221/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -69921,7 +69921,7 @@
           <t>E | 330呎 (1房)
 $832万
 $25,221/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -69929,7 +69929,7 @@
           <t>F | 330呎 (1房)
 $820万
 $24,852/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -69937,7 +69937,7 @@
           <t>G | 338呎 (1房)
 $879万
 $26,000/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -69945,7 +69945,7 @@
           <t>H | 598呎 (3房)
 $1720万
 $28,769/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -69960,7 +69960,7 @@
           <t>A | 454呎 (2房)
 $1147万
 $25,264/呎
-(22年-05月-16日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -69968,7 +69968,7 @@
           <t>B | 564呎 (2房)
 $1457万
 $25,830/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -69976,7 +69976,7 @@
           <t>C | 460呎 (2房)
 $1188万
 $25,837/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -69984,7 +69984,7 @@
           <t>D | 330呎 (1房)
 $827万
 $25,061/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -69992,7 +69992,7 @@
           <t>E | 330呎 (1房)
 $827万
 $25,061/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -70000,7 +70000,7 @@
           <t>F | 330呎 (1房)
 $815万
 $24,697/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -70008,7 +70008,7 @@
           <t>G | 338呎 (1房)
 $835万
 $24,695/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -70016,7 +70016,7 @@
           <t>H | 597呎 (3房)
 $1636万
 $27,399/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -70031,7 +70031,7 @@
           <t>A | 454呎 (2房)
 $1147万
 $25,264/呎
-(22年-05月-29日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -70039,7 +70039,7 @@
           <t>B | 564呎 (2房)
 $1524万
 $27,025/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -70047,7 +70047,7 @@
           <t>C | 460呎 (2房)
 $1188万
 $25,837/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -70055,7 +70055,7 @@
           <t>D | 330呎 (1房)
 $827万
 $25,061/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -70063,7 +70063,7 @@
           <t>E | 330呎 (1房)
 $608万
 $18,415/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -70071,7 +70071,7 @@
           <t>F | 330呎 (1房)
 $596万
 $18,058/呎
-(25年-07月-30日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -70079,7 +70079,7 @@
           <t>G | 338呎 (1房)
 $873万
 $25,837/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -70087,7 +70087,7 @@
           <t>H | 598呎 (3房)
 $1617万
 $27,040/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70102,7 +70102,7 @@
           <t>A | 454呎 (2房)
 $1140万
 $25,115/呎
-(22年-05月-15日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -70110,7 +70110,7 @@
           <t>B | 564呎 (2房)
 $1157万
 $20,512/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -70118,7 +70118,7 @@
           <t>C | 460呎 (2房)
 $1138万
 $24,750/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -70126,7 +70126,7 @@
           <t>D | 330呎 (1房)
 $817万
 $24,748/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -70134,7 +70134,7 @@
           <t>E | 330呎 (1房)
 $781万
 $23,655/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -70142,7 +70142,7 @@
           <t>F | 330呎 (1房)
 $817万
 $24,748/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -70150,7 +70150,7 @@
           <t>G | 338呎 (1房)
 $824万
 $24,388/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -70158,7 +70158,7 @@
           <t>H | 597呎 (3房)
 $1672万
 $28,007/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -70173,7 +70173,7 @@
           <t>A | 454呎 (2房)
 $1110万
 $24,447/呎
-(22年-05月-15日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -70181,7 +70181,7 @@
           <t>B | 564呎 (2房)
 $1498万
 $26,551/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -70189,7 +70189,7 @@
           <t>C | 460呎 (2房)
 $1081万
 $23,507/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -70197,7 +70197,7 @@
           <t>D | 330呎 (1房)
 $812万
 $24,594/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -70205,7 +70205,7 @@
           <t>E | 330呎 (1房)
 $776万
 $23,506/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -70213,7 +70213,7 @@
           <t>F | 330呎 (1房)
 $776万
 $23,506/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -70221,7 +70221,7 @@
           <t>G | 338呎 (1房)
 $819万
 $24,234/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -70229,7 +70229,7 @@
           <t>H | 597呎 (3房)
 $1631万
 $27,317/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -70244,7 +70244,7 @@
           <t>A | 454呎 (2房)
 $1133万
 $24,963/呎
-(22年-09月-25日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -70252,7 +70252,7 @@
           <t>B | 564呎 (2房)
 $1423万
 $25,230/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -70260,7 +70260,7 @@
           <t>C | 460呎 (2房)
 $1124万
 $24,437/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -70268,7 +70268,7 @@
           <t>D | 330呎 (1房)
 $806万
 $24,436/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -70276,7 +70276,7 @@
           <t>E | 330呎 (1房)
 $806万
 $24,436/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -70284,7 +70284,7 @@
           <t>F | 330呎 (1房)
 $771万
 $23,358/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -70292,7 +70292,7 @@
           <t>G | 338呎 (1房)
 $852万
 $25,195/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -70300,7 +70300,7 @@
           <t>H | 597呎 (3房)
 $1501万
 $25,147/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70315,7 +70315,7 @@
           <t>A | 454呎 (2房)
 $1130万
 $24,890/呎
-(22年-05月-05日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -70323,7 +70323,7 @@
           <t>B | 564呎 (2房)
 $1414万
 $25,080/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -70331,7 +70331,7 @@
           <t>C | 460呎 (2房)
 $1068万
 $23,207/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -70339,7 +70339,7 @@
           <t>D | 330呎 (1房)
 $775万
 $23,476/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -70347,7 +70347,7 @@
           <t>E | 330呎 (1房)
 $801万
 $24,279/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -70355,7 +70355,7 @@
           <t>F | 330呎 (1房)
 $766万
 $23,206/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -70363,7 +70363,7 @@
           <t>G | 338呎 (1房)
 $846万
 $25,027/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -70371,7 +70371,7 @@
           <t>H | 597呎 (3房)
 $1510万
 $25,286/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70386,7 +70386,7 @@
           <t>A | 454呎 (2房)
 $1086万
 $23,914/呎
-(22年-05月-30日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -70394,7 +70394,7 @@
           <t>B | 564呎 (2房)
 $1392万
 $24,681/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -70402,7 +70402,7 @@
           <t>C | 460呎 (2房)
 $1122万
 $24,389/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -70410,7 +70410,7 @@
           <t>D | 330呎 (1房)
 $796万
 $24,124/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -70418,7 +70418,7 @@
           <t>E | 330呎 (1房)
 $796万
 $24,124/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -70426,7 +70426,7 @@
           <t>F | 330呎 (1房)
 $761万
 $23,058/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -70434,7 +70434,7 @@
           <t>G | 338呎 (1房)
 $599万
 $17,722/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -70442,7 +70442,7 @@
           <t>H | 598呎 (3房)
 $1536万
 $25,691/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70457,7 +70457,7 @@
           <t>A | 454呎 (2房)
 $1074万
 $23,656/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -70465,7 +70465,7 @@
           <t>B | 564呎 (2房)
 $1343万
 $23,805/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -70473,7 +70473,7 @@
           <t>C | 460呎 (2房)
 $1102万
 $23,965/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -70481,7 +70481,7 @@
           <t>D | 330呎 (1房)
 $791万
 $23,964/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -70489,7 +70489,7 @@
           <t>E | 330呎 (1房)
 $791万
 $23,964/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -70497,7 +70497,7 @@
           <t>F | 330呎 (1房)
 $581万
 $17,609/呎
-(25年-02月-10日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -70505,7 +70505,7 @@
           <t>G | 338呎 (1房)
 $798万
 $23,615/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -70513,7 +70513,7 @@
           <t>H | 598呎 (3房)
 $1464万
 $24,488/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70528,7 +70528,7 @@
           <t>A | 454呎 (2房)
 $1068万
 $23,524/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -70536,7 +70536,7 @@
           <t>B | 564呎 (2房)
 $1365万
 $24,202/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -70544,7 +70544,7 @@
           <t>C | 460呎 (2房)
 $1047万
 $22,757/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -70552,7 +70552,7 @@
           <t>D | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -70560,7 +70560,7 @@
           <t>E | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -70568,7 +70568,7 @@
           <t>F | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -70576,7 +70576,7 @@
           <t>G | 338呎 (1房)
 $830万
 $24,547/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -70584,7 +70584,7 @@
           <t>H | 598呎 (3房)
 $1439万
 $24,070/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70599,7 +70599,7 @@
           <t>A | 454呎 (2房)
 $848万
 $18,685/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -70607,7 +70607,7 @@
           <t>B | 564呎 (2房)
 $1305万
 $23,131/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -70615,7 +70615,7 @@
           <t>C | 460呎 (2房)
 $1047万
 $22,757/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -70623,7 +70623,7 @@
           <t>D | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -70631,7 +70631,7 @@
           <t>E | 330呎 (1房)
 $751万
 $22,758/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -70639,7 +70639,7 @@
           <t>F | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -70647,7 +70647,7 @@
           <t>G | 338呎 (1房)
 $793万
 $23,462/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -70655,7 +70655,7 @@
           <t>H | 598呎 (3房)
 $1376万
 $23,007/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70670,7 +70670,7 @@
           <t>A | 454呎 (2房)
 $837万
 $18,445/呎
-(24年-05月-12日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -70678,7 +70678,7 @@
           <t>B | 564呎 (2房)
 $1035万
 $18,344/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -70686,7 +70686,7 @@
           <t>C | 460呎 (2房)
 $1081万
 $23,496/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -70694,7 +70694,7 @@
           <t>D | 330呎 (1房)
 $578万
 $17,524/呎
-(25年-07月-28日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -70702,7 +70702,7 @@
           <t>E | 330呎 (1房)
 $775万
 $23,497/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -70710,7 +70710,7 @@
           <t>F | 330呎 (1房)
 $570万
 $17,264/呎
-(25年-02月-17日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -70718,7 +70718,7 @@
           <t>G | 338呎 (1房)
 $782万
 $23,151/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -70726,7 +70726,7 @@
           <t>H | 598呎 (3房)
 $1358万
 $22,707/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70741,7 +70741,7 @@
           <t>A | 454呎 (2房)
 $1035万
 $22,806/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -70749,7 +70749,7 @@
           <t>B | 564呎 (2房)
 $1279万
 $22,683/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -70757,7 +70757,7 @@
           <t>C | 460呎 (2房)
 $1074万
 $23,339/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -70765,7 +70765,7 @@
           <t>D | 330呎 (1房)
 $574万
 $17,406/呎
-(25年-08月-06日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -70773,7 +70773,7 @@
           <t>E | 330呎 (1房)
 $770万
 $23,336/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -70781,7 +70781,7 @@
           <t>F | 330呎 (1房)
 $770万
 $23,336/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -70789,7 +70789,7 @@
           <t>G | 338呎 (1房)
 $813万
 $24,062/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -70797,7 +70797,7 @@
           <t>H | 598呎 (3房)
 $1349万
 $22,557/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70812,7 +70812,7 @@
           <t>A | 454呎 (2房)
 $1076万
 $23,705/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -70820,7 +70820,7 @@
           <t>B | 564呎 (2房)
 $1021万
 $18,103/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -70828,7 +70828,7 @@
           <t>C | 460呎 (2房)
 $1031万
 $22,413/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -70836,7 +70836,7 @@
           <t>D | 330呎 (1房)
 $765万
 $23,182/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -70844,7 +70844,7 @@
           <t>E | 330呎 (1房)
 $731万
 $22,158/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -70852,7 +70852,7 @@
           <t>F | 330呎 (1房)
 $765万
 $23,182/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -70860,7 +70860,7 @@
           <t>G | 338呎 (1房)
 $808万
 $23,899/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -70868,7 +70868,7 @@
           <t>H | 597呎 (3房)
 $1123万
 $18,811/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -70883,7 +70883,7 @@
           <t>A | 454呎 (2房)
 $1034万
 $22,767/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -70891,7 +70891,7 @@
           <t>B | 564呎 (2房)
 $1321万
 $23,417/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -70899,7 +70899,7 @@
           <t>C | 460呎 (2房)
 $1047万
 $22,761/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -70907,7 +70907,7 @@
           <t>D | 330呎 (1房)
 $718万
 $21,758/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -70915,7 +70915,7 @@
           <t>E | 330呎 (1房)
 $751万
 $22,764/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -70923,7 +70923,7 @@
           <t>F | 330呎 (1房)
 $751万
 $22,764/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -70931,7 +70931,7 @@
           <t>G | 338呎 (1房)
 $758万
 $22,429/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -70939,7 +70939,7 @@
           <t>H | 598呎 (3房)
 $1393万
 $23,288/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -70954,7 +70954,7 @@
           <t>A | 454呎 (2房)
 $1062万
 $23,392/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -70962,7 +70962,7 @@
           <t>B | 564呎 (2房)
 $1254万
 $22,232/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -70970,7 +70970,7 @@
           <t>C | 460呎 (2房)
 $982万
 $21,352/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -70978,7 +70978,7 @@
           <t>D | 330呎 (1房)
 $729万
 $22,085/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -70986,7 +70986,7 @@
           <t>E | 330呎 (1房)
 $697万
 $21,109/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -70994,7 +70994,7 @@
           <t>F | 330呎 (1房)
 $729万
 $22,085/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -71002,7 +71002,7 @@
           <t>G | 338呎 (1房)
 $770万
 $22,766/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -71010,7 +71010,7 @@
           <t>H | 597呎 (3房)
 $1337万
 $22,400/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -71025,7 +71025,7 @@
           <t>A | 454呎 (2房)
 $1043万
 $22,974/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -71033,7 +71033,7 @@
           <t>B | 564呎 (2房)
 $1288万
 $22,842/呎
-(21年-09月-21日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -71041,7 +71041,7 @@
           <t>C | 460呎 (2房)
 $973万
 $21,143/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -71049,7 +71049,7 @@
           <t>D | 330呎 (1房)
 $687万
 $20,809/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -71057,7 +71057,7 @@
           <t>E | 330呎 (1房)
 $687万
 $20,809/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -71065,7 +71065,7 @@
           <t>F | 330呎 (1房)
 $687万
 $20,809/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -71073,7 +71073,7 @@
           <t>G | 338呎 (1房)
 $578万
 $17,101/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -71081,7 +71081,7 @@
           <t>H | 597呎 (3房)
 $1358万
 $22,749/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -71243,7 +71243,7 @@
           <t>A | 777呎 (3房)
 $2160万
 $27,799/呎
-(23年-12月-20日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -71251,7 +71251,7 @@
           <t>B | 766呎 (3房)
 $1943万
 $25,362/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -71259,7 +71259,7 @@
           <t>C | 439呎 (2房)
 $926万
 $21,093/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -71267,7 +71267,7 @@
           <t>D | 427呎 (2房)
 $912万
 $21,370/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -71275,7 +71275,7 @@
           <t>E | 333呎 (1房)
 $713万
 $21,408/呎
-(26年-04月-09日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -71283,7 +71283,7 @@
           <t>F | 445呎 (2房)
 $940万
 $21,126/呎
-(24年-04月-17日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -71291,7 +71291,7 @@
           <t>G | 482呎 (2房)
 $969万
 $20,110/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -71299,7 +71299,7 @@
           <t>H | 787呎 (3房)
 $2439万
 $30,991/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -71314,7 +71314,7 @@
           <t>A | 763呎 (3房)
 $1915万
 $25,101/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -71322,7 +71322,7 @@
           <t>B | 766呎 (3房)
 $2453万
 $32,026/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -71330,7 +71330,7 @@
           <t>C | 439呎 (2房)
 $919万
 $20,925/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -71338,7 +71338,7 @@
           <t>D | 427呎 (2房)
 $907万
 $21,244/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -71346,7 +71346,7 @@
           <t>E | 333呎 (1房)
 $698万
 $20,961/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -71354,7 +71354,7 @@
           <t>F | 445呎 (2房)
 $1172万
 $26,330/呎
-(21年-09月-22日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -71362,7 +71362,7 @@
           <t>G | 482呎 (2房)
 $964万
 $19,994/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -71370,7 +71370,7 @@
           <t>H | 774呎 (3房)
 $2021万
 $26,107/呎
-(24年-12月-02日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -71385,7 +71385,7 @@
           <t>A | 763呎 (3房)
 $1910万
 $25,031/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -71393,7 +71393,7 @@
           <t>B | 766呎 (3房)
 $2333万
 $30,452/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -71401,7 +71401,7 @@
           <t>C | 439呎 (2房)
 $913万
 $20,793/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -71409,7 +71409,7 @@
           <t>D | 427呎 (2房)
 $902万
 $21,115/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -71417,7 +71417,7 @@
           <t>E | 332呎 (1房)
 $888万
 $26,741/呎
-(23年-05月-29日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -71425,7 +71425,7 @@
           <t>F | 445呎 (2房)
 $1232万
 $27,692/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -71433,7 +71433,7 @@
           <t>G | 482呎 (2房)
 $1256万
 $26,050/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -71441,7 +71441,7 @@
           <t>H | 774呎 (3房)
 $2012万
 $25,999/呎
-(24年-09月-26日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -71456,7 +71456,7 @@
           <t>A | 763呎 (3房)
 $1962万
 $25,714/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -71464,7 +71464,7 @@
           <t>B | 766呎 (3房)
 $2213万
 $28,892/呎
-(22年-09月-26日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -71472,7 +71472,7 @@
           <t>C | 439呎 (2房)
 $907万
 $20,667/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -71480,7 +71480,7 @@
           <t>D | 427呎 (2房)
 $896万
 $20,988/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -71488,7 +71488,7 @@
           <t>E | 333呎 (1房)
 $926万
 $27,796/呎
-(21年-08月-02日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -71496,7 +71496,7 @@
           <t>F | 445呎 (2房)
 $910万
 $20,458/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -71504,7 +71504,7 @@
           <t>G | 482呎 (2房)
 $952万
 $19,761/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -71512,7 +71512,7 @@
           <t>H | 774呎 (3房)
 $2053万
 $26,523/呎
-(26年-05月-18日)</t>
+(26年-05月)</t>
         </is>
       </c>
     </row>
@@ -71527,7 +71527,7 @@
           <t>A | 763呎 (3房)
 $1900万
 $24,895/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -71535,7 +71535,7 @@
           <t>B | 766呎 (3房)
 $2202万
 $28,740/呎
-(23年-06月-22日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -71543,7 +71543,7 @@
           <t>C | 439呎 (2房)
 $902万
 $20,542/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -71551,7 +71551,7 @@
           <t>D | 427呎 (2房)
 $891万
 $20,864/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -71559,7 +71559,7 @@
           <t>E | 332呎 (1房)
 $963万
 $29,006/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -71567,7 +71567,7 @@
           <t>F | 445呎 (2房)
 $1151万
 $25,872/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -71575,7 +71575,7 @@
           <t>G | 482呎 (2房)
 $1298万
 $26,936/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -71583,7 +71583,7 @@
           <t>H | 774呎 (3房)
 $2004万
 $25,898/呎
-(24年-07月-29日)</t>
+(24年-07月)</t>
         </is>
       </c>
     </row>
@@ -71598,7 +71598,7 @@
           <t>A | 763呎 (3房)
 $1894万
 $24,827/呎
-(24年-02月-15日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -71606,7 +71606,7 @@
           <t>B | 766呎 (3房)
 $1914万
 $24,984/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -71614,7 +71614,7 @@
           <t>C | 439呎 (2房)
 $896万
 $20,419/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -71622,7 +71622,7 @@
           <t>D | 427呎 (2房)
 $886万
 $20,740/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -71630,7 +71630,7 @@
           <t>E | 332呎 (1房)
 $915万
 $27,566/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -71638,7 +71638,7 @@
           <t>F | 445呎 (2房)
 $1144万
 $25,719/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -71646,7 +71646,7 @@
           <t>G | 482呎 (2房)
 $1291万
 $26,776/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -71654,7 +71654,7 @@
           <t>H | 774呎 (3房)
 $1999万
 $25,831/呎
-(24年-08月-25日)</t>
+(24年-08月)</t>
         </is>
       </c>
     </row>
@@ -71669,7 +71669,7 @@
           <t>A | 763呎 (3房)
 $1889万
 $24,758/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -71677,7 +71677,7 @@
           <t>B | 766呎 (3房)
 $2284万
 $29,815/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -71685,7 +71685,7 @@
           <t>C | 439呎 (2房)
 $891万
 $20,296/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -71693,7 +71693,7 @@
           <t>D | 427呎 (2房)
 $880万
 $20,618/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -71701,7 +71701,7 @@
           <t>E | 332呎 (1房)
 $868万
 $26,142/呎
-(23年-02月-08日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -71709,7 +71709,7 @@
           <t>F | 445呎 (2房)
 $1138万
 $25,566/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -71717,7 +71717,7 @@
           <t>G | 482呎 (2房)
 $1283万
 $26,614/呎
-(21年-07月-04日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -71725,7 +71725,7 @@
           <t>H | 774呎 (3房)
 $1994万
 $25,760/呎
-(24年-12月-15日)</t>
+(24年-12月)</t>
         </is>
       </c>
     </row>
@@ -71740,7 +71740,7 @@
           <t>A | 763呎 (3房)
 $1889万
 $24,758/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -71748,7 +71748,7 @@
           <t>B | 766呎 (3房)
 $2389万
 $31,193/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -71756,7 +71756,7 @@
           <t>C | 439呎 (2房)
 $891万
 $20,296/呎
-(24年-03月-07日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -71764,7 +71764,7 @@
           <t>D | 427呎 (2房)
 $880万
 $20,618/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -71772,7 +71772,7 @@
           <t>E | 333呎 (1房)
 $952万
 $28,589/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -71780,7 +71780,7 @@
           <t>F | 445呎 (2房)
 $1138万
 $25,566/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -71788,7 +71788,7 @@
           <t>G | 482呎 (2房)
 $1283万
 $26,614/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -71796,7 +71796,7 @@
           <t>H | 774呎 (3房)
 $1994万
 $25,760/呎
-(25年-07月-29日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -71811,7 +71811,7 @@
           <t>A | 763呎 (3房)
 $2152万
 $28,201/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -71819,7 +71819,7 @@
           <t>B | 766呎 (3房)
 $1869万
 $24,397/呎
-(24年-01月-04日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -71827,7 +71827,7 @@
           <t>C | 439呎 (2房)
 $880万
 $20,052/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -71835,7 +71835,7 @@
           <t>D | 427呎 (2房)
 $873万
 $20,454/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -71843,7 +71843,7 @@
           <t>E | 332呎 (1房)
 $941万
 $28,346/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -71851,7 +71851,7 @@
           <t>F | 445呎 (2房)
 $902万
 $20,261/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -71859,7 +71859,7 @@
           <t>G | 482呎 (2房)
 $1267万
 $26,295/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -71867,7 +71867,7 @@
           <t>H | 774呎 (3房)
 $1983万
 $25,623/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -71882,7 +71882,7 @@
           <t>A | 763呎 (3房)
 $1874万
 $24,556/呎
-(24年-02月-26日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -71890,7 +71890,7 @@
           <t>B | 766呎 (3房)
 $1891万
 $24,687/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -71898,7 +71898,7 @@
           <t>C | 439呎 (2房)
 $875万
 $19,936/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -71906,7 +71906,7 @@
           <t>D | 427呎 (2房)
 $871万
 $20,393/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -71914,7 +71914,7 @@
           <t>E | 332呎 (1房)
 $904万
 $27,244/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -71922,7 +71922,7 @@
           <t>F | 445呎 (2房)
 $1169万
 $26,267/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -71930,7 +71930,7 @@
           <t>G | 482呎 (2房)
 $1204万
 $24,979/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -71938,7 +71938,7 @@
           <t>H | 774呎 (3房)
 $1980万
 $25,580/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -71953,7 +71953,7 @@
           <t>A | 763呎 (3房)
 $1868万
 $24,488/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -71961,7 +71961,7 @@
           <t>B | 766呎 (3房)
 $2364万
 $30,864/呎
-(21年-11月-14日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -71969,7 +71969,7 @@
           <t>C | 439呎 (2房)
 $891万
 $20,296/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -71977,7 +71977,7 @@
           <t>D | 427呎 (2房)
 $868万
 $20,333/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -71985,7 +71985,7 @@
           <t>E | 332呎 (1房)
 $930万
 $28,015/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -71993,7 +71993,7 @@
           <t>F | 445呎 (2房)
 $1110万
 $24,955/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -72001,7 +72001,7 @@
           <t>G | 482呎 (2房)
 $913万
 $18,944/呎
-(25年-01月-21日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -72009,7 +72009,7 @@
           <t>H | 774呎 (3房)
 $1972万
 $25,483/呎
-(24年-10月-07日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -72024,7 +72024,7 @@
           <t>A | 763呎 (3房)
 $1864万
 $24,434/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -72032,7 +72032,7 @@
           <t>B | 766呎 (3房)
 $2351万
 $30,696/呎
-(21年-11月-14日)</t>
+(21年-11月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -72040,7 +72040,7 @@
           <t>C | 439呎 (2房)
 $865万
 $19,699/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -72048,7 +72048,7 @@
           <t>D | 427呎 (2房)
 $866万
 $20,272/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -72056,7 +72056,7 @@
           <t>E | 332呎 (1房)
 $925万
 $27,852/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -72064,7 +72064,7 @@
           <t>F | 445呎 (2房)
 $1104万
 $24,802/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -72072,7 +72072,7 @@
           <t>G | 482呎 (2房)
 $1244万
 $25,815/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -72080,7 +72080,7 @@
           <t>H | 774呎 (3房)
 $1967万
 $25,415/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
     </row>
@@ -72095,7 +72095,7 @@
           <t>A | 763呎 (3房)
 $1858万
 $24,351/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -72103,7 +72103,7 @@
           <t>B | 766呎 (3房)
 $2211万
 $28,859/呎
-(21年-09月-12日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -72111,7 +72111,7 @@
           <t>C | 439呎 (2房)
 $860万
 $19,588/呎
-(23年-12月-27日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -72119,7 +72119,7 @@
           <t>D | 427呎 (2房)
 $876万
 $20,504/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -72127,7 +72127,7 @@
           <t>E | 333呎 (1房)
 $889万
 $26,688/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -72135,7 +72135,7 @@
           <t>F | 445呎 (2房)
 $1097万
 $24,649/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -72143,7 +72143,7 @@
           <t>G | 482呎 (2房)
 $904万
 $18,751/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -72151,7 +72151,7 @@
           <t>H | 774呎 (3房)
 $1953万
 $25,231/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72166,7 +72166,7 @@
           <t>A | 763呎 (3房)
 $1853万
 $24,284/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -72174,7 +72174,7 @@
           <t>B | 766呎 (3房)
 $2326万
 $30,359/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -72182,7 +72182,7 @@
           <t>C | 439呎 (2房)
 $857万
 $19,528/呎
-(23年-12月-14日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -72190,7 +72190,7 @@
           <t>D | 427呎 (2房)
 $1021万
 $23,920/呎
-(23年-05月-01日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -72198,7 +72198,7 @@
           <t>E | 332呎 (1房)
 $914万
 $27,518/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -72206,7 +72206,7 @@
           <t>F | 445呎 (2房)
 $1090万
 $24,497/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -72214,7 +72214,7 @@
           <t>G | 482呎 (2房)
 $1151万
 $23,882/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -72222,7 +72222,7 @@
           <t>H | 774呎 (3房)
 $1948万
 $25,161/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72237,7 +72237,7 @@
           <t>A | 763呎 (3房)
 $1848万
 $24,215/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -72245,7 +72245,7 @@
           <t>B | 766呎 (3房)
 $2287万
 $29,859/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -72253,7 +72253,7 @@
           <t>C | 439呎 (2房)
 $855万
 $19,469/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -72261,7 +72261,7 @@
           <t>D | 427呎 (2房)
 $1055万
 $24,717/呎
-(22年-05月-12日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -72269,7 +72269,7 @@
           <t>E | 333呎 (1房)
 $908万
 $27,273/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -72277,7 +72277,7 @@
           <t>F | 445呎 (2房)
 $864万
 $19,416/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -72285,7 +72285,7 @@
           <t>G | 482呎 (2房)
 $1197万
 $24,828/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -72293,7 +72293,7 @@
           <t>H | 774呎 (3房)
 $1942万
 $25,094/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72308,7 +72308,7 @@
           <t>A | 763呎 (3房)
 $1842万
 $24,148/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -72316,7 +72316,7 @@
           <t>B | 766呎 (3房)
 $2073万
 $27,068/呎
-(23年-04月-27日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -72324,7 +72324,7 @@
           <t>C | 439呎 (2房)
 $852万
 $19,410/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -72332,7 +72332,7 @@
           <t>D | 427呎 (2房)
 $1015万
 $23,778/呎
-(22年-08月-21日)</t>
+(22年-08月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -72340,7 +72340,7 @@
           <t>E | 332呎 (1房)
 $903万
 $27,190/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -72348,7 +72348,7 @@
           <t>F | 445呎 (2房)
 $1055万
 $23,706/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -72356,7 +72356,7 @@
           <t>G | 482呎 (2房)
 $1189万
 $24,670/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -72364,7 +72364,7 @@
           <t>H | 774呎 (3房)
 $1937万
 $25,025/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -72379,7 +72379,7 @@
           <t>A | 763呎 (3房)
 $1842万
 $24,148/呎
-(25年-02月-09日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -72387,7 +72387,7 @@
           <t>B | 766呎 (3房)
 $2073万
 $27,068/呎
-(23年-04月-19日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -72395,7 +72395,7 @@
           <t>C | 439呎 (2房)
 $852万
 $19,410/呎
-(23年-12月-06日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -72403,7 +72403,7 @@
           <t>D | 428呎 (2房)
 $1040万
 $24,297/呎
-(22年-05月-31日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -72411,7 +72411,7 @@
           <t>E | 332呎 (1房)
 $903万
 $27,190/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -72419,7 +72419,7 @@
           <t>F | 445呎 (2房)
 $842万
 $18,910/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -72427,7 +72427,7 @@
           <t>G | 482呎 (2房)
 $887万
 $18,400/呎
-(24年-06月-27日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -72435,7 +72435,7 @@
           <t>H | 774呎 (3房)
 $1937万
 $25,025/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -72450,7 +72450,7 @@
           <t>A | 763呎 (3房)
 $1925万
 $25,231/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -72458,7 +72458,7 @@
           <t>B | 766呎 (3房)
 $2050万
 $26,765/呎
-(23年-05月-03日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -72466,7 +72466,7 @@
           <t>C | 439呎 (2房)
 $846万
 $19,267/呎
-(24年-03月-03日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -72474,7 +72474,7 @@
           <t>D | 428呎 (2房)
 $1009万
 $23,582/呎
-(23年-03月-20日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -72482,7 +72482,7 @@
           <t>E | 333呎 (1房)
 $637万
 $19,138/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -72490,7 +72490,7 @@
           <t>F | 445呎 (2房)
 $1054万
 $23,676/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -72498,7 +72498,7 @@
           <t>G | 482呎 (2房)
 $1174万
 $24,359/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -72506,7 +72506,7 @@
           <t>H | 774呎 (3房)
 $1926万
 $24,886/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72521,7 +72521,7 @@
           <t>A | 763呎 (3房)
 $1827万
 $23,945/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -72529,7 +72529,7 @@
           <t>B | 766呎 (3房)
 $2137万
 $27,903/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -72537,7 +72537,7 @@
           <t>C | 439呎 (2房)
 $847万
 $19,294/呎
-(24年-02月-08日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -72545,7 +72545,7 @@
           <t>D | 428呎 (2房)
 $1006万
 $23,509/呎
-(22年-06月-09日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -72553,7 +72553,7 @@
           <t>E | 332呎 (1房)
 $869万
 $26,163/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -72561,7 +72561,7 @@
           <t>F | 445呎 (2房)
 $1047万
 $23,526/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -72569,7 +72569,7 @@
           <t>G | 482呎 (2房)
 $1115万
 $23,131/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -72577,7 +72577,7 @@
           <t>H | 774呎 (3房)
 $1921万
 $24,817/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -72592,7 +72592,7 @@
           <t>A | 763呎 (3房)
 $1880万
 $24,640/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -72600,7 +72600,7 @@
           <t>B | 766呎 (3房)
 $2027万
 $26,461/呎
-(23年-07月-19日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -72608,7 +72608,7 @@
           <t>C | 439呎 (2房)
 $842万
 $19,180/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -72616,7 +72616,7 @@
           <t>D | 428呎 (2房)
 $1003万
 $23,439/呎
-(22年-07月-12日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -72624,7 +72624,7 @@
           <t>E | 333呎 (1房)
 $863万
 $25,922/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -72632,7 +72632,7 @@
           <t>F | 445呎 (2房)
 $1076万
 $24,173/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -72640,7 +72640,7 @@
           <t>G | 482呎 (2房)
 $1108万
 $22,981/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -72648,7 +72648,7 @@
           <t>H | 774呎 (3房)
 $1916万
 $24,748/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72663,7 +72663,7 @@
           <t>A | 763呎 (3房)
 $1810万
 $23,721/呎
-(24年-03月-11日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -72671,7 +72671,7 @@
           <t>B | 766呎 (3房)
 $2015万
 $26,309/呎
-(23年-05月-18日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -72679,7 +72679,7 @@
           <t>C | 439呎 (2房)
 $837万
 $19,064/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -72687,7 +72687,7 @@
           <t>D | 427呎 (2房)
 $1019万
 $23,871/呎
-(22年-05月-04日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -72695,7 +72695,7 @@
           <t>E | 333呎 (1房)
 $820万
 $24,622/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -72703,7 +72703,7 @@
           <t>F | 445呎 (2房)
 $1022万
 $22,957/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -72711,7 +72711,7 @@
           <t>G | 482呎 (2房)
 $1151万
 $23,888/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -72719,7 +72719,7 @@
           <t>H | 774呎 (3房)
 $1910万
 $24,680/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72734,7 +72734,7 @@
           <t>A | 763呎 (3房)
 $1811万
 $23,740/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -72742,7 +72742,7 @@
           <t>B | 766呎 (3房)
 $1801万
 $23,514/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -72750,7 +72750,7 @@
           <t>C | 439呎 (2房)
 $828万
 $18,863/呎
-(24年-03月-06日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -72758,7 +72758,7 @@
           <t>D | 428呎 (2房)
 $1006万
 $23,500/呎
-(22年-05月-05日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -72766,7 +72766,7 @@
           <t>E | 332呎 (1房)
 $852万
 $25,678/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -72774,7 +72774,7 @@
           <t>F | 445呎 (2房)
 $1062万
 $23,861/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -72782,7 +72782,7 @@
           <t>G | 482呎 (2房)
 $1144万
 $23,732/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -72790,7 +72790,7 @@
           <t>H | 774呎 (3房)
 $1905万
 $24,610/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72805,7 +72805,7 @@
           <t>A | 763呎 (3房)
 $1807万
 $23,684/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -72813,7 +72813,7 @@
           <t>B | 766呎 (3房)
 $2089万
 $27,266/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -72821,7 +72821,7 @@
           <t>C | 439呎 (2房)
 $829万
 $18,891/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -72829,7 +72829,7 @@
           <t>D | 428呎 (2房)
 $1051万
 $24,556/呎
-(22年-01月-23日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -72837,7 +72837,7 @@
           <t>E | 333呎 (1房)
 $810万
 $24,315/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -72845,7 +72845,7 @@
           <t>F | 445呎 (2房)
 $1055万
 $23,703/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -72853,7 +72853,7 @@
           <t>G | 482呎 (2房)
 $847万
 $17,581/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -72861,7 +72861,7 @@
           <t>H | 774呎 (3房)
 $1899万
 $24,540/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72876,7 +72876,7 @@
           <t>A | 763呎 (3房)
 $1801万
 $23,604/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -72884,7 +72884,7 @@
           <t>B | 766呎 (3房)
 $2028万
 $26,480/呎
-(22年-05月-04日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -72892,7 +72892,7 @@
           <t>C | 439呎 (2房)
 $827万
 $18,836/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -72900,7 +72900,7 @@
           <t>D | 427呎 (2房)
 $1008万
 $23,595/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -72908,7 +72908,7 @@
           <t>E | 333呎 (1房)
 $804万
 $24,159/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -72916,7 +72916,7 @@
           <t>F | 445呎 (2房)
 $1002万
 $22,508/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -72924,7 +72924,7 @@
           <t>G | 482呎 (2房)
 $1079万
 $22,382/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -72932,7 +72932,7 @@
           <t>H | 774呎 (3房)
 $1894万
 $24,470/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -72947,7 +72947,7 @@
           <t>A | 763呎 (3房)
 $1801万
 $23,604/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -72955,7 +72955,7 @@
           <t>B | 766呎 (3房)
 $1980万
 $25,854/呎
-(23年-05月-04日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -72963,7 +72963,7 @@
           <t>C | 439呎 (2房)
 $827万
 $18,836/呎
-(23年-12月-26日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -72971,7 +72971,7 @@
           <t>D | 427呎 (2房)
 $1002万
 $23,468/呎
-(22年-02月-17日)</t>
+(22年-02月)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -72979,7 +72979,7 @@
           <t>E | 333呎 (1房)
 $804万
 $24,159/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -72987,7 +72987,7 @@
           <t>F | 445呎 (2房)
 $1002万
 $22,508/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -72995,7 +72995,7 @@
           <t>G | 482呎 (2房)
 $842万
 $17,465/呎
-(24年-07月-15日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -73003,7 +73003,7 @@
           <t>H | 774呎 (3房)
 $1894万
 $24,470/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73018,7 +73018,7 @@
           <t>A | 763呎 (3房)
 $1791万
 $23,471/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -73026,7 +73026,7 @@
           <t>B | 766呎 (3房)
 $2052万
 $26,789/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -73034,7 +73034,7 @@
           <t>C | 439呎 (2房)
 $834万
 $19,005/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -73042,7 +73042,7 @@
           <t>D | 427呎 (2房)
 $991万
 $23,204/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -73050,7 +73050,7 @@
           <t>E | 332呎 (1房)
 $831万
 $25,030/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -73058,7 +73058,7 @@
           <t>F | 445呎 (2房)
 $988万
 $22,207/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -73066,7 +73066,7 @@
           <t>G | 482呎 (2房)
 $1077万
 $22,338/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -73074,7 +73074,7 @@
           <t>H | 774呎 (3房)
 $1883万
 $24,332/呎
-(24年-04月-22日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73089,7 +73089,7 @@
           <t>A | 763呎 (3房)
 $1785万
 $23,400/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -73097,7 +73097,7 @@
           <t>B | 766呎 (3房)
 $1829万
 $23,875/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -73105,7 +73105,7 @@
           <t>C | 439呎 (2房)
 $820万
 $18,667/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -73113,7 +73113,7 @@
           <t>D | 428呎 (2房)
 $982万
 $22,956/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -73121,7 +73121,7 @@
           <t>E | 332呎 (1房)
 $826万
 $24,867/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -73129,7 +73129,7 @@
           <t>F | 445呎 (2房)
 $1027万
 $23,076/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -73137,7 +73137,7 @@
           <t>G | 482呎 (2房)
 $1106万
 $22,946/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -73145,7 +73145,7 @@
           <t>H | 774呎 (3房)
 $1878万
 $24,264/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73160,7 +73160,7 @@
           <t>A | 763呎 (3房)
 $1780万
 $23,333/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -73168,7 +73168,7 @@
           <t>B | 766呎 (3房)
 $1770万
 $23,108/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -73176,7 +73176,7 @@
           <t>C | 439呎 (2房)
 $817万
 $18,610/呎
-(24年-01月-23日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -73184,7 +73184,7 @@
           <t>D | 428呎 (2房)
 $1019万
 $23,815/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -73192,7 +73192,7 @@
           <t>E | 333呎 (1房)
 $820万
 $24,631/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -73200,7 +73200,7 @@
           <t>F | 445呎 (2房)
 $1020万
 $22,921/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -73208,7 +73208,7 @@
           <t>G | 482呎 (2房)
 $1062万
 $22,033/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -73216,7 +73216,7 @@
           <t>H | 774呎 (3房)
 $1873万
 $24,194/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73231,7 +73231,7 @@
           <t>A | 763呎 (3房)
 $1775万
 $23,266/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -73239,7 +73239,7 @@
           <t>B | 766呎 (3房)
 $1765万
 $23,039/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -73247,7 +73247,7 @@
           <t>C | 439呎 (2房)
 $815万
 $18,556/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -73255,7 +73255,7 @@
           <t>D | 427呎 (2房)
 $1000万
 $23,410/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -73263,7 +73263,7 @@
           <t>E | 332呎 (1房)
 $788万
 $23,732/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -73271,7 +73271,7 @@
           <t>F | 445呎 (2房)
 $1013万
 $22,764/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -73279,7 +73279,7 @@
           <t>G | 482呎 (2房)
 $1043万
 $21,633/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -73287,7 +73287,7 @@
           <t>H | 774呎 (3房)
 $1867万
 $24,124/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73302,7 +73302,7 @@
           <t>A | 763呎 (3房)
 $1770万
 $23,199/呎
-(24年-04月-10日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -73310,7 +73310,7 @@
           <t>B | 766呎 (3房)
 $1760万
 $22,970/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -73318,7 +73318,7 @@
           <t>C | 439呎 (2房)
 $812万
 $18,501/呎
-(24年-01月-11日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -73326,7 +73326,7 @@
           <t>D | 428呎 (2房)
 $997万
 $23,285/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -73334,7 +73334,7 @@
           <t>E | 332呎 (1房)
 $774万
 $23,307/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -73342,7 +73342,7 @@
           <t>F | 445呎 (2房)
 $1006万
 $22,604/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -73350,7 +73350,7 @@
           <t>G | 482呎 (2房)
 $1083万
 $22,477/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -73358,7 +73358,7 @@
           <t>H | 774呎 (3房)
 $1862万
 $24,054/呎
-(24年-05月-06日)</t>
+(24年-05月)</t>
         </is>
       </c>
     </row>
@@ -73373,7 +73373,7 @@
           <t>A | 763呎 (3房)
 $1748万
 $22,904/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -73381,7 +73381,7 @@
           <t>B | 766呎 (3房)
 $1737万
 $22,676/呎
-(25年-11月-25日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -73389,7 +73389,7 @@
           <t>C | 439呎 (2房)
 $810万
 $18,446/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -73397,7 +73397,7 @@
           <t>D | 428呎 (2房)
 $976万
 $22,815/呎
-(22年-01月-02日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -73405,7 +73405,7 @@
           <t>E | 332呎 (1房)
 $786万
 $23,681/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -73413,7 +73413,7 @@
           <t>F | 445呎 (2房)
 $933万
 $20,957/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -73421,7 +73421,7 @@
           <t>G | 482呎 (2房)
 $824万
 $17,102/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -73429,7 +73429,7 @@
           <t>H | 774呎 (3房)
 $1856万
 $23,982/呎
-(25年-11月-16日)</t>
+(25年-11月)</t>
         </is>
       </c>
     </row>
@@ -73603,7 +73603,7 @@
           <t>A | 969呎 (3房)
 $3000万
 $30,956/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -73612,7 +73612,7 @@
           <t>C | 459呎 (2房)
 $1002万
 $21,834/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -73620,7 +73620,7 @@
           <t>D | 456呎 (2房)
 $970万
 $21,279/呎
-(24年-03月-13日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -73628,7 +73628,7 @@
           <t>E | 452呎 (2房)
 $932万
 $20,626/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -73636,7 +73636,7 @@
           <t>F | 1325呎 (4+房)
 $3600万
 $27,170/呎
-(23年-12月-27日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>
@@ -73646,7 +73646,7 @@
           <t>J | 357呎 (1房)
 $752万
 $21,050/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -73654,7 +73654,7 @@
           <t>K | 457呎 (2房)
 $987万
 $21,602/呎
-(24年-03月-18日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -73669,7 +73669,7 @@
           <t>A | 657呎 (3房)
 $1499万
 $22,811/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -73677,7 +73677,7 @@
           <t>B | 329呎 (1房)
 $730万
 $22,182/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -73685,7 +73685,7 @@
           <t>C | 459呎 (2房)
 $999万
 $21,771/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -73693,7 +73693,7 @@
           <t>D | 456呎 (2房)
 $881万
 $19,320/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -73701,7 +73701,7 @@
           <t>E | 452呎 (2房)
 $927万
 $20,504/呎
-(25年-03月-05日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -73709,7 +73709,7 @@
           <t>F | 332呎 (1房)
 $693万
 $20,877/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -73717,7 +73717,7 @@
           <t>G | 536呎 (2房)
 $1323万
 $24,688/呎
-(22年-05月-23日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -73725,7 +73725,7 @@
           <t>H | 349呎 (1房)
 $756万
 $21,676/呎
-(26年-04月-12日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -73733,7 +73733,7 @@
           <t>J | 451呎 (2房)
 $941万
 $20,869/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -73741,7 +73741,7 @@
           <t>K | 457呎 (2房)
 $982万
 $21,484/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73756,7 +73756,7 @@
           <t>A | 656呎 (3房)
 $1736万
 $26,466/呎
-(23年-02月-12日)</t>
+(23年-02月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -73764,7 +73764,7 @@
           <t>B | 329呎 (1房)
 $738万
 $22,447/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -73772,7 +73772,7 @@
           <t>C | 459呎 (2房)
 $1011万
 $22,033/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -73780,7 +73780,7 @@
           <t>D | 456呎 (2房)
 $876万
 $19,208/呎
-(26年-03月-29日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -73788,7 +73788,7 @@
           <t>E | 452呎 (2房)
 $921万
 $20,381/呎
-(24年-11月-24日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -73796,7 +73796,7 @@
           <t>F | 332呎 (1房)
 $691万
 $20,813/呎
-(24年-06月-10日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -73804,7 +73804,7 @@
           <t>G | 536呎 (2房)
 $1383万
 $25,808/呎
-(22年-01月-09日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -73812,7 +73812,7 @@
           <t>H | 349呎 (1房)
 $752万
 $21,539/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -73820,7 +73820,7 @@
           <t>J | 451呎 (2房)
 $951万
 $21,091/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -73828,7 +73828,7 @@
           <t>K | 457呎 (2房)
 $976万
 $21,365/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73843,7 +73843,7 @@
           <t>A | 657呎 (3房)
 $1490万
 $22,674/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -73851,7 +73851,7 @@
           <t>B | 329呎 (1房)
 $725万
 $22,049/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -73859,7 +73859,7 @@
           <t>C | 459呎 (2房)
 $993万
 $21,641/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -73867,7 +73867,7 @@
           <t>D | 456呎 (2房)
 $871万
 $19,099/呎
-(26年-03月-18日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -73875,7 +73875,7 @@
           <t>E | 452呎 (2房)
 $916万
 $20,259/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -73883,7 +73883,7 @@
           <t>F | 332呎 (1房)
 $689万
 $20,750/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -73891,7 +73891,7 @@
           <t>G | 536呎 (2房)
 $1347万
 $25,136/呎
-(22年-07月-26日)</t>
+(22年-07月)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -73899,7 +73899,7 @@
           <t>H | 349呎 (1房)
 $887万
 $25,415/呎
-(23年-05月-30日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -73907,7 +73907,7 @@
           <t>J | 451呎 (2房)
 $931万
 $20,643/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -73915,7 +73915,7 @@
           <t>K | 457呎 (2房)
 $971万
 $21,247/呎
-(24年-04月-14日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -73930,7 +73930,7 @@
           <t>A | 657呎 (3房)
 $1485万
 $22,607/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -73938,7 +73938,7 @@
           <t>B | 329呎 (1房)
 $723万
 $21,985/呎
-(23年-12月-07日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -73946,7 +73946,7 @@
           <t>C | 459呎 (2房)
 $990万
 $21,573/呎
-(24年-01月-11日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -73954,7 +73954,7 @@
           <t>D | 456呎 (2房)
 $934万
 $20,480/呎
-(26年-02月-25日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -73962,7 +73962,7 @@
           <t>E | 452呎 (2房)
 $910万
 $20,139/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -73970,7 +73970,7 @@
           <t>F | 332呎 (1房)
 $687万
 $20,684/呎
-(26年-04月-21日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -73978,7 +73978,7 @@
           <t>G | 536呎 (2房)
 $1423万
 $26,545/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -73986,7 +73986,7 @@
           <t>H | 348呎 (1房)
 $882万
 $25,333/呎
-(23年-04月-18日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -73994,7 +73994,7 @@
           <t>J | 451呎 (2房)
 $926万
 $20,530/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -74002,7 +74002,7 @@
           <t>K | 457呎 (2房)
 $980万
 $21,453/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74017,7 +74017,7 @@
           <t>A | 657呎 (3房)
 $1481万
 $22,540/呎
-(24年-05月-12日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -74025,7 +74025,7 @@
           <t>B | 329呎 (1房)
 $721万
 $21,918/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -74033,7 +74033,7 @@
           <t>C | 459呎 (2房)
 $987万
 $21,508/呎
-(23年-12月-27日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -74041,7 +74041,7 @@
           <t>D | 456呎 (2房)
 $928万
 $20,362/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -74049,7 +74049,7 @@
           <t>E | 452呎 (2房)
 $919万
 $20,323/呎
-(24年-04月-25日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -74057,7 +74057,7 @@
           <t>F | 332呎 (1房)
 $696万
 $20,949/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -74065,7 +74065,7 @@
           <t>G | 536呎 (2房)
 $1110万
 $20,700/呎
-(23年-12月-03日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -74073,7 +74073,7 @@
           <t>H | 348呎 (1房)
 $887万
 $25,486/呎
-(23年-06月-15日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -74081,7 +74081,7 @@
           <t>J | 451呎 (2房)
 $921万
 $20,417/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -74089,7 +74089,7 @@
           <t>K | 457呎 (2房)
 $960万
 $21,011/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74104,7 +74104,7 @@
           <t>A | 657呎 (3房)
 $1476万
 $22,473/呎
-(24年-01月-03日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -74112,7 +74112,7 @@
           <t>B | 329呎 (1房)
 $719万
 $21,851/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -74120,7 +74120,7 @@
           <t>C | 459呎 (2房)
 $984万
 $21,442/呎
-(24年-01月-30日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -74128,7 +74128,7 @@
           <t>D | 456呎 (2房)
 $923万
 $20,243/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -74136,7 +74136,7 @@
           <t>E | 452呎 (2房)
 $899万
 $19,898/呎
-(24年-08月-13日)</t>
+(24年-08月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -74144,7 +74144,7 @@
           <t>F | 332呎 (1房)
 $683万
 $20,566/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -74152,7 +74152,7 @@
           <t>G | 536呎 (2房)
 $1106万
 $20,638/呎
-(23年-12月-26日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -74160,7 +74160,7 @@
           <t>H | 349呎 (1房)
 $871万
 $24,963/呎
-(23年-04月-17日)</t>
+(23年-04月)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -74168,7 +74168,7 @@
           <t>J | 451呎 (2房)
 $930万
 $20,632/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -74176,7 +74176,7 @@
           <t>K | 457呎 (2房)
 $955万
 $20,893/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74191,7 +74191,7 @@
           <t>A | 656呎 (3房)
 $1716万
 $26,152/呎
-(23年-03月-23日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -74199,7 +74199,7 @@
           <t>B | 329呎 (1房)
 $719万
 $21,851/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -74207,7 +74207,7 @@
           <t>C | 459呎 (2房)
 $984万
 $21,442/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -74215,7 +74215,7 @@
           <t>D | 457呎 (2房)
 $1243万
 $27,193/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -74223,7 +74223,7 @@
           <t>E | 452呎 (2房)
 $899万
 $19,898/呎
-(24年-04月-21日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -74231,7 +74231,7 @@
           <t>F | 332呎 (1房)
 $683万
 $20,566/呎
-(26年-05月-12日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -74239,7 +74239,7 @@
           <t>G | 536呎 (2房)
 $1335万
 $24,912/呎
-(22年-06月-26日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -74247,7 +74247,7 @@
           <t>H | 348呎 (1房)
 $892万
 $25,641/呎
-(22年-05月-29日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -74255,7 +74255,7 @@
           <t>J | 451呎 (2房)
 $916万
 $20,304/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -74263,7 +74263,7 @@
           <t>K | 457呎 (2房)
 $955万
 $20,893/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74278,7 +74278,7 @@
           <t>A | 657呎 (3房)
 $1468万
 $22,339/呎
-(23年-12月-17日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -74286,7 +74286,7 @@
           <t>B | 329呎 (1房)
 $725万
 $22,049/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -74294,7 +74294,7 @@
           <t>C | 459呎 (2房)
 $978万
 $21,314/呎
-(24年-01月-14日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -74302,7 +74302,7 @@
           <t>D | 456呎 (2房)
 $1270万
 $27,855/呎
-(21年-10月-18日)</t>
+(21年-10月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -74310,7 +74310,7 @@
           <t>E | 452呎 (2房)
 $892万
 $19,741/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -74318,7 +74318,7 @@
           <t>F | 332呎 (1房)
 $679万
 $20,443/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -74326,7 +74326,7 @@
           <t>G | 536呎 (2房)
 $1115万
 $20,806/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -74334,7 +74334,7 @@
           <t>H | 348呎 (1房)
 $864万
 $24,836/呎
-(23年-03月-21日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -74342,7 +74342,7 @@
           <t>J | 451呎 (2房)
 $906万
 $20,078/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -74350,7 +74350,7 @@
           <t>K | 457呎 (2房)
 $958万
 $20,972/呎
-(24年-04月-11日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74365,7 +74365,7 @@
           <t>A | 657呎 (3房)
 $1463万
 $22,272/呎
-(23年-12月-20日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -74373,7 +74373,7 @@
           <t>B | 329呎 (1房)
 $710万
 $21,568/呎
-(24年-03月-04日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -74381,7 +74381,7 @@
           <t>C | 459呎 (2房)
 $975万
 $21,251/呎
-(24年-01月-09日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -74389,7 +74389,7 @@
           <t>D | 457呎 (2房)
 $1207万
 $26,409/呎
-(21年-07月-28日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -74397,7 +74397,7 @@
           <t>E | 452呎 (2房)
 $890万
 $19,681/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -74405,7 +74405,7 @@
           <t>F | 332呎 (1房)
 $677万
 $20,383/呎
-(26年-04月-01日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -74413,7 +74413,7 @@
           <t>G | 536呎 (2房)
 $1096万
 $20,451/呎
-(24年-01月-07日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -74421,7 +74421,7 @@
           <t>H | 349呎 (1房)
 $882万
 $25,287/呎
-(22年-05月-23日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -74429,7 +74429,7 @@
           <t>J | 451呎 (2房)
 $900万
 $19,965/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -74437,7 +74437,7 @@
           <t>K | 457呎 (2房)
 $953万
 $20,851/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74452,7 +74452,7 @@
           <t>A | 657呎 (3房)
 $1480万
 $22,521/呎
-(24年-01月-11日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -74460,7 +74460,7 @@
           <t>B | 329呎 (1房)
 $710万
 $21,590/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -74468,7 +74468,7 @@
           <t>C | 459呎 (2房)
 $972万
 $21,187/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -74476,7 +74476,7 @@
           <t>D | 456呎 (2房)
 $902万
 $19,770/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -74484,7 +74484,7 @@
           <t>E | 452呎 (2房)
 $901万
 $19,925/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -74492,7 +74492,7 @@
           <t>F | 332呎 (1房)
 $675万
 $20,322/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -74500,7 +74500,7 @@
           <t>G | 536呎 (2房)
 $1093万
 $20,390/呎
-(24年-03月-21日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -74508,7 +74508,7 @@
           <t>H | 349呎 (1房)
 $890万
 $25,510/呎
-(22年-05月-16日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -74516,7 +74516,7 @@
           <t>J | 451呎 (2房)
 $895万
 $19,851/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -74524,7 +74524,7 @@
           <t>K | 457呎 (2房)
 $933万
 $20,416/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74539,7 +74539,7 @@
           <t>A | 657呎 (3房)
 $1455万
 $22,140/呎
-(23年-12月-27日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -74547,7 +74547,7 @@
           <t>B | 329呎 (1房)
 $708万
 $21,526/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -74555,7 +74555,7 @@
           <t>C | 459呎 (2房)
 $970万
 $21,124/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -74563,7 +74563,7 @@
           <t>D | 456呎 (2房)
 $1223万
 $26,814/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -74571,7 +74571,7 @@
           <t>E | 452呎 (2房)
 $884万
 $19,564/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -74579,7 +74579,7 @@
           <t>F | 332呎 (1房)
 $673万
 $20,262/呎
-(26年-05月-25日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -74587,7 +74587,7 @@
           <t>G | 536呎 (2房)
 $1090万
 $20,328/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -74595,7 +74595,7 @@
           <t>H | 348呎 (1房)
 $877万
 $25,207/呎
-(22年-05月-16日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -74603,7 +74603,7 @@
           <t>J | 451呎 (2房)
 $905万
 $20,058/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -74611,7 +74611,7 @@
           <t>K | 457呎 (2房)
 $928万
 $20,298/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -74626,7 +74626,7 @@
           <t>A | 657呎 (3房)
 $1450万
 $22,075/呎
-(23年-12月-11日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -74634,7 +74634,7 @@
           <t>B | 329呎 (1房)
 $706万
 $21,465/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -74642,7 +74642,7 @@
           <t>C | 459呎 (2房)
 $967万
 $21,061/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -74650,7 +74650,7 @@
           <t>D | 457呎 (2房)
 $1215万
 $26,593/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -74658,7 +74658,7 @@
           <t>E | 452呎 (2房)
 $895万
 $19,805/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -74666,7 +74666,7 @@
           <t>F | 332呎 (1房)
 $686万
 $20,675/呎
-(26年-05月-14日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -74674,7 +74674,7 @@
           <t>G | 536呎 (2房)
 $1118万
 $20,849/呎
-(24年-05月-05日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -74682,7 +74682,7 @@
           <t>H | 348呎 (1房)
 $926万
 $26,618/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -74690,7 +74690,7 @@
           <t>J | 451呎 (2房)
 $899万
 $19,942/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -74698,7 +74698,7 @@
           <t>K | 457呎 (2房)
 $922万
 $20,179/呎
-(24年-04月-16日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74713,7 +74713,7 @@
           <t>A | 657呎 (3房)
 $1446万
 $22,008/呎
-(23年-12月-21日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -74721,7 +74721,7 @@
           <t>B | 329呎 (1房)
 $704万
 $21,398/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -74729,7 +74729,7 @@
           <t>C | 459呎 (2房)
 $964万
 $20,996/呎
-(24年-01月-28日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -74737,7 +74737,7 @@
           <t>D | 456呎 (2房)
 $1154万
 $25,318/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -74745,7 +74745,7 @@
           <t>E | 452呎 (2房)
 $892万
 $19,743/呎
-(24年-04月-18日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -74753,7 +74753,7 @@
           <t>F | 332呎 (1房)
 $669万
 $20,139/呎
-(25年-09月-14日)</t>
+(25年-09月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -74761,7 +74761,7 @@
           <t>G | 536呎 (2房)
 $1083万
 $20,207/呎
-(23年-12月-12日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -74769,7 +74769,7 @@
           <t>H | 349呎 (1房)
 $851万
 $24,395/呎
-(22年-05月-05日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -74777,7 +74777,7 @@
           <t>J | 451呎 (2房)
 $880万
 $19,512/呎
-(24年-03月-25日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -74785,7 +74785,7 @@
           <t>K | 457呎 (2房)
 $917万
 $20,061/呎
-(24年-04月-08日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74800,7 +74800,7 @@
           <t>A | 656呎 (3房)
 $1675万
 $25,535/呎
-(23年-06月-15日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -74808,7 +74808,7 @@
           <t>B | 329呎 (1房)
 $702万
 $21,334/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -74816,7 +74816,7 @@
           <t>C | 459呎 (2房)
 $961万
 $20,932/呎
-(24年-02月-20日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -74824,7 +74824,7 @@
           <t>D | 456呎 (2房)
 $876万
 $19,200/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -74832,7 +74832,7 @@
           <t>E | 452呎 (2房)
 $876万
 $19,389/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -74840,7 +74840,7 @@
           <t>F | 332呎 (1房)
 $667万
 $20,078/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -74848,7 +74848,7 @@
           <t>G | 536呎 (2房)
 $1080万
 $20,147/呎
-(23年-12月-18日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -74856,7 +74856,7 @@
           <t>H | 348呎 (1房)
 $870万
 $24,986/呎
-(22年-05月-05日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -74864,7 +74864,7 @@
           <t>J | 451呎 (2房)
 $1291万
 $28,632/呎
-(21年-09月-28日)</t>
+(21年-09月)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -74872,7 +74872,7 @@
           <t>K | 457呎 (2房)
 $911万
 $19,943/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -74887,7 +74887,7 @@
           <t>A | 656呎 (3房)
 $1751万
 $26,692/呎
-(21年-12月-30日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -74895,7 +74895,7 @@
           <t>B | 329呎 (1房)
 $710万
 $21,593/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -74903,7 +74903,7 @@
           <t>C | 459呎 (2房)
 $958万
 $20,869/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -74911,7 +74911,7 @@
           <t>D | 457呎 (2房)
 $1140万
 $24,954/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -74935,7 +74935,7 @@
           <t>G | 536呎 (2房)
 $1269万
 $23,675/呎
-(23年-01月-18日)</t>
+(23年-01月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -74943,7 +74943,7 @@
           <t>H | 348呎 (1房)
 $867万
 $24,908/呎
-(22年-05月-09日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -74951,7 +74951,7 @@
           <t>J | 451呎 (2房)
 $870万
 $19,288/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -74959,7 +74959,7 @@
           <t>K | 457呎 (2房)
 $906万
 $19,825/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -74974,7 +74974,7 @@
           <t>A | 657呎 (3房)
 $1710万
 $26,035/呎
-(22年-06月-21日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -74982,7 +74982,7 @@
           <t>B | 329呎 (1房)
 $700万
 $21,274/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -74990,7 +74990,7 @@
           <t>C | 459呎 (2房)
 $958万
 $20,869/呎
-(23年-12月-04日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -74998,7 +74998,7 @@
           <t>D | 456呎 (2房)
 $1193万
 $26,164/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -75006,7 +75006,7 @@
           <t>E | 452呎 (2房)
 $1127万
 $24,938/呎
-(22年-06月-22日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -75014,7 +75014,7 @@
           <t>F | 331呎 (1房)
 $937万
 $28,305/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -75022,7 +75022,7 @@
           <t>G | 536呎 (2房)
 $1077万
 $20,088/呎
-(23年-12月-10日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -75030,7 +75030,7 @@
           <t>H | 349呎 (1房)
 $682万
 $19,544/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -75038,7 +75038,7 @@
           <t>J | 451呎 (2房)
 $1203万
 $26,676/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -75046,7 +75046,7 @@
           <t>K | 457呎 (2房)
 $1236万
 $27,053/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75061,7 +75061,7 @@
           <t>A | 656呎 (3房)
 $1660万
 $25,306/呎
-(22年-06月-27日)</t>
+(22年-06月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -75069,7 +75069,7 @@
           <t>B | 329呎 (1房)
 $696万
 $21,146/呎
-(24年-03月-27日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -75077,7 +75077,7 @@
           <t>C | 459呎 (2房)
 $952万
 $20,745/呎
-(24年-03月-24日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -75085,7 +75085,7 @@
           <t>D | 456呎 (2房)
 $1126万
 $24,700/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -75093,7 +75093,7 @@
           <t>E | 452呎 (2房)
 $868万
 $19,215/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -75101,7 +75101,7 @@
           <t>F | 332呎 (1房)
 $926万
 $27,889/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -75109,7 +75109,7 @@
           <t>G | 536呎 (2房)
 $1277万
 $23,819/呎
-(23年-07月-02日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -75117,7 +75117,7 @@
           <t>H | 348呎 (1房)
 $913万
 $26,227/呎
-(22年-01月-12日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -75125,7 +75125,7 @@
           <t>J | 451呎 (2房)
 $1175万
 $26,062/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -75133,7 +75133,7 @@
           <t>K | 457呎 (2房)
 $1168万
 $25,547/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75148,7 +75148,7 @@
           <t>A | 657呎 (3房)
 $1655万
 $25,192/呎
-(22年-09月-22日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -75156,7 +75156,7 @@
           <t>B | 329呎 (1房)
 $694万
 $21,079/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -75164,7 +75164,7 @@
           <t>C | 459呎 (2房)
 $949万
 $20,684/呎
-(24年-01月-25日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -75172,7 +75172,7 @@
           <t>D | 456呎 (2房)
 $1136万
 $24,908/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -75180,7 +75180,7 @@
           <t>E | 452呎 (2房)
 $866万
 $19,157/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -75188,7 +75188,7 @@
           <t>F | 331呎 (1房)
 $920万
 $27,801/呎
-(21年-08月-03日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -75196,7 +75196,7 @@
           <t>G | 536呎 (2房)
 $1364万
 $25,453/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -75204,7 +75204,7 @@
           <t>H | 349呎 (1房)
 $676万
 $19,372/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -75212,7 +75212,7 @@
           <t>J | 451呎 (2房)
 $1222万
 $27,104/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -75220,7 +75220,7 @@
           <t>K | 457呎 (2房)
 $1214万
 $26,567/呎
-(21年-08月-30日)</t>
+(21年-08月)</t>
         </is>
       </c>
     </row>
@@ -75235,7 +75235,7 @@
           <t>A | 656呎 (3房)
 $1646万
 $25,096/呎
-(23年-03月-02日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -75243,7 +75243,7 @@
           <t>B | 329呎 (1房)
 $692万
 $21,018/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -75251,7 +75251,7 @@
           <t>C | 459呎 (2房)
 $946万
 $20,621/呎
-(23年-12月-20日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -75259,7 +75259,7 @@
           <t>D | 457呎 (2房)
 $1079万
 $23,606/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -75267,7 +75267,7 @@
           <t>E | 452呎 (2房)
 $863万
 $19,102/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -75275,7 +75275,7 @@
           <t>F | 332呎 (1房)
 $874万
 $26,337/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -75283,7 +75283,7 @@
           <t>G | 536呎 (2房)
 $1254万
 $23,394/呎
-(23年-07月-31日)</t>
+(23年-07月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -75291,7 +75291,7 @@
           <t>H | 349呎 (1房)
 $877万
 $25,123/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -75299,7 +75299,7 @@
           <t>J | 451呎 (2房)
 $1161万
 $25,752/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -75307,7 +75307,7 @@
           <t>K | 457呎 (2房)
 $1153万
 $25,239/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75322,7 +75322,7 @@
           <t>A | 656呎 (3房)
 $1645万
 $25,079/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -75330,7 +75330,7 @@
           <t>B | 329呎 (1房)
 $689万
 $20,954/呎
-(26年-02月-04日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -75338,7 +75338,7 @@
           <t>C | 459呎 (2房)
 $944万
 $20,560/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -75346,7 +75346,7 @@
           <t>D | 457呎 (2房)
 $1121万
 $24,538/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -75354,7 +75354,7 @@
           <t>E | 452呎 (2房)
 $874万
 $19,336/呎
-(24年-04月-23日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -75362,7 +75362,7 @@
           <t>F | 331呎 (1房)
 $909万
 $27,471/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -75370,7 +75370,7 @@
           <t>G | 536呎 (2房)
 $1061万
 $19,789/呎
-(23年-12月-12日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -75378,7 +75378,7 @@
           <t>H | 348呎 (1房)
 $900万
 $25,859/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -75386,7 +75386,7 @@
           <t>J | 451呎 (2房)
 $1208万
 $26,783/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -75394,7 +75394,7 @@
           <t>K | 457呎 (2房)
 $1199万
 $26,243/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75409,7 +75409,7 @@
           <t>A | 656呎 (3房)
 $1640万
 $25,005/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -75417,7 +75417,7 @@
           <t>B | 329呎 (1房)
 $687万
 $20,891/呎
-(24年-04月-15日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -75425,7 +75425,7 @@
           <t>C | 459呎 (2房)
 $955万
 $20,810/呎
-(24年-01月-03日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -75433,7 +75433,7 @@
           <t>D | 456呎 (2房)
 $1114万
 $24,439/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -75441,7 +75441,7 @@
           <t>E | 452呎 (2房)
 $858万
 $18,987/呎
-(24年-05月-02日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -75449,7 +75449,7 @@
           <t>F | 332呎 (1房)
 $914万
 $27,524/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -75457,7 +75457,7 @@
           <t>G | 536呎 (2房)
 $1382万
 $25,791/呎
-(22年-01月-04日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -75465,7 +75465,7 @@
           <t>H | 348呎 (1房)
 $891万
 $25,595/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -75473,7 +75473,7 @@
           <t>J | 451呎 (2房)
 $1188万
 $26,350/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -75481,7 +75481,7 @@
           <t>K | 457呎 (2房)
 $1180万
 $25,812/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75496,7 +75496,7 @@
           <t>A | 656呎 (3房)
 $1635万
 $24,930/呎
-(23年-03月-09日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -75504,7 +75504,7 @@
           <t>B | 329呎 (1房)
 $685万
 $20,827/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -75512,7 +75512,7 @@
           <t>C | 459呎 (2房)
 $938万
 $20,438/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -75520,7 +75520,7 @@
           <t>D | 457呎 (2房)
 $1058万
 $23,155/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -75528,7 +75528,7 @@
           <t>E | 452呎 (2房)
 $856万
 $18,929/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -75536,7 +75536,7 @@
           <t>F | 331呎 (1房)
 $859万
 $25,940/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -75544,7 +75544,7 @@
           <t>G | 536呎 (2房)
 $1243万
 $23,185/呎
-(23年-05月-17日)</t>
+(23年-05月)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -75552,7 +75552,7 @@
           <t>H | 348呎 (1房)
 $854万
 $24,526/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -75560,7 +75560,7 @@
           <t>J | 451呎 (2房)
 $828万
 $18,370/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -75568,7 +75568,7 @@
           <t>K | 457呎 (2房)
 $1052万
 $23,031/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75583,7 +75583,7 @@
           <t>A | 656呎 (3房)
 $1631万
 $24,857/呎
-(22年-10月-11日)</t>
+(22年-10月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -75591,7 +75591,7 @@
           <t>B | 329呎 (1房)
 $680万
 $20,675/呎
-(24年-03月-07日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -75599,7 +75599,7 @@
           <t>C | 459呎 (2房)
 $935万
 $20,375/呎
-(24年-01月-21日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -75607,7 +75607,7 @@
           <t>D | 456呎 (2房)
 $1100万
 $24,123/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -75615,7 +75615,7 @@
           <t>E | 452呎 (2房)
 $853万
 $18,874/呎
-(24年-04月-29日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -75623,7 +75623,7 @@
           <t>F | 331呎 (1房)
 $893万
 $26,970/呎
-(21年-08月-01日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -75631,7 +75631,7 @@
           <t>G | 536呎 (2房)
 $1239万
 $23,116/呎
-(22年-05月-05日)</t>
+(22年-05月)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -75639,7 +75639,7 @@
           <t>H | 348呎 (1房)
 $821万
 $23,592/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -75647,7 +75647,7 @@
           <t>J | 451呎 (2房)
 $1088万
 $24,122/呎
-(21年-07月-21日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -75655,7 +75655,7 @@
           <t>K | 457呎 (2房)
 $1034万
 $22,632/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75670,7 +75670,7 @@
           <t>A | 656呎 (3房)
 $1631万
 $24,857/呎
-(23年-06月-11日)</t>
+(23年-06月)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -75678,7 +75678,7 @@
           <t>B | 329呎 (1房)
 $683万
 $20,760/呎
-(24年-04月-01日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -75686,7 +75686,7 @@
           <t>C | 459呎 (2房)
 $935万
 $20,375/呎
-(23年-12月-19日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -75694,7 +75694,7 @@
           <t>D | 456呎 (2房)
 $839万
 $18,390/呎
-(24年-09月-02日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -75702,7 +75702,7 @@
           <t>E | 452呎 (2房)
 $853万
 $18,874/呎
-(24年-05月-07日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -75710,7 +75710,7 @@
           <t>F | 331呎 (1房)
 $853万
 $25,779/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -75718,7 +75718,7 @@
           <t>G | 536呎 (2房)
 $1051万
 $19,614/呎
-(24年-02月-22日)</t>
+(24年-02月)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -75726,7 +75726,7 @@
           <t>H | 349呎 (1房)
 $821万
 $23,524/呎
-(21年-12月-09日)</t>
+(21年-12月)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -75734,7 +75734,7 @@
           <t>J | 451呎 (2房)
 $1076万
 $23,847/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -75742,7 +75742,7 @@
           <t>K | 457呎 (2房)
 $1082万
 $23,678/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75757,7 +75757,7 @@
           <t>A | 657呎 (3房)
 $1395万
 $21,231/呎
-(23年-11月-28日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -75765,7 +75765,7 @@
           <t>B | 329呎 (1房)
 $679万
 $20,638/呎
-(24年-04月-04日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -75773,7 +75773,7 @@
           <t>C | 459呎 (2房)
 $930万
 $20,255/呎
-(24年-01月-03日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -75781,7 +75781,7 @@
           <t>D | 456呎 (2房)
 $1038万
 $22,757/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -75789,7 +75789,7 @@
           <t>E | 452呎 (2房)
 $848万
 $18,761/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -75797,7 +75797,7 @@
           <t>F | 332呎 (1房)
 $882万
 $26,557/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -75805,7 +75805,7 @@
           <t>G | 536呎 (2房)
 $1041万
 $19,427/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -75813,7 +75813,7 @@
           <t>H | 348呎 (1房)
 $812万
 $23,328/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -75821,7 +75821,7 @@
           <t>J | 451呎 (2房)
 $1111万
 $24,627/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -75829,7 +75829,7 @@
           <t>K | 457呎 (2房)
 $1021万
 $22,333/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75844,7 +75844,7 @@
           <t>A | 657呎 (3房)
 $1391万
 $21,167/呎
-(23年-11月-29日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -75852,7 +75852,7 @@
           <t>B | 329呎 (1房)
 $677万
 $20,574/呎
-(24年-03月-26日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -75860,7 +75860,7 @@
           <t>C | 459呎 (2房)
 $927万
 $20,194/呎
-(23年-11月-30日)</t>
+(23年-11月)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -75868,7 +75868,7 @@
           <t>D | 456呎 (2房)
 $1031万
 $22,605/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -75876,7 +75876,7 @@
           <t>E | 452呎 (2房)
 $1065万
 $23,560/呎
-(22年-09月-29日)</t>
+(22年-09月)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -75884,7 +75884,7 @@
           <t>F | 332呎 (1房)
 $838万
 $25,226/呎
-(21年-08月-03日)</t>
+(21年-08月)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -75892,7 +75892,7 @@
           <t>G | 536呎 (2房)
 $1332万
 $24,854/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -75900,7 +75900,7 @@
           <t>H | 349呎 (1房)
 $805万
 $23,069/呎
-(22年-01月-03日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -75908,7 +75908,7 @@
           <t>J | 451呎 (2房)
 $1055万
 $23,384/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -75916,7 +75916,7 @@
           <t>K | 457呎 (2房)
 $1014万
 $22,182/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -75931,7 +75931,7 @@
           <t>A | 657呎 (3房)
 $1386万
 $21,104/呎
-(23年-12月-17日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -75939,7 +75939,7 @@
           <t>B | 329呎 (1房)
 $675万
 $20,514/呎
-(24年-01月-24日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -75947,7 +75947,7 @@
           <t>C | 459呎 (2房)
 $924万
 $20,133/呎
-(23年-12月-10日)</t>
+(23年-12月)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -75955,7 +75955,7 @@
           <t>D | 456呎 (2房)
 $1036万
 $22,717/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -75963,7 +75963,7 @@
           <t>E | 452呎 (2房)
 $843万
 $18,650/呎
-(24年-04月-24日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -75971,7 +75971,7 @@
           <t>F | 331呎 (1房)
 $871万
 $26,305/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -75979,7 +75979,7 @@
           <t>G | 536呎 (2房)
 $1035万
 $19,310/呎
-(24年-03月-18日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -75987,7 +75987,7 @@
           <t>H | 348呎 (1房)
 $798万
 $22,945/呎
-(22年-01月-05日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -75995,7 +75995,7 @@
           <t>J | 451呎 (2房)
 $1048万
 $23,228/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -76003,7 +76003,7 @@
           <t>K | 457呎 (2房)
 $1007万
 $22,033/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -76018,7 +76018,7 @@
           <t>A | 657呎 (3房)
 $1382万
 $21,040/呎
-(24年-03月-19日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -76026,7 +76026,7 @@
           <t>B | 329呎 (1房)
 $673万
 $20,453/呎
-(24年-04月-07日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -76034,7 +76034,7 @@
           <t>C | 459呎 (2房)
 $921万
 $20,072/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -76042,7 +76042,7 @@
           <t>D | 457呎 (2房)
 $1029万
 $22,514/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -76050,7 +76050,7 @@
           <t>E | 452呎 (2房)
 $840万
 $18,595/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -76058,7 +76058,7 @@
           <t>F | 332呎 (1房)
 $865万
 $26,057/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -76066,7 +76066,7 @@
           <t>G | 536呎 (2房)
 $1036万
 $19,323/呎
-(24年-03月-18日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -76074,7 +76074,7 @@
           <t>H | 349呎 (1房)
 $591万
 $16,946/呎
-(24年-09月-25日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -76082,7 +76082,7 @@
           <t>J | 451呎 (2房)
 $1089万
 $24,142/呎
-(21年-07月-22日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
@@ -76090,7 +76090,7 @@
           <t>K | 457呎 (2房)
 $1000万
 $21,882/呎
-(21年-07月-29日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -76105,7 +76105,7 @@
           <t>A | 657呎 (3房)
 $1378万
 $20,977/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -76113,7 +76113,7 @@
           <t>B | 329呎 (1房)
 $671万
 $20,392/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -76121,7 +76121,7 @@
           <t>C | 459呎 (2房)
 $919万
 $20,013/呎
-(24年-01月-21日)</t>
+(24年-01月)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -76129,7 +76129,7 @@
           <t>D | 456呎 (2房)
 $1057万
 $23,180/呎
-(21年-07月-26日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -76137,7 +76137,7 @@
           <t>E | 452呎 (2房)
 $838万
 $18,540/呎
-(24年-05月-01日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -76145,7 +76145,7 @@
           <t>F | 331呎 (1房)
 $860万
 $25,973/呎
-(21年-07月-27日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -76153,7 +76153,7 @@
           <t>G | 536呎 (2房)
 $1033万
 $19,265/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -76161,7 +76161,7 @@
           <t>H | 349呎 (1房)
 $590万
 $16,897/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -76169,7 +76169,7 @@
           <t>J | 451呎 (2房)
 $1082万
 $23,980/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="K34" s="20" t="inlineStr">
@@ -76177,7 +76177,7 @@
           <t>K | 457呎 (2房)
 $1039万
 $22,740/呎
-(21年-07月-02日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -76192,7 +76192,7 @@
           <t>A | 657呎 (3房)
 $1356万
 $20,633/呎
-(24年-03月-18日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -76200,7 +76200,7 @@
           <t>B | 329呎 (1房)
 $669万
 $20,331/呎
-(26年-04月-20日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -76208,7 +76208,7 @@
           <t>C | 459呎 (2房)
 $930万
 $20,255/呎
-(24年-03月-14日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -76216,7 +76216,7 @@
           <t>D | 456呎 (2房)
 $782万
 $17,154/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -76224,7 +76224,7 @@
           <t>E | 452呎 (2房)
 $1085万
 $24,004/呎
-(22年-01月-24日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -76232,7 +76232,7 @@
           <t>F | 331呎 (1房)
 $836万
 $25,248/呎
-(21年-07月-09日)</t>
+(21年-07月)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -76240,7 +76240,7 @@
           <t>G | 536呎 (2房)
 $1015万
 $18,944/呎
-(24年-03月-20日)</t>
+(24年-03月)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -76248,7 +76248,7 @@
           <t>H | 348呎 (1房)
 $779万
 $22,388/呎
-(22年-01月-20日)</t>
+(22年-01月)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -76264,7 +76264,7 @@
           <t>K | 457呎 (2房)
 $1020万
 $22,319/呎
-(21年-07月-25日)</t>
+(21年-07月)</t>
         </is>
       </c>
     </row>
@@ -76390,7 +76390,7 @@
           <t>A | 1793呎 (4+房)
 $6320万
 $35,250/呎
-(23年-03月-27日)</t>
+(23年-03月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -76398,7 +76398,7 @@
           <t>B | 1699呎 (4+房)
 $6380万
 $37,552/呎
-(23年-03月-14日)</t>
+(23年-03月)</t>
         </is>
       </c>
     </row>
@@ -76413,7 +76413,7 @@
           <t>A | 1687呎 (4+房)
 $4950万
 $29,342/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -76421,7 +76421,7 @@
           <t>B | 1687呎 (4+房)
 $4998万
 $29,627/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -76436,7 +76436,7 @@
           <t>A | 1687呎 (4+房)
 $4781万
 $28,342/呎
-(24年-04月-02日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -76444,7 +76444,7 @@
           <t>B | 1687呎 (4+房)
 $4930万
 $29,223/呎
-(24年-03月-17日)</t>
+(24年-03月)</t>
         </is>
       </c>
     </row>
@@ -76459,7 +76459,7 @@
           <t>A | 1687呎 (4+房)
 $4830万
 $28,631/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -76467,7 +76467,7 @@
           <t>B | 1687呎 (4+房)
 $4878万
 $28,917/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>
@@ -76482,7 +76482,7 @@
           <t>A | 1687呎 (4+房)
 $4782万
 $28,345/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -76490,7 +76490,7 @@
           <t>B | 1687呎 (4+房)
 $4830万
 $28,628/呎
-(24年-04月-09日)</t>
+(24年-04月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-启德-维港1号.xlsx
+++ b/files/九龙-启德-维港1号.xlsx
@@ -66561,7 +66561,7 @@
           <t>A | 643呎 (3房)
 $1531万
 $23,806/呎
-(24年-12月)</t>
+(24年-12月-12日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -66569,7 +66569,7 @@
           <t>B | 443呎 (2房)
 $913万
 $20,614/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -66577,7 +66577,7 @@
           <t>C | 438呎 (2房)
 $932万
 $21,281/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -66585,7 +66585,7 @@
           <t>D | 445呎 (2房)
 $959万
 $21,548/呎
-(25年-09月)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -66593,7 +66593,7 @@
           <t>E | 426呎 (2房)
 $930万
 $21,822/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -66601,7 +66601,7 @@
           <t>F | 448呎 (2房)
 $974万
 $21,743/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -66609,7 +66609,7 @@
           <t>G | 778呎 (3房)
 $2420万
 $31,105/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -66617,7 +66617,7 @@
           <t>H | 642呎 (3房)
 $1450万
 $22,586/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -66632,7 +66632,7 @@
           <t>A | 643呎 (3房)
 $2012万
 $31,289/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -66640,7 +66640,7 @@
           <t>B | 443呎 (2房)
 $1236万
 $27,894/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -66648,7 +66648,7 @@
           <t>C | 438呎 (2房)
 $927万
 $21,160/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -66656,7 +66656,7 @@
           <t>D | 445呎 (2房)
 $954万
 $21,427/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -66664,7 +66664,7 @@
           <t>E | 426呎 (2房)
 $924万
 $21,700/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -66672,7 +66672,7 @@
           <t>F | 448呎 (2房)
 $969万
 $21,623/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -66680,7 +66680,7 @@
           <t>G | 765呎 (3房)
 $1912万
 $24,999/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -66688,7 +66688,7 @@
           <t>H | 644呎 (3房)
 $1467万
 $22,784/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -66703,7 +66703,7 @@
           <t>A | 643呎 (3房)
 $1515万
 $23,557/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -66711,7 +66711,7 @@
           <t>B | 443呎 (2房)
 $903万
 $20,375/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -66719,7 +66719,7 @@
           <t>C | 438呎 (2房)
 $922万
 $21,041/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -66727,7 +66727,7 @@
           <t>D | 445呎 (2房)
 $948万
 $21,306/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -66735,7 +66735,7 @@
           <t>E | 426呎 (2房)
 $933万
 $21,899/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -66743,7 +66743,7 @@
           <t>F | 448呎 (2房)
 $963万
 $21,502/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -66751,7 +66751,7 @@
           <t>G | 765呎 (3房)
 $1907万
 $24,929/呎
-(26年-01月)</t>
+(26年-01月-04日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -66759,7 +66759,7 @@
           <t>H | 644呎 (3房)
 $1441万
 $22,380/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -66774,7 +66774,7 @@
           <t>A | 643呎 (3房)
 $1991万
 $30,958/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -66782,7 +66782,7 @@
           <t>B | 443呎 (2房)
 $897万
 $20,255/呎
-(26年-03月)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -66790,7 +66790,7 @@
           <t>C | 438呎 (2房)
 $921万
 $21,025/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -66798,7 +66798,7 @@
           <t>D | 445呎 (2房)
 $943万
 $21,184/呎
-(25年-09月)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -66806,7 +66806,7 @@
           <t>E | 426呎 (2房)
 $914万
 $21,453/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -66814,7 +66814,7 @@
           <t>F | 448呎 (2房)
 $958万
 $21,384/呎
-(24年-12月)</t>
+(24年-12月-04日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -66822,7 +66822,7 @@
           <t>G | 765呎 (3房)
 $1902万
 $24,861/呎
-(26年-01月)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -66830,7 +66830,7 @@
           <t>H | 644呎 (3房)
 $1437万
 $22,314/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -66845,7 +66845,7 @@
           <t>A | 643呎 (3房)
 $1499万
 $23,306/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -66853,7 +66853,7 @@
           <t>B | 443呎 (2房)
 $892万
 $20,140/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -66861,7 +66861,7 @@
           <t>C | 438呎 (2房)
 $920万
 $21,007/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -66869,7 +66869,7 @@
           <t>D | 445呎 (2房)
 $937万
 $21,063/呎
-(25年-11月)</t>
+(25年-11月-12日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -66877,7 +66877,7 @@
           <t>E | 426呎 (2房)
 $909万
 $21,331/呎
-(24年-04月)</t>
+(24年-04月-28日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -66885,7 +66885,7 @@
           <t>F | 448呎 (2房)
 $952万
 $21,261/呎
-(24年-12月)</t>
+(24年-12月-09日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -66893,7 +66893,7 @@
           <t>G | 765呎 (3房)
 $1897万
 $24,792/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -66901,7 +66901,7 @@
           <t>H | 644呎 (3房)
 $1433万
 $22,247/呎
-(24年-03月)</t>
+(24年-03月-04日)</t>
         </is>
       </c>
     </row>
@@ -66916,7 +66916,7 @@
           <t>A | 643呎 (3房)
 $1491万
 $23,182/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -66924,7 +66924,7 @@
           <t>B | 443呎 (2房)
 $887万
 $20,018/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -66932,7 +66932,7 @@
           <t>C | 438呎 (2房)
 $919万
 $20,989/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -66940,7 +66940,7 @@
           <t>D | 445呎 (2房)
 $932万
 $20,942/呎
-(25年-10月)</t>
+(25年-10月-19日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -66948,7 +66948,7 @@
           <t>E | 426呎 (2房)
 $904万
 $21,209/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -66956,7 +66956,7 @@
           <t>F | 448呎 (2房)
 $947万
 $21,141/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -66964,7 +66964,7 @@
           <t>G | 765呎 (3房)
 $1910万
 $24,974/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -66972,7 +66972,7 @@
           <t>H | 644呎 (3房)
 $1428万
 $22,180/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -66987,7 +66987,7 @@
           <t>A | 643呎 (3房)
 $1483万
 $23,058/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -66995,7 +66995,7 @@
           <t>B | 444呎 (2房)
 $1147万
 $25,829/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -67003,7 +67003,7 @@
           <t>C | 438呎 (2房)
 $918万
 $20,970/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -67011,7 +67011,7 @@
           <t>D | 445呎 (2房)
 $926万
 $20,820/呎
-(25年-09月)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -67019,7 +67019,7 @@
           <t>E | 426呎 (2房)
 $898万
 $21,085/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -67027,7 +67027,7 @@
           <t>F | 448呎 (2房)
 $942万
 $21,022/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -67035,7 +67035,7 @@
           <t>G | 765呎 (3房)
 $1886万
 $24,654/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -67043,7 +67043,7 @@
           <t>H | 644呎 (3房)
 $1424万
 $22,115/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -67058,7 +67058,7 @@
           <t>A | 643呎 (3房)
 $1504万
 $23,393/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -67066,7 +67066,7 @@
           <t>B | 444呎 (2房)
 $1200万
 $27,023/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -67074,7 +67074,7 @@
           <t>C | 438呎 (2房)
 $1207万
 $27,562/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -67082,7 +67082,7 @@
           <t>D | 445呎 (2房)
 $926万
 $20,820/呎
-(25年-10月)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -67090,7 +67090,7 @@
           <t>E | 426呎 (2房)
 $898万
 $21,085/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -67098,7 +67098,7 @@
           <t>F | 448呎 (2房)
 $1301万
 $29,045/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -67106,7 +67106,7 @@
           <t>G | 765呎 (3房)
 $1886万
 $24,654/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -67114,7 +67114,7 @@
           <t>H | 644呎 (3房)
 $1424万
 $22,115/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -67129,7 +67129,7 @@
           <t>A | 643呎 (3房)
 $1466万
 $22,807/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -67137,7 +67137,7 @@
           <t>B | 443呎 (2房)
 $1186万
 $26,761/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -67145,7 +67145,7 @@
           <t>C | 438呎 (2房)
 $1140万
 $26,037/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -67153,7 +67153,7 @@
           <t>D | 445呎 (2房)
 $916万
 $20,580/呎
-(24年-12月)</t>
+(24年-12月-11日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -67161,7 +67161,7 @@
           <t>E | 426呎 (2房)
 $888万
 $20,843/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -67169,7 +67169,7 @@
           <t>F | 448呎 (2房)
 $931万
 $20,781/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -67177,7 +67177,7 @@
           <t>G | 765呎 (3房)
 $1906万
 $24,919/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -67185,7 +67185,7 @@
           <t>H | 644呎 (3房)
 $1416万
 $21,983/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -67200,7 +67200,7 @@
           <t>A | 643呎 (3房)
 $1458万
 $22,683/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -67208,7 +67208,7 @@
           <t>B | 444呎 (2房)
 $1178万
 $26,541/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -67216,7 +67216,7 @@
           <t>C | 438呎 (2房)
 $925万
 $21,116/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -67224,7 +67224,7 @@
           <t>D | 445呎 (2房)
 $910万
 $20,458/呎
-(25年-01月)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -67232,7 +67232,7 @@
           <t>E | 426呎 (2房)
 $883万
 $20,718/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -67240,7 +67240,7 @@
           <t>F | 448呎 (2房)
 $926万
 $20,658/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -67248,7 +67248,7 @@
           <t>G | 765呎 (3房)
 $1870万
 $24,447/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -67256,7 +67256,7 @@
           <t>H | 644呎 (3房)
 $1412万
 $21,918/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -67271,7 +67271,7 @@
           <t>A | 643呎 (3房)
 $1450万
 $22,557/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -67279,7 +67279,7 @@
           <t>B | 444呎 (2房)
 $1159万
 $26,110/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -67287,7 +67287,7 @@
           <t>C | 438呎 (2房)
 $1179万
 $26,916/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -67295,7 +67295,7 @@
           <t>D | 445呎 (2房)
 $905万
 $20,337/呎
-(25年-06月)</t>
+(25年-06月-29日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -67303,7 +67303,7 @@
           <t>E | 426呎 (2房)
 $877万
 $20,596/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -67311,7 +67311,7 @@
           <t>F | 448呎 (2房)
 $934万
 $20,853/呎
-(24年-07月)</t>
+(24年-07月-23日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -67319,7 +67319,7 @@
           <t>G | 765呎 (3房)
 $1865万
 $24,379/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -67327,7 +67327,7 @@
           <t>H | 644呎 (3房)
 $1407万
 $21,851/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
     </row>
@@ -67342,7 +67342,7 @@
           <t>A | 643呎 (3房)
 $1785万
 $27,760/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -67350,7 +67350,7 @@
           <t>B | 444呎 (2房)
 $1101万
 $24,802/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -67358,7 +67358,7 @@
           <t>C | 438呎 (2房)
 $1172万
 $26,756/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -67366,7 +67366,7 @@
           <t>D | 445呎 (2房)
 $900万
 $20,216/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -67374,7 +67374,7 @@
           <t>E | 426呎 (2房)
 $872万
 $20,474/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -67382,7 +67382,7 @@
           <t>F | 448呎 (2房)
 $915万
 $20,420/呎
-(24年-05月)</t>
+(24年-05月-08日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -67390,7 +67390,7 @@
           <t>G | 765呎 (3房)
 $1860万
 $24,310/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -67398,7 +67398,7 @@
           <t>H | 644呎 (3房)
 $1403万
 $21,786/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -67413,7 +67413,7 @@
           <t>A | 643呎 (3房)
 $1775万
 $27,607/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -67421,7 +67421,7 @@
           <t>B | 444呎 (2房)
 $1094万
 $24,649/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -67429,7 +67429,7 @@
           <t>C | 438呎 (2房)
 $1165万
 $26,594/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -67437,7 +67437,7 @@
           <t>D | 444呎 (2房)
 $1140万
 $25,676/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -67445,7 +67445,7 @@
           <t>E | 426呎 (2房)
 $1141万
 $26,777/呎
-(21年-09月)</t>
+(21年-09月-06日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -67453,7 +67453,7 @@
           <t>F | 448呎 (2房)
 $909万
 $20,299/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -67461,7 +67461,7 @@
           <t>G | 765呎 (3房)
 $2074万
 $27,118/呎
-(23年-08月)</t>
+(23年-08月-17日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -67469,7 +67469,7 @@
           <t>H | 644呎 (3房)
 $1399万
 $21,720/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -67484,7 +67484,7 @@
           <t>A | 643呎 (3房)
 $1765万
 $27,453/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -67492,7 +67492,7 @@
           <t>B | 444呎 (2房)
 $1088万
 $24,495/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -67500,7 +67500,7 @@
           <t>C | 438呎 (2房)
 $1106万
 $25,263/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -67508,7 +67508,7 @@
           <t>D | 444呎 (2房)
 $1186万
 $26,700/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -67516,7 +67516,7 @@
           <t>E | 426呎 (2房)
 $1173万
 $27,528/呎
-(21年-08月)</t>
+(21年-08月-10日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -67524,7 +67524,7 @@
           <t>F | 448呎 (2房)
 $904万
 $20,179/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -67532,7 +67532,7 @@
           <t>G | 765呎 (3房)
 $2263万
 $29,583/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -67540,7 +67540,7 @@
           <t>H | 644呎 (3房)
 $1395万
 $21,657/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -67555,7 +67555,7 @@
           <t>A | 643呎 (3房)
 $1755万
 $27,297/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -67563,7 +67563,7 @@
           <t>B | 444呎 (2房)
 $1108万
 $24,959/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -67571,7 +67571,7 @@
           <t>C | 438呎 (2房)
 $1163万
 $26,562/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -67579,7 +67579,7 @@
           <t>D | 445呎 (2房)
 $1178万
 $26,481/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -67587,7 +67587,7 @@
           <t>E | 426呎 (2房)
 $1166万
 $27,362/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -67595,7 +67595,7 @@
           <t>F | 448呎 (2房)
 $899万
 $20,058/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -67603,7 +67603,7 @@
           <t>G | 765呎 (3房)
 $2108万
 $27,556/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -67611,7 +67611,7 @@
           <t>H | 644呎 (3房)
 $1390万
 $21,590/呎
-(24年-01月)</t>
+(24年-01月-18日)</t>
         </is>
       </c>
     </row>
@@ -67626,7 +67626,7 @@
           <t>A | 643呎 (3房)
 $1826万
 $28,398/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -67634,7 +67634,7 @@
           <t>B | 443呎 (2房)
 $1065万
 $24,034/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -67642,7 +67642,7 @@
           <t>C | 438呎 (2房)
 $1144万
 $26,107/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -67650,7 +67650,7 @@
           <t>D | 445呎 (2房)
 $1119万
 $25,155/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -67658,7 +67658,7 @@
           <t>E | 426呎 (2房)
 $1159万
 $27,197/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -67666,7 +67666,7 @@
           <t>F | 447呎 (2房)
 $1180万
 $26,389/呎
-(21年-08月)</t>
+(21年-08月-18日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -67674,7 +67674,7 @@
           <t>G | 765呎 (3房)
 $2193万
 $28,668/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -67682,7 +67682,7 @@
           <t>H | 644呎 (3房)
 $1386万
 $21,526/呎
-(24年-02月)</t>
+(24年-02月-07日)</t>
         </is>
       </c>
     </row>
@@ -67697,7 +67697,7 @@
           <t>A | 643呎 (3房)
 $1826万
 $28,398/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -67705,7 +67705,7 @@
           <t>B | 443呎 (2房)
 $1052万
 $23,758/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -67713,7 +67713,7 @@
           <t>C | 438呎 (2房)
 $1144万
 $26,107/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -67721,7 +67721,7 @@
           <t>D | 445呎 (2房)
 $1119万
 $25,155/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -67729,7 +67729,7 @@
           <t>E | 426呎 (2房)
 $1135万
 $26,653/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -67737,7 +67737,7 @@
           <t>F | 447呎 (2房)
 $1180万
 $26,389/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -67745,7 +67745,7 @@
           <t>G | 765呎 (3房)
 $2193万
 $28,668/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -67753,7 +67753,7 @@
           <t>H | 644呎 (3房)
 $1881万
 $29,207/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
     </row>
@@ -67768,7 +67768,7 @@
           <t>A | 643呎 (3房)
 $1426万
 $22,180/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -67776,7 +67776,7 @@
           <t>B | 444呎 (2房)
 $1087万
 $24,486/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -67784,7 +67784,7 @@
           <t>C | 438呎 (2房)
 $1092万
 $24,932/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -67792,7 +67792,7 @@
           <t>D | 445呎 (2房)
 $1118万
 $25,135/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -67800,7 +67800,7 @@
           <t>E | 426呎 (2房)
 $1121万
 $26,324/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -67808,7 +67808,7 @@
           <t>F | 447呎 (2房)
 $1165万
 $26,072/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -67816,7 +67816,7 @@
           <t>G | 765呎 (3房)
 $2168万
 $28,344/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -67824,7 +67824,7 @@
           <t>H | 644呎 (3房)
 $1550万
 $24,071/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -67839,7 +67839,7 @@
           <t>A | 643呎 (3房)
 $1716万
 $26,680/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -67847,7 +67847,7 @@
           <t>B | 443呎 (2房)
 $1033万
 $23,309/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -67855,7 +67855,7 @@
           <t>C | 438呎 (2房)
 $1089万
 $24,854/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -67863,7 +67863,7 @@
           <t>D | 444呎 (2房)
 $1150万
 $25,892/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -67871,7 +67871,7 @@
           <t>E | 426呎 (2房)
 $1114万
 $26,162/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -67879,7 +67879,7 @@
           <t>F | 448呎 (2房)
 $1212万
 $27,049/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -67887,7 +67887,7 @@
           <t>G | 765呎 (3房)
 $2061万
 $26,937/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -67895,7 +67895,7 @@
           <t>H | 643呎 (3房)
 $1767万
 $27,487/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -67910,7 +67910,7 @@
           <t>A | 643呎 (3房)
 $1731万
 $26,919/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -67918,7 +67918,7 @@
           <t>B | 444呎 (2房)
 $1073万
 $24,176/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -67926,7 +67926,7 @@
           <t>C | 438呎 (2房)
 $1082万
 $24,696/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -67934,7 +67934,7 @@
           <t>D | 444呎 (2房)
 $1092万
 $24,595/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -67942,7 +67942,7 @@
           <t>E | 426呎 (2房)
 $1059万
 $24,850/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -67950,7 +67950,7 @@
           <t>F | 447呎 (2房)
 $1204万
 $26,942/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -67958,7 +67958,7 @@
           <t>G | 765呎 (3房)
 $2049万
 $26,783/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -67966,7 +67966,7 @@
           <t>H | 644呎 (3房)
 $1432万
 $22,239/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -67981,7 +67981,7 @@
           <t>A | 643呎 (3房)
 $1645万
 $25,580/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -67989,7 +67989,7 @@
           <t>B | 443呎 (2房)
 $1019万
 $23,009/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -67997,7 +67997,7 @@
           <t>C | 438呎 (2房)
 $1027万
 $23,457/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -68005,7 +68005,7 @@
           <t>D | 445呎 (2房)
 $1135万
 $25,512/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -68013,7 +68013,7 @@
           <t>E | 426呎 (2房)
 $1101万
 $25,836/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -68021,7 +68021,7 @@
           <t>F | 447呎 (2房)
 $1157万
 $25,888/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -68029,7 +68029,7 @@
           <t>G | 765呎 (3房)
 $2037万
 $26,627/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -68037,7 +68037,7 @@
           <t>H | 644呎 (3房)
 $1828万
 $28,384/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -68052,7 +68052,7 @@
           <t>A | 643呎 (3房)
 $1660万
 $25,821/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -68060,7 +68060,7 @@
           <t>B | 443呎 (2房)
 $1059万
 $23,914/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -68068,7 +68068,7 @@
           <t>C | 438呎 (2房)
 $1068万
 $24,384/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -68076,7 +68076,7 @@
           <t>D | 444呎 (2房)
 $1078万
 $24,284/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -68084,7 +68084,7 @@
           <t>E | 426呎 (2房)
 $1045万
 $24,538/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -68092,7 +68092,7 @@
           <t>F | 448呎 (2房)
 $1190万
 $26,551/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -68100,7 +68100,7 @@
           <t>G | 765呎 (3房)
 $1804万
 $23,588/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -68108,7 +68108,7 @@
           <t>H | 643呎 (3房)
 $1720万
 $26,751/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -68123,7 +68123,7 @@
           <t>A | 643呎 (3房)
 $1505万
 $23,406/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -68131,7 +68131,7 @@
           <t>B | 443呎 (2房)
 $1053万
 $23,761/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -68139,7 +68139,7 @@
           <t>C | 438呎 (2房)
 $1061万
 $24,226/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -68147,7 +68147,7 @@
           <t>D | 444呎 (2房)
 $1071万
 $24,131/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -68155,7 +68155,7 @@
           <t>E | 426呎 (2房)
 $1087万
 $25,507/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -68163,7 +68163,7 @@
           <t>F | 447呎 (2房)
 $1143万
 $25,568/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -68171,7 +68171,7 @@
           <t>G | 765呎 (3房)
 $1799万
 $23,518/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -68179,7 +68179,7 @@
           <t>H | 643呎 (3房)
 $1642万
 $25,543/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -68194,7 +68194,7 @@
           <t>A | 643呎 (3房)
 $1479万
 $23,006/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -68202,7 +68202,7 @@
           <t>B | 443呎 (2房)
 $1046万
 $23,600/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -68210,7 +68210,7 @@
           <t>C | 438呎 (2房)
 $1019万
 $23,272/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -68218,7 +68218,7 @@
           <t>D | 445呎 (2房)
 $1114万
 $25,027/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -68226,7 +68226,7 @@
           <t>E | 426呎 (2房)
 $1080万
 $25,345/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -68234,7 +68234,7 @@
           <t>F | 447呎 (2房)
 $1123万
 $25,116/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -68242,7 +68242,7 @@
           <t>G | 765呎 (3房)
 $1991万
 $26,027/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -68250,7 +68250,7 @@
           <t>H | 643呎 (3房)
 $1709万
 $26,572/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -68265,7 +68265,7 @@
           <t>A | 643呎 (3房)
 $1548万
 $24,070/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -68273,7 +68273,7 @@
           <t>B | 444呎 (2房)
 $999万
 $22,507/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -68281,7 +68281,7 @@
           <t>C | 438呎 (2房)
 $1008万
 $23,007/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -68289,7 +68289,7 @@
           <t>D | 444呎 (2房)
 $1114万
 $25,083/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -68297,7 +68297,7 @@
           <t>E | 426呎 (2房)
 $1080万
 $25,345/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -68305,7 +68305,7 @@
           <t>F | 447呎 (2房)
 $1136万
 $25,407/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -68313,7 +68313,7 @@
           <t>G | 765呎 (3房)
 $1925万
 $25,165/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -68321,7 +68321,7 @@
           <t>H | 643呎 (3房)
 $1690万
 $26,281/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -68336,7 +68336,7 @@
           <t>A | 643呎 (3房)
 $1460万
 $22,706/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -68344,7 +68344,7 @@
           <t>B | 443呎 (2房)
 $1032万
 $23,287/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -68352,7 +68352,7 @@
           <t>C | 438呎 (2房)
 $1041万
 $23,758/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -68360,7 +68360,7 @@
           <t>D | 444呎 (2房)
 $1051万
 $23,667/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -68368,7 +68368,7 @@
           <t>E | 426呎 (2房)
 $1019万
 $23,913/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -68376,7 +68376,7 @@
           <t>F | 447呎 (2房)
 $1108万
 $24,796/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -68384,7 +68384,7 @@
           <t>G | 765呎 (3房)
 $1879万
 $24,567/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -68392,7 +68392,7 @@
           <t>H | 643呎 (3房)
 $1669万
 $25,955/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -68407,7 +68407,7 @@
           <t>A | 643呎 (3房)
 $1450万
 $22,557/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -68415,7 +68415,7 @@
           <t>B | 443呎 (2房)
 $979万
 $22,106/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -68423,7 +68423,7 @@
           <t>C | 438呎 (2房)
 $1034万
 $23,598/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -68431,7 +68431,7 @@
           <t>D | 444呎 (2房)
 $1044万
 $23,511/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -68439,7 +68439,7 @@
           <t>E | 426呎 (2房)
 $1059万
 $24,854/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -68447,7 +68447,7 @@
           <t>F | 447呎 (2房)
 $1101万
 $24,638/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -68455,7 +68455,7 @@
           <t>G | 765呎 (3房)
 $1868万
 $24,413/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -68463,7 +68463,7 @@
           <t>H | 643呎 (3房)
 $1658万
 $25,788/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -68478,7 +68478,7 @@
           <t>A | 643呎 (3房)
 $1507万
 $23,443/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -68486,7 +68486,7 @@
           <t>B | 444呎 (2房)
 $973万
 $21,908/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -68494,7 +68494,7 @@
           <t>C | 438呎 (2房)
 $1027万
 $23,443/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -68502,7 +68502,7 @@
           <t>D | 444呎 (2房)
 $1085万
 $24,437/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -68510,7 +68510,7 @@
           <t>E | 426呎 (2房)
 $1005万
 $23,601/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -68518,7 +68518,7 @@
           <t>F | 447呎 (2房)
 $1145万
 $25,611/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -68526,7 +68526,7 @@
           <t>G | 765呎 (3房)
 $1856万
 $24,259/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -68534,7 +68534,7 @@
           <t>H | 644呎 (3房)
 $1575万
 $24,453/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -68549,7 +68549,7 @@
           <t>A | 643呎 (3房)
 $1431万
 $22,257/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -68557,7 +68557,7 @@
           <t>B | 443呎 (2房)
 $966万
 $21,806/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -68565,7 +68565,7 @@
           <t>C | 438呎 (2房)
 $812万
 $18,527/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -68573,7 +68573,7 @@
           <t>D | 445呎 (2房)
 $1030万
 $23,151/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -68581,7 +68581,7 @@
           <t>E | 426呎 (2房)
 $999万
 $23,444/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -68589,7 +68589,7 @@
           <t>F | 447呎 (2房)
 $1087万
 $24,320/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -68597,7 +68597,7 @@
           <t>G | 765呎 (3房)
 $1844万
 $24,105/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -68605,7 +68605,7 @@
           <t>H | 644呎 (3房)
 $1221万
 $18,958/呎
-(23年-12月)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
     </row>
@@ -68620,7 +68620,7 @@
           <t>A | 643呎 (3房)
 $1487万
 $23,129/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -68628,7 +68628,7 @@
           <t>B | 443呎 (2房)
 $948万
 $21,406/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -68636,7 +68636,7 @@
           <t>C | 438呎 (2房)
 $1000万
 $22,831/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -68644,7 +68644,7 @@
           <t>D | 445呎 (2房)
 $1059万
 $23,791/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -68652,7 +68652,7 @@
           <t>E | 426呎 (2房)
 $981万
 $23,028/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -68660,7 +68660,7 @@
           <t>F | 448呎 (2房)
 $1117万
 $24,942/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -68668,7 +68668,7 @@
           <t>G | 765呎 (3房)
 $1832万
 $23,950/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -68676,7 +68676,7 @@
           <t>H | 644呎 (3房)
 $1195万
 $18,557/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
     </row>
@@ -68691,7 +68691,7 @@
           <t>A | 643呎 (3房)
 $1396万
 $21,708/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -68699,7 +68699,7 @@
           <t>B | 443呎 (2房)
 $960万
 $21,679/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -68707,7 +68707,7 @@
           <t>C | 438呎 (2房)
 $972万
 $22,187/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -68715,7 +68715,7 @@
           <t>D | 445呎 (2房)
 $1028万
 $23,092/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -68723,7 +68723,7 @@
           <t>E | 426呎 (2房)
 $996万
 $23,387/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -68731,7 +68731,7 @@
           <t>F | 447呎 (2房)
 $1049万
 $23,472/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -68739,7 +68739,7 @@
           <t>G | 765呎 (3房)
 $1884万
 $24,626/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -68747,7 +68747,7 @@
           <t>H | 644呎 (3房)
 $1174万
 $18,234/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
     </row>
@@ -68909,7 +68909,7 @@
           <t>A | 1484呎 (4+房)
 $5095万
 $34,335/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -68919,7 +68919,7 @@
           <t>D | 329呎 (1房)
 $862万
 $26,204/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -68927,7 +68927,7 @@
           <t>E | 330呎 (1房)
 $647万
 $19,597/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -68935,7 +68935,7 @@
           <t>F | 330呎 (1房)
 $684万
 $20,715/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -68943,7 +68943,7 @@
           <t>G | 338呎 (1房)
 $975万
 $28,840/呎
-(21年-09月)</t>
+(21年-09月-20日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -68951,7 +68951,7 @@
           <t>H | 598呎 (3房)
 $1565万
 $26,172/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
     </row>
@@ -68966,7 +68966,7 @@
           <t>A | 454呎 (2房)
 $1188万
 $26,163/呎
-(22年-09月)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -68974,7 +68974,7 @@
           <t>B | 564呎 (2房)
 $1227万
 $21,761/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -68982,7 +68982,7 @@
           <t>C | 460呎 (2房)
 $954万
 $20,750/呎
-(26年-03月)</t>
+(26年-03月-22日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -68990,7 +68990,7 @@
           <t>D | 330呎 (1房)
 $860万
 $26,055/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -68998,7 +68998,7 @@
           <t>E | 330呎 (1房)
 $643万
 $19,485/呎
-(25年-10月)</t>
+(25年-10月-07日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -69006,7 +69006,7 @@
           <t>F | 330呎 (1房)
 $946万
 $28,676/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -69014,7 +69014,7 @@
           <t>G | 338呎 (1房)
 $696万
 $20,595/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -69022,7 +69022,7 @@
           <t>H | 597呎 (3房)
 $1405万
 $23,538/呎
-(26年-04月)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -69037,7 +69037,7 @@
           <t>A | 454呎 (2房)
 $1209万
 $26,639/呎
-(22年-09月)</t>
+(22年-09月-19日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -69045,7 +69045,7 @@
           <t>B | 564呎 (2房)
 $1221万
 $21,644/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -69053,7 +69053,7 @@
           <t>C | 460呎 (2房)
 $1228万
 $26,704/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -69061,7 +69061,7 @@
           <t>D | 330呎 (1房)
 $894万
 $27,103/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -69069,7 +69069,7 @@
           <t>E | 330呎 (1房)
 $922万
 $27,942/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -69077,7 +69077,7 @@
           <t>F | 330呎 (1房)
 $676万
 $20,479/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -69085,7 +69085,7 @@
           <t>G | 338呎 (1房)
 $703万
 $20,793/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -69093,7 +69093,7 @@
           <t>H | 597呎 (3房)
 $1398万
 $23,412/呎
-(24年-08月)</t>
+(24年-08月-29日)</t>
         </is>
       </c>
     </row>
@@ -69108,7 +69108,7 @@
           <t>A | 454呎 (2房)
 $1174万
 $25,852/呎
-(23年-03月)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -69116,7 +69116,7 @@
           <t>B | 564呎 (2房)
 $1222万
 $21,672/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -69124,7 +69124,7 @@
           <t>C | 460呎 (2房)
 $1278万
 $27,778/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -69132,7 +69132,7 @@
           <t>D | 330呎 (1房)
 $889万
 $26,945/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -69140,7 +69140,7 @@
           <t>E | 330呎 (1房)
 $917万
 $27,779/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -69148,7 +69148,7 @@
           <t>F | 330呎 (1房)
 $672万
 $20,361/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -69156,7 +69156,7 @@
           <t>G | 338呎 (1房)
 $958万
 $28,346/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -69164,7 +69164,7 @@
           <t>H | 597呎 (3房)
 $1474万
 $24,683/呎
-(25年-09月)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -69179,7 +69179,7 @@
           <t>A | 454呎 (2房)
 $1167万
 $25,698/呎
-(23年-03月)</t>
+(23年-03月-16日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -69187,7 +69187,7 @@
           <t>B | 564呎 (2房)
 $1234万
 $21,888/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -69195,7 +69195,7 @@
           <t>C | 460呎 (2房)
 $1270万
 $27,615/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -69203,7 +69203,7 @@
           <t>D | 330呎 (1房)
 $884万
 $26,788/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -69211,7 +69211,7 @@
           <t>E | 330呎 (1房)
 $881万
 $26,703/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -69219,7 +69219,7 @@
           <t>F | 330呎 (1房)
 $678万
 $20,552/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -69227,7 +69227,7 @@
           <t>G | 338呎 (1房)
 $684万
 $20,240/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -69235,7 +69235,7 @@
           <t>H | 597呎 (3房)
 $1382万
 $23,157/呎
-(25年-01月)</t>
+(25年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -69250,7 +69250,7 @@
           <t>A | 454呎 (2房)
 $1160万
 $25,544/呎
-(22年-05月)</t>
+(22年-05月-30日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -69258,7 +69258,7 @@
           <t>B | 564呎 (2房)
 $1190万
 $21,105/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -69266,7 +69266,7 @@
           <t>C | 460呎 (2房)
 $1263万
 $27,454/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -69274,7 +69274,7 @@
           <t>D | 330呎 (1房)
 $879万
 $26,630/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -69282,7 +69282,7 @@
           <t>E | 330呎 (1房)
 $866万
 $26,242/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -69290,7 +69290,7 @@
           <t>F | 330呎 (1房)
 $631万
 $19,115/呎
-(25年-08月)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -69298,7 +69298,7 @@
           <t>G | 338呎 (1房)
 $680万
 $20,121/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -69306,7 +69306,7 @@
           <t>H | 597呎 (3房)
 $1375万
 $23,030/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -69321,7 +69321,7 @@
           <t>A | 454呎 (2房)
 $1181万
 $26,009/呎
-(22年-09月)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -69329,7 +69329,7 @@
           <t>B | 564呎 (2房)
 $1184万
 $20,988/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -69337,7 +69337,7 @@
           <t>C | 460呎 (2房)
 $1256万
 $27,293/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -69345,7 +69345,7 @@
           <t>D | 330呎 (1房)
 $874万
 $26,476/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -69353,7 +69353,7 @@
           <t>E | 330呎 (1房)
 $861万
 $26,088/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -69361,7 +69361,7 @@
           <t>F | 330呎 (1房)
 $627万
 $19,000/呎
-(25年-08月)</t>
+(25年-08月-24日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -69369,7 +69369,7 @@
           <t>G | 338呎 (1房)
 $676万
 $20,003/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -69377,7 +69377,7 @@
           <t>H | 597呎 (3房)
 $1367万
 $22,905/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -69392,7 +69392,7 @@
           <t>A | 454呎 (2房)
 $1251万
 $27,546/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -69400,7 +69400,7 @@
           <t>B | 564呎 (2房)
 $1184万
 $20,988/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -69408,7 +69408,7 @@
           <t>C | 460呎 (2房)
 $1200万
 $26,087/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -69416,7 +69416,7 @@
           <t>D | 330呎 (1房)
 $874万
 $26,476/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -69424,7 +69424,7 @@
           <t>E | 330呎 (1房)
 $861万
 $26,088/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -69432,7 +69432,7 @@
           <t>F | 330呎 (1房)
 $901万
 $27,294/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -69440,7 +69440,7 @@
           <t>G | 338呎 (1房)
 $941万
 $27,849/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -69448,7 +69448,7 @@
           <t>H | 597呎 (3房)
 $1387万
 $23,235/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
     </row>
@@ -69463,7 +69463,7 @@
           <t>A | 454呎 (2房)
 $1144万
 $25,189/呎
-(22年-09月)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -69471,7 +69471,7 @@
           <t>B | 564呎 (2房)
 $1189万
 $21,083/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -69479,7 +69479,7 @@
           <t>C | 460呎 (2房)
 $1241万
 $26,970/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -69487,7 +69487,7 @@
           <t>D | 330呎 (1房)
 $825万
 $25,006/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -69495,7 +69495,7 @@
           <t>E | 330呎 (1房)
 $890万
 $26,970/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -69503,7 +69503,7 @@
           <t>F | 330呎 (1房)
 $607万
 $18,403/呎
-(25年-08月)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -69511,7 +69511,7 @@
           <t>G | 338呎 (1房)
 $930万
 $27,521/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -69519,7 +69519,7 @@
           <t>H | 597呎 (3房)
 $1372万
 $22,977/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
     </row>
@@ -69534,7 +69534,7 @@
           <t>A | 454呎 (2房)
 $1140万
 $25,115/呎
-(22年-05月)</t>
+(22年-05月-29日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -69542,7 +69542,7 @@
           <t>B | 564呎 (2房)
 $1164万
 $20,640/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -69550,7 +69550,7 @@
           <t>C | 460呎 (2房)
 $938万
 $20,398/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -69558,7 +69558,7 @@
           <t>D | 330呎 (1房)
 $820万
 $24,855/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -69566,7 +69566,7 @@
           <t>E | 330呎 (1房)
 $885万
 $26,809/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -69574,7 +69574,7 @@
           <t>F | 330呎 (1房)
 $885万
 $26,809/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -69582,7 +69582,7 @@
           <t>G | 338呎 (1房)
 $925万
 $27,358/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -69590,7 +69590,7 @@
           <t>H | 597呎 (3房)
 $1364万
 $22,848/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -69605,7 +69605,7 @@
           <t>A | 454呎 (2房)
 $1164万
 $25,648/呎
-(22年-09月)</t>
+(22年-09月-12日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -69613,7 +69613,7 @@
           <t>B | 564呎 (2房)
 $1158万
 $20,525/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -69621,7 +69621,7 @@
           <t>C | 460呎 (2房)
 $1226万
 $26,648/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -69629,7 +69629,7 @@
           <t>D | 330呎 (1房)
 $853万
 $25,848/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -69637,7 +69637,7 @@
           <t>E | 330呎 (1房)
 $840万
 $25,470/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -69645,7 +69645,7 @@
           <t>F | 330呎 (1房)
 $879万
 $26,645/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -69653,7 +69653,7 @@
           <t>G | 338呎 (1房)
 $919万
 $27,189/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -69661,7 +69661,7 @@
           <t>H | 598呎 (3房)
 $1664万
 $27,828/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -69676,7 +69676,7 @@
           <t>A | 454呎 (2房)
 $1174万
 $25,870/呎
-(22年-06月)</t>
+(22年-06月-09日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -69684,7 +69684,7 @@
           <t>B | 564呎 (2房)
 $1169万
 $20,730/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -69692,7 +69692,7 @@
           <t>C | 460呎 (2房)
 $1164万
 $25,315/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -69700,7 +69700,7 @@
           <t>D | 330呎 (1房)
 $810万
 $24,555/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -69708,7 +69708,7 @@
           <t>E | 330呎 (1房)
 $874万
 $26,485/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -69716,7 +69716,7 @@
           <t>F | 330呎 (1房)
 $874万
 $26,485/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -69724,7 +69724,7 @@
           <t>G | 338呎 (1房)
 $895万
 $26,485/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -69732,7 +69732,7 @@
           <t>H | 597呎 (3房)
 $1330万
 $22,270/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -69747,7 +69747,7 @@
           <t>A | 454呎 (2房)
 $1130万
 $24,888/呎
-(22年-05月)</t>
+(22年-05月-24日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -69755,7 +69755,7 @@
           <t>B | 564呎 (2房)
 $1145万
 $20,294/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -69763,7 +69763,7 @@
           <t>C | 460呎 (2房)
 $922万
 $20,033/呎
-(26年-03月)</t>
+(26年-03月-23日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -69771,7 +69771,7 @@
           <t>D | 330呎 (1房)
 $805万
 $24,406/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -69779,7 +69779,7 @@
           <t>E | 330呎 (1房)
 $869万
 $26,324/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -69787,7 +69787,7 @@
           <t>F | 330呎 (1房)
 $869万
 $26,324/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -69795,7 +69795,7 @@
           <t>G | 338呎 (1房)
 $622万
 $18,396/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -69803,7 +69803,7 @@
           <t>H | 597呎 (3房)
 $1322万
 $22,142/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
     </row>
@@ -69818,7 +69818,7 @@
           <t>A | 454呎 (2房)
 $1127万
 $24,815/呎
-(22年-06月)</t>
+(22年-06月-05日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -69826,7 +69826,7 @@
           <t>B | 564呎 (2房)
 $1138万
 $20,179/呎
-(24年-03月)</t>
+(24年-03月-02日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -69834,7 +69834,7 @@
           <t>C | 460呎 (2房)
 $1204万
 $26,163/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -69842,7 +69842,7 @@
           <t>D | 330呎 (1房)
 $837万
 $25,376/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -69850,7 +69850,7 @@
           <t>E | 330呎 (1房)
 $863万
 $26,161/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -69858,7 +69858,7 @@
           <t>F | 330呎 (1房)
 $863万
 $26,161/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -69866,7 +69866,7 @@
           <t>G | 338呎 (1房)
 $884万
 $26,163/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -69874,7 +69874,7 @@
           <t>H | 598呎 (3房)
 $1636万
 $27,356/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
     </row>
@@ -69889,7 +69889,7 @@
           <t>A | 454呎 (2房)
 $1178万
 $25,941/呎
-(21年-12月)</t>
+(21年-12月-13日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -69897,7 +69897,7 @@
           <t>B | 564呎 (2房)
 $1149万
 $20,378/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -69905,7 +69905,7 @@
           <t>C | 460呎 (2房)
 $1196万
 $26,002/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -69913,7 +69913,7 @@
           <t>D | 330呎 (1房)
 $832万
 $25,221/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -69921,7 +69921,7 @@
           <t>E | 330呎 (1房)
 $832万
 $25,221/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -69929,7 +69929,7 @@
           <t>F | 330呎 (1房)
 $820万
 $24,852/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -69937,7 +69937,7 @@
           <t>G | 338呎 (1房)
 $879万
 $26,000/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -69945,7 +69945,7 @@
           <t>H | 598呎 (3房)
 $1720万
 $28,769/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -69960,7 +69960,7 @@
           <t>A | 454呎 (2房)
 $1147万
 $25,264/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -69968,7 +69968,7 @@
           <t>B | 564呎 (2房)
 $1457万
 $25,830/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -69976,7 +69976,7 @@
           <t>C | 460呎 (2房)
 $1188万
 $25,837/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -69984,7 +69984,7 @@
           <t>D | 330呎 (1房)
 $827万
 $25,061/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -69992,7 +69992,7 @@
           <t>E | 330呎 (1房)
 $827万
 $25,061/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -70000,7 +70000,7 @@
           <t>F | 330呎 (1房)
 $815万
 $24,697/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -70008,7 +70008,7 @@
           <t>G | 338呎 (1房)
 $835万
 $24,695/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -70016,7 +70016,7 @@
           <t>H | 597呎 (3房)
 $1636万
 $27,399/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -70031,7 +70031,7 @@
           <t>A | 454呎 (2房)
 $1147万
 $25,264/呎
-(22年-05月)</t>
+(22年-05月-29日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -70039,7 +70039,7 @@
           <t>B | 564呎 (2房)
 $1524万
 $27,025/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -70047,7 +70047,7 @@
           <t>C | 460呎 (2房)
 $1188万
 $25,837/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -70055,7 +70055,7 @@
           <t>D | 330呎 (1房)
 $827万
 $25,061/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -70063,7 +70063,7 @@
           <t>E | 330呎 (1房)
 $608万
 $18,415/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -70071,7 +70071,7 @@
           <t>F | 330呎 (1房)
 $596万
 $18,058/呎
-(25年-07月)</t>
+(25年-07月-30日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -70079,7 +70079,7 @@
           <t>G | 338呎 (1房)
 $873万
 $25,837/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -70087,7 +70087,7 @@
           <t>H | 598呎 (3房)
 $1617万
 $27,040/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
     </row>
@@ -70102,7 +70102,7 @@
           <t>A | 454呎 (2房)
 $1140万
 $25,115/呎
-(22年-05月)</t>
+(22年-05月-15日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -70110,7 +70110,7 @@
           <t>B | 564呎 (2房)
 $1157万
 $20,512/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -70118,7 +70118,7 @@
           <t>C | 460呎 (2房)
 $1138万
 $24,750/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -70126,7 +70126,7 @@
           <t>D | 330呎 (1房)
 $817万
 $24,748/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -70134,7 +70134,7 @@
           <t>E | 330呎 (1房)
 $781万
 $23,655/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -70142,7 +70142,7 @@
           <t>F | 330呎 (1房)
 $817万
 $24,748/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -70150,7 +70150,7 @@
           <t>G | 338呎 (1房)
 $824万
 $24,388/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -70158,7 +70158,7 @@
           <t>H | 597呎 (3房)
 $1672万
 $28,007/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -70173,7 +70173,7 @@
           <t>A | 454呎 (2房)
 $1110万
 $24,447/呎
-(22年-05月)</t>
+(22年-05月-15日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -70181,7 +70181,7 @@
           <t>B | 564呎 (2房)
 $1498万
 $26,551/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -70189,7 +70189,7 @@
           <t>C | 460呎 (2房)
 $1081万
 $23,507/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -70197,7 +70197,7 @@
           <t>D | 330呎 (1房)
 $812万
 $24,594/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -70205,7 +70205,7 @@
           <t>E | 330呎 (1房)
 $776万
 $23,506/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -70213,7 +70213,7 @@
           <t>F | 330呎 (1房)
 $776万
 $23,506/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -70221,7 +70221,7 @@
           <t>G | 338呎 (1房)
 $819万
 $24,234/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -70229,7 +70229,7 @@
           <t>H | 597呎 (3房)
 $1631万
 $27,317/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
     </row>
@@ -70244,7 +70244,7 @@
           <t>A | 454呎 (2房)
 $1133万
 $24,963/呎
-(22年-09月)</t>
+(22年-09月-25日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -70252,7 +70252,7 @@
           <t>B | 564呎 (2房)
 $1423万
 $25,230/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -70260,7 +70260,7 @@
           <t>C | 460呎 (2房)
 $1124万
 $24,437/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -70268,7 +70268,7 @@
           <t>D | 330呎 (1房)
 $806万
 $24,436/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -70276,7 +70276,7 @@
           <t>E | 330呎 (1房)
 $806万
 $24,436/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -70284,7 +70284,7 @@
           <t>F | 330呎 (1房)
 $771万
 $23,358/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -70292,7 +70292,7 @@
           <t>G | 338呎 (1房)
 $852万
 $25,195/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -70300,7 +70300,7 @@
           <t>H | 597呎 (3房)
 $1501万
 $25,147/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -70315,7 +70315,7 @@
           <t>A | 454呎 (2房)
 $1130万
 $24,890/呎
-(22年-05月)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -70323,7 +70323,7 @@
           <t>B | 564呎 (2房)
 $1414万
 $25,080/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -70331,7 +70331,7 @@
           <t>C | 460呎 (2房)
 $1068万
 $23,207/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -70339,7 +70339,7 @@
           <t>D | 330呎 (1房)
 $775万
 $23,476/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -70347,7 +70347,7 @@
           <t>E | 330呎 (1房)
 $801万
 $24,279/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -70355,7 +70355,7 @@
           <t>F | 330呎 (1房)
 $766万
 $23,206/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -70363,7 +70363,7 @@
           <t>G | 338呎 (1房)
 $846万
 $25,027/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -70371,7 +70371,7 @@
           <t>H | 597呎 (3房)
 $1510万
 $25,286/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -70386,7 +70386,7 @@
           <t>A | 454呎 (2房)
 $1086万
 $23,914/呎
-(22年-05月)</t>
+(22年-05月-30日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -70394,7 +70394,7 @@
           <t>B | 564呎 (2房)
 $1392万
 $24,681/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -70402,7 +70402,7 @@
           <t>C | 460呎 (2房)
 $1122万
 $24,389/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -70410,7 +70410,7 @@
           <t>D | 330呎 (1房)
 $796万
 $24,124/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -70418,7 +70418,7 @@
           <t>E | 330呎 (1房)
 $796万
 $24,124/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -70426,7 +70426,7 @@
           <t>F | 330呎 (1房)
 $761万
 $23,058/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -70434,7 +70434,7 @@
           <t>G | 338呎 (1房)
 $599万
 $17,722/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -70442,7 +70442,7 @@
           <t>H | 598呎 (3房)
 $1536万
 $25,691/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -70457,7 +70457,7 @@
           <t>A | 454呎 (2房)
 $1074万
 $23,656/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -70465,7 +70465,7 @@
           <t>B | 564呎 (2房)
 $1343万
 $23,805/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -70473,7 +70473,7 @@
           <t>C | 460呎 (2房)
 $1102万
 $23,965/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -70481,7 +70481,7 @@
           <t>D | 330呎 (1房)
 $791万
 $23,964/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -70489,7 +70489,7 @@
           <t>E | 330呎 (1房)
 $791万
 $23,964/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -70497,7 +70497,7 @@
           <t>F | 330呎 (1房)
 $581万
 $17,609/呎
-(25年-02月)</t>
+(25年-02月-10日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -70505,7 +70505,7 @@
           <t>G | 338呎 (1房)
 $798万
 $23,615/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -70513,7 +70513,7 @@
           <t>H | 598呎 (3房)
 $1464万
 $24,488/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -70528,7 +70528,7 @@
           <t>A | 454呎 (2房)
 $1068万
 $23,524/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -70536,7 +70536,7 @@
           <t>B | 564呎 (2房)
 $1365万
 $24,202/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -70544,7 +70544,7 @@
           <t>C | 460呎 (2房)
 $1047万
 $22,757/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -70552,7 +70552,7 @@
           <t>D | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -70560,7 +70560,7 @@
           <t>E | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -70568,7 +70568,7 @@
           <t>F | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -70576,7 +70576,7 @@
           <t>G | 338呎 (1房)
 $830万
 $24,547/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -70584,7 +70584,7 @@
           <t>H | 598呎 (3房)
 $1439万
 $24,070/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -70599,7 +70599,7 @@
           <t>A | 454呎 (2房)
 $848万
 $18,685/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -70607,7 +70607,7 @@
           <t>B | 564呎 (2房)
 $1305万
 $23,131/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -70615,7 +70615,7 @@
           <t>C | 460呎 (2房)
 $1047万
 $22,757/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -70623,7 +70623,7 @@
           <t>D | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -70631,7 +70631,7 @@
           <t>E | 330呎 (1房)
 $751万
 $22,758/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -70639,7 +70639,7 @@
           <t>F | 330呎 (1房)
 $786万
 $23,812/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -70647,7 +70647,7 @@
           <t>G | 338呎 (1房)
 $793万
 $23,462/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -70655,7 +70655,7 @@
           <t>H | 598呎 (3房)
 $1376万
 $23,007/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -70670,7 +70670,7 @@
           <t>A | 454呎 (2房)
 $837万
 $18,445/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -70678,7 +70678,7 @@
           <t>B | 564呎 (2房)
 $1035万
 $18,344/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -70686,7 +70686,7 @@
           <t>C | 460呎 (2房)
 $1081万
 $23,496/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -70694,7 +70694,7 @@
           <t>D | 330呎 (1房)
 $578万
 $17,524/呎
-(25年-07月)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -70702,7 +70702,7 @@
           <t>E | 330呎 (1房)
 $775万
 $23,497/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -70710,7 +70710,7 @@
           <t>F | 330呎 (1房)
 $570万
 $17,264/呎
-(25年-02月)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -70718,7 +70718,7 @@
           <t>G | 338呎 (1房)
 $782万
 $23,151/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -70726,7 +70726,7 @@
           <t>H | 598呎 (3房)
 $1358万
 $22,707/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -70741,7 +70741,7 @@
           <t>A | 454呎 (2房)
 $1035万
 $22,806/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -70749,7 +70749,7 @@
           <t>B | 564呎 (2房)
 $1279万
 $22,683/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -70757,7 +70757,7 @@
           <t>C | 460呎 (2房)
 $1074万
 $23,339/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -70765,7 +70765,7 @@
           <t>D | 330呎 (1房)
 $574万
 $17,406/呎
-(25年-08月)</t>
+(25年-08月-06日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -70773,7 +70773,7 @@
           <t>E | 330呎 (1房)
 $770万
 $23,336/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -70781,7 +70781,7 @@
           <t>F | 330呎 (1房)
 $770万
 $23,336/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -70789,7 +70789,7 @@
           <t>G | 338呎 (1房)
 $813万
 $24,062/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -70797,7 +70797,7 @@
           <t>H | 598呎 (3房)
 $1349万
 $22,557/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
     </row>
@@ -70812,7 +70812,7 @@
           <t>A | 454呎 (2房)
 $1076万
 $23,705/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -70820,7 +70820,7 @@
           <t>B | 564呎 (2房)
 $1021万
 $18,103/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -70828,7 +70828,7 @@
           <t>C | 460呎 (2房)
 $1031万
 $22,413/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -70836,7 +70836,7 @@
           <t>D | 330呎 (1房)
 $765万
 $23,182/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -70844,7 +70844,7 @@
           <t>E | 330呎 (1房)
 $731万
 $22,158/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -70852,7 +70852,7 @@
           <t>F | 330呎 (1房)
 $765万
 $23,182/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -70860,7 +70860,7 @@
           <t>G | 338呎 (1房)
 $808万
 $23,899/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -70868,7 +70868,7 @@
           <t>H | 597呎 (3房)
 $1123万
 $18,811/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
     </row>
@@ -70883,7 +70883,7 @@
           <t>A | 454呎 (2房)
 $1034万
 $22,767/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -70891,7 +70891,7 @@
           <t>B | 564呎 (2房)
 $1321万
 $23,417/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -70899,7 +70899,7 @@
           <t>C | 460呎 (2房)
 $1047万
 $22,761/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -70907,7 +70907,7 @@
           <t>D | 330呎 (1房)
 $718万
 $21,758/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -70915,7 +70915,7 @@
           <t>E | 330呎 (1房)
 $751万
 $22,764/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -70923,7 +70923,7 @@
           <t>F | 330呎 (1房)
 $751万
 $22,764/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -70931,7 +70931,7 @@
           <t>G | 338呎 (1房)
 $758万
 $22,429/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -70939,7 +70939,7 @@
           <t>H | 598呎 (3房)
 $1393万
 $23,288/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -70954,7 +70954,7 @@
           <t>A | 454呎 (2房)
 $1062万
 $23,392/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -70962,7 +70962,7 @@
           <t>B | 564呎 (2房)
 $1254万
 $22,232/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -70970,7 +70970,7 @@
           <t>C | 460呎 (2房)
 $982万
 $21,352/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -70978,7 +70978,7 @@
           <t>D | 330呎 (1房)
 $729万
 $22,085/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -70986,7 +70986,7 @@
           <t>E | 330呎 (1房)
 $697万
 $21,109/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -70994,7 +70994,7 @@
           <t>F | 330呎 (1房)
 $729万
 $22,085/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -71002,7 +71002,7 @@
           <t>G | 338呎 (1房)
 $770万
 $22,766/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -71010,7 +71010,7 @@
           <t>H | 597呎 (3房)
 $1337万
 $22,400/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -71025,7 +71025,7 @@
           <t>A | 454呎 (2房)
 $1043万
 $22,974/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -71033,7 +71033,7 @@
           <t>B | 564呎 (2房)
 $1288万
 $22,842/呎
-(21年-09月)</t>
+(21年-09月-21日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -71041,7 +71041,7 @@
           <t>C | 460呎 (2房)
 $973万
 $21,143/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -71049,7 +71049,7 @@
           <t>D | 330呎 (1房)
 $687万
 $20,809/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -71057,7 +71057,7 @@
           <t>E | 330呎 (1房)
 $687万
 $20,809/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -71065,7 +71065,7 @@
           <t>F | 330呎 (1房)
 $687万
 $20,809/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -71073,7 +71073,7 @@
           <t>G | 338呎 (1房)
 $578万
 $17,101/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -71081,7 +71081,7 @@
           <t>H | 597呎 (3房)
 $1358万
 $22,749/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
     </row>
@@ -71243,7 +71243,7 @@
           <t>A | 777呎 (3房)
 $2160万
 $27,799/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -71251,7 +71251,7 @@
           <t>B | 766呎 (3房)
 $1943万
 $25,362/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -71259,7 +71259,7 @@
           <t>C | 439呎 (2房)
 $926万
 $21,093/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -71267,7 +71267,7 @@
           <t>D | 427呎 (2房)
 $912万
 $21,370/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -71275,7 +71275,7 @@
           <t>E | 333呎 (1房)
 $713万
 $21,408/呎
-(26年-04月)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -71283,7 +71283,7 @@
           <t>F | 445呎 (2房)
 $940万
 $21,126/呎
-(24年-04月)</t>
+(24年-04月-17日)</t>
         </is>
       </c>
       <c r="H5" s="20" t="inlineStr">
@@ -71291,7 +71291,7 @@
           <t>G | 482呎 (2房)
 $969万
 $20,110/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="I5" s="20" t="inlineStr">
@@ -71299,7 +71299,7 @@
           <t>H | 787呎 (3房)
 $2439万
 $30,991/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -71314,7 +71314,7 @@
           <t>A | 763呎 (3房)
 $1915万
 $25,101/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -71322,7 +71322,7 @@
           <t>B | 766呎 (3房)
 $2453万
 $32,026/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -71330,7 +71330,7 @@
           <t>C | 439呎 (2房)
 $919万
 $20,925/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -71338,7 +71338,7 @@
           <t>D | 427呎 (2房)
 $907万
 $21,244/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -71346,7 +71346,7 @@
           <t>E | 333呎 (1房)
 $698万
 $20,961/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -71354,7 +71354,7 @@
           <t>F | 445呎 (2房)
 $1172万
 $26,330/呎
-(21年-09月)</t>
+(21年-09月-22日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -71362,7 +71362,7 @@
           <t>G | 482呎 (2房)
 $964万
 $19,994/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -71370,7 +71370,7 @@
           <t>H | 774呎 (3房)
 $2021万
 $26,107/呎
-(24年-12月)</t>
+(24年-12月-02日)</t>
         </is>
       </c>
     </row>
@@ -71385,7 +71385,7 @@
           <t>A | 763呎 (3房)
 $1910万
 $25,031/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -71393,7 +71393,7 @@
           <t>B | 766呎 (3房)
 $2333万
 $30,452/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -71401,7 +71401,7 @@
           <t>C | 439呎 (2房)
 $913万
 $20,793/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -71409,7 +71409,7 @@
           <t>D | 427呎 (2房)
 $902万
 $21,115/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -71417,7 +71417,7 @@
           <t>E | 332呎 (1房)
 $888万
 $26,741/呎
-(23年-05月)</t>
+(23年-05月-29日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -71425,7 +71425,7 @@
           <t>F | 445呎 (2房)
 $1232万
 $27,692/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -71433,7 +71433,7 @@
           <t>G | 482呎 (2房)
 $1256万
 $26,050/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -71441,7 +71441,7 @@
           <t>H | 774呎 (3房)
 $2012万
 $25,999/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
     </row>
@@ -71456,7 +71456,7 @@
           <t>A | 763呎 (3房)
 $1962万
 $25,714/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -71464,7 +71464,7 @@
           <t>B | 766呎 (3房)
 $2213万
 $28,892/呎
-(22年-09月)</t>
+(22年-09月-26日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -71472,7 +71472,7 @@
           <t>C | 439呎 (2房)
 $907万
 $20,667/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -71480,7 +71480,7 @@
           <t>D | 427呎 (2房)
 $896万
 $20,988/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -71488,7 +71488,7 @@
           <t>E | 333呎 (1房)
 $926万
 $27,796/呎
-(21年-08月)</t>
+(21年-08月-02日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -71496,7 +71496,7 @@
           <t>F | 445呎 (2房)
 $910万
 $20,458/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -71504,7 +71504,7 @@
           <t>G | 482呎 (2房)
 $952万
 $19,761/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -71512,7 +71512,7 @@
           <t>H | 774呎 (3房)
 $2053万
 $26,523/呎
-(26年-05月)</t>
+(26年-05月-18日)</t>
         </is>
       </c>
     </row>
@@ -71527,7 +71527,7 @@
           <t>A | 763呎 (3房)
 $1900万
 $24,895/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -71535,7 +71535,7 @@
           <t>B | 766呎 (3房)
 $2202万
 $28,740/呎
-(23年-06月)</t>
+(23年-06月-22日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -71543,7 +71543,7 @@
           <t>C | 439呎 (2房)
 $902万
 $20,542/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -71551,7 +71551,7 @@
           <t>D | 427呎 (2房)
 $891万
 $20,864/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -71559,7 +71559,7 @@
           <t>E | 332呎 (1房)
 $963万
 $29,006/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -71567,7 +71567,7 @@
           <t>F | 445呎 (2房)
 $1151万
 $25,872/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -71575,7 +71575,7 @@
           <t>G | 482呎 (2房)
 $1298万
 $26,936/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -71583,7 +71583,7 @@
           <t>H | 774呎 (3房)
 $2004万
 $25,898/呎
-(24年-07月)</t>
+(24年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -71598,7 +71598,7 @@
           <t>A | 763呎 (3房)
 $1894万
 $24,827/呎
-(24年-02月)</t>
+(24年-02月-15日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -71606,7 +71606,7 @@
           <t>B | 766呎 (3房)
 $1914万
 $24,984/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -71614,7 +71614,7 @@
           <t>C | 439呎 (2房)
 $896万
 $20,419/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -71622,7 +71622,7 @@
           <t>D | 427呎 (2房)
 $886万
 $20,740/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -71630,7 +71630,7 @@
           <t>E | 332呎 (1房)
 $915万
 $27,566/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -71638,7 +71638,7 @@
           <t>F | 445呎 (2房)
 $1144万
 $25,719/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -71646,7 +71646,7 @@
           <t>G | 482呎 (2房)
 $1291万
 $26,776/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -71654,7 +71654,7 @@
           <t>H | 774呎 (3房)
 $1999万
 $25,831/呎
-(24年-08月)</t>
+(24年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -71669,7 +71669,7 @@
           <t>A | 763呎 (3房)
 $1889万
 $24,758/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -71677,7 +71677,7 @@
           <t>B | 766呎 (3房)
 $2284万
 $29,815/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -71685,7 +71685,7 @@
           <t>C | 439呎 (2房)
 $891万
 $20,296/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -71693,7 +71693,7 @@
           <t>D | 427呎 (2房)
 $880万
 $20,618/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -71701,7 +71701,7 @@
           <t>E | 332呎 (1房)
 $868万
 $26,142/呎
-(23年-02月)</t>
+(23年-02月-08日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -71709,7 +71709,7 @@
           <t>F | 445呎 (2房)
 $1138万
 $25,566/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -71717,7 +71717,7 @@
           <t>G | 482呎 (2房)
 $1283万
 $26,614/呎
-(21年-07月)</t>
+(21年-07月-04日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -71725,7 +71725,7 @@
           <t>H | 774呎 (3房)
 $1994万
 $25,760/呎
-(24年-12月)</t>
+(24年-12月-15日)</t>
         </is>
       </c>
     </row>
@@ -71740,7 +71740,7 @@
           <t>A | 763呎 (3房)
 $1889万
 $24,758/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -71748,7 +71748,7 @@
           <t>B | 766呎 (3房)
 $2389万
 $31,193/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -71756,7 +71756,7 @@
           <t>C | 439呎 (2房)
 $891万
 $20,296/呎
-(24年-03月)</t>
+(24年-03月-07日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -71764,7 +71764,7 @@
           <t>D | 427呎 (2房)
 $880万
 $20,618/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -71772,7 +71772,7 @@
           <t>E | 333呎 (1房)
 $952万
 $28,589/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -71780,7 +71780,7 @@
           <t>F | 445呎 (2房)
 $1138万
 $25,566/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -71788,7 +71788,7 @@
           <t>G | 482呎 (2房)
 $1283万
 $26,614/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -71796,7 +71796,7 @@
           <t>H | 774呎 (3房)
 $1994万
 $25,760/呎
-(25年-07月)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -71811,7 +71811,7 @@
           <t>A | 763呎 (3房)
 $2152万
 $28,201/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -71819,7 +71819,7 @@
           <t>B | 766呎 (3房)
 $1869万
 $24,397/呎
-(24年-01月)</t>
+(24年-01月-04日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -71827,7 +71827,7 @@
           <t>C | 439呎 (2房)
 $880万
 $20,052/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -71835,7 +71835,7 @@
           <t>D | 427呎 (2房)
 $873万
 $20,454/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -71843,7 +71843,7 @@
           <t>E | 332呎 (1房)
 $941万
 $28,346/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -71851,7 +71851,7 @@
           <t>F | 445呎 (2房)
 $902万
 $20,261/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -71859,7 +71859,7 @@
           <t>G | 482呎 (2房)
 $1267万
 $26,295/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -71867,7 +71867,7 @@
           <t>H | 774呎 (3房)
 $1983万
 $25,623/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -71882,7 +71882,7 @@
           <t>A | 763呎 (3房)
 $1874万
 $24,556/呎
-(24年-02月)</t>
+(24年-02月-26日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -71890,7 +71890,7 @@
           <t>B | 766呎 (3房)
 $1891万
 $24,687/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -71898,7 +71898,7 @@
           <t>C | 439呎 (2房)
 $875万
 $19,936/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -71906,7 +71906,7 @@
           <t>D | 427呎 (2房)
 $871万
 $20,393/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -71914,7 +71914,7 @@
           <t>E | 332呎 (1房)
 $904万
 $27,244/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -71922,7 +71922,7 @@
           <t>F | 445呎 (2房)
 $1169万
 $26,267/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -71930,7 +71930,7 @@
           <t>G | 482呎 (2房)
 $1204万
 $24,979/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -71938,7 +71938,7 @@
           <t>H | 774呎 (3房)
 $1980万
 $25,580/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -71953,7 +71953,7 @@
           <t>A | 763呎 (3房)
 $1868万
 $24,488/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -71961,7 +71961,7 @@
           <t>B | 766呎 (3房)
 $2364万
 $30,864/呎
-(21年-11月)</t>
+(21年-11月-14日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -71969,7 +71969,7 @@
           <t>C | 439呎 (2房)
 $891万
 $20,296/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -71977,7 +71977,7 @@
           <t>D | 427呎 (2房)
 $868万
 $20,333/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -71985,7 +71985,7 @@
           <t>E | 332呎 (1房)
 $930万
 $28,015/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -71993,7 +71993,7 @@
           <t>F | 445呎 (2房)
 $1110万
 $24,955/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -72001,7 +72001,7 @@
           <t>G | 482呎 (2房)
 $913万
 $18,944/呎
-(25年-01月)</t>
+(25年-01月-21日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -72009,7 +72009,7 @@
           <t>H | 774呎 (3房)
 $1972万
 $25,483/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
     </row>
@@ -72024,7 +72024,7 @@
           <t>A | 763呎 (3房)
 $1864万
 $24,434/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -72032,7 +72032,7 @@
           <t>B | 766呎 (3房)
 $2351万
 $30,696/呎
-(21年-11月)</t>
+(21年-11月-14日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -72040,7 +72040,7 @@
           <t>C | 439呎 (2房)
 $865万
 $19,699/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -72048,7 +72048,7 @@
           <t>D | 427呎 (2房)
 $866万
 $20,272/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -72056,7 +72056,7 @@
           <t>E | 332呎 (1房)
 $925万
 $27,852/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -72064,7 +72064,7 @@
           <t>F | 445呎 (2房)
 $1104万
 $24,802/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -72072,7 +72072,7 @@
           <t>G | 482呎 (2房)
 $1244万
 $25,815/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -72080,7 +72080,7 @@
           <t>H | 774呎 (3房)
 $1967万
 $25,415/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
     </row>
@@ -72095,7 +72095,7 @@
           <t>A | 763呎 (3房)
 $1858万
 $24,351/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -72103,7 +72103,7 @@
           <t>B | 766呎 (3房)
 $2211万
 $28,859/呎
-(21年-09月)</t>
+(21年-09月-12日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -72111,7 +72111,7 @@
           <t>C | 439呎 (2房)
 $860万
 $19,588/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -72119,7 +72119,7 @@
           <t>D | 427呎 (2房)
 $876万
 $20,504/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -72127,7 +72127,7 @@
           <t>E | 333呎 (1房)
 $889万
 $26,688/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -72135,7 +72135,7 @@
           <t>F | 445呎 (2房)
 $1097万
 $24,649/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -72143,7 +72143,7 @@
           <t>G | 482呎 (2房)
 $904万
 $18,751/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -72151,7 +72151,7 @@
           <t>H | 774呎 (3房)
 $1953万
 $25,231/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -72166,7 +72166,7 @@
           <t>A | 763呎 (3房)
 $1853万
 $24,284/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -72174,7 +72174,7 @@
           <t>B | 766呎 (3房)
 $2326万
 $30,359/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -72182,7 +72182,7 @@
           <t>C | 439呎 (2房)
 $857万
 $19,528/呎
-(23年-12月)</t>
+(23年-12月-14日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -72190,7 +72190,7 @@
           <t>D | 427呎 (2房)
 $1021万
 $23,920/呎
-(23年-05月)</t>
+(23年-05月-01日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -72198,7 +72198,7 @@
           <t>E | 332呎 (1房)
 $914万
 $27,518/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -72206,7 +72206,7 @@
           <t>F | 445呎 (2房)
 $1090万
 $24,497/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -72214,7 +72214,7 @@
           <t>G | 482呎 (2房)
 $1151万
 $23,882/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -72222,7 +72222,7 @@
           <t>H | 774呎 (3房)
 $1948万
 $25,161/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -72237,7 +72237,7 @@
           <t>A | 763呎 (3房)
 $1848万
 $24,215/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -72245,7 +72245,7 @@
           <t>B | 766呎 (3房)
 $2287万
 $29,859/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -72253,7 +72253,7 @@
           <t>C | 439呎 (2房)
 $855万
 $19,469/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -72261,7 +72261,7 @@
           <t>D | 427呎 (2房)
 $1055万
 $24,717/呎
-(22年-05月)</t>
+(22年-05月-12日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -72269,7 +72269,7 @@
           <t>E | 333呎 (1房)
 $908万
 $27,273/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -72277,7 +72277,7 @@
           <t>F | 445呎 (2房)
 $864万
 $19,416/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -72285,7 +72285,7 @@
           <t>G | 482呎 (2房)
 $1197万
 $24,828/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -72293,7 +72293,7 @@
           <t>H | 774呎 (3房)
 $1942万
 $25,094/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
     </row>
@@ -72308,7 +72308,7 @@
           <t>A | 763呎 (3房)
 $1842万
 $24,148/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -72316,7 +72316,7 @@
           <t>B | 766呎 (3房)
 $2073万
 $27,068/呎
-(23年-04月)</t>
+(23年-04月-27日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -72324,7 +72324,7 @@
           <t>C | 439呎 (2房)
 $852万
 $19,410/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -72332,7 +72332,7 @@
           <t>D | 427呎 (2房)
 $1015万
 $23,778/呎
-(22年-08月)</t>
+(22年-08月-21日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -72340,7 +72340,7 @@
           <t>E | 332呎 (1房)
 $903万
 $27,190/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -72348,7 +72348,7 @@
           <t>F | 445呎 (2房)
 $1055万
 $23,706/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -72356,7 +72356,7 @@
           <t>G | 482呎 (2房)
 $1189万
 $24,670/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -72364,7 +72364,7 @@
           <t>H | 774呎 (3房)
 $1937万
 $25,025/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -72379,7 +72379,7 @@
           <t>A | 763呎 (3房)
 $1842万
 $24,148/呎
-(25年-02月)</t>
+(25年-02月-09日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -72387,7 +72387,7 @@
           <t>B | 766呎 (3房)
 $2073万
 $27,068/呎
-(23年-04月)</t>
+(23年-04月-19日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -72395,7 +72395,7 @@
           <t>C | 439呎 (2房)
 $852万
 $19,410/呎
-(23年-12月)</t>
+(23年-12月-06日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -72403,7 +72403,7 @@
           <t>D | 428呎 (2房)
 $1040万
 $24,297/呎
-(22年-05月)</t>
+(22年-05月-31日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -72411,7 +72411,7 @@
           <t>E | 332呎 (1房)
 $903万
 $27,190/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -72419,7 +72419,7 @@
           <t>F | 445呎 (2房)
 $842万
 $18,910/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -72427,7 +72427,7 @@
           <t>G | 482呎 (2房)
 $887万
 $18,400/呎
-(24年-06月)</t>
+(24年-06月-27日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -72435,7 +72435,7 @@
           <t>H | 774呎 (3房)
 $1937万
 $25,025/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
     </row>
@@ -72450,7 +72450,7 @@
           <t>A | 763呎 (3房)
 $1925万
 $25,231/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -72458,7 +72458,7 @@
           <t>B | 766呎 (3房)
 $2050万
 $26,765/呎
-(23年-05月)</t>
+(23年-05月-03日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -72466,7 +72466,7 @@
           <t>C | 439呎 (2房)
 $846万
 $19,267/呎
-(24年-03月)</t>
+(24年-03月-03日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -72474,7 +72474,7 @@
           <t>D | 428呎 (2房)
 $1009万
 $23,582/呎
-(23年-03月)</t>
+(23年-03月-20日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -72482,7 +72482,7 @@
           <t>E | 333呎 (1房)
 $637万
 $19,138/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -72490,7 +72490,7 @@
           <t>F | 445呎 (2房)
 $1054万
 $23,676/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -72498,7 +72498,7 @@
           <t>G | 482呎 (2房)
 $1174万
 $24,359/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -72506,7 +72506,7 @@
           <t>H | 774呎 (3房)
 $1926万
 $24,886/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -72521,7 +72521,7 @@
           <t>A | 763呎 (3房)
 $1827万
 $23,945/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -72529,7 +72529,7 @@
           <t>B | 766呎 (3房)
 $2137万
 $27,903/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -72537,7 +72537,7 @@
           <t>C | 439呎 (2房)
 $847万
 $19,294/呎
-(24年-02月)</t>
+(24年-02月-08日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -72545,7 +72545,7 @@
           <t>D | 428呎 (2房)
 $1006万
 $23,509/呎
-(22年-06月)</t>
+(22年-06月-09日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -72553,7 +72553,7 @@
           <t>E | 332呎 (1房)
 $869万
 $26,163/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -72561,7 +72561,7 @@
           <t>F | 445呎 (2房)
 $1047万
 $23,526/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -72569,7 +72569,7 @@
           <t>G | 482呎 (2房)
 $1115万
 $23,131/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -72577,7 +72577,7 @@
           <t>H | 774呎 (3房)
 $1921万
 $24,817/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
     </row>
@@ -72592,7 +72592,7 @@
           <t>A | 763呎 (3房)
 $1880万
 $24,640/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -72600,7 +72600,7 @@
           <t>B | 766呎 (3房)
 $2027万
 $26,461/呎
-(23年-07月)</t>
+(23年-07月-19日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -72608,7 +72608,7 @@
           <t>C | 439呎 (2房)
 $842万
 $19,180/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -72616,7 +72616,7 @@
           <t>D | 428呎 (2房)
 $1003万
 $23,439/呎
-(22年-07月)</t>
+(22年-07月-12日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -72624,7 +72624,7 @@
           <t>E | 333呎 (1房)
 $863万
 $25,922/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -72632,7 +72632,7 @@
           <t>F | 445呎 (2房)
 $1076万
 $24,173/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -72640,7 +72640,7 @@
           <t>G | 482呎 (2房)
 $1108万
 $22,981/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -72648,7 +72648,7 @@
           <t>H | 774呎 (3房)
 $1916万
 $24,748/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
     </row>
@@ -72663,7 +72663,7 @@
           <t>A | 763呎 (3房)
 $1810万
 $23,721/呎
-(24年-03月)</t>
+(24年-03月-11日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -72671,7 +72671,7 @@
           <t>B | 766呎 (3房)
 $2015万
 $26,309/呎
-(23年-05月)</t>
+(23年-05月-18日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -72679,7 +72679,7 @@
           <t>C | 439呎 (2房)
 $837万
 $19,064/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -72687,7 +72687,7 @@
           <t>D | 427呎 (2房)
 $1019万
 $23,871/呎
-(22年-05月)</t>
+(22年-05月-04日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -72695,7 +72695,7 @@
           <t>E | 333呎 (1房)
 $820万
 $24,622/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -72703,7 +72703,7 @@
           <t>F | 445呎 (2房)
 $1022万
 $22,957/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -72711,7 +72711,7 @@
           <t>G | 482呎 (2房)
 $1151万
 $23,888/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -72719,7 +72719,7 @@
           <t>H | 774呎 (3房)
 $1910万
 $24,680/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -72734,7 +72734,7 @@
           <t>A | 763呎 (3房)
 $1811万
 $23,740/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -72742,7 +72742,7 @@
           <t>B | 766呎 (3房)
 $1801万
 $23,514/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -72750,7 +72750,7 @@
           <t>C | 439呎 (2房)
 $828万
 $18,863/呎
-(24年-03月)</t>
+(24年-03月-06日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -72758,7 +72758,7 @@
           <t>D | 428呎 (2房)
 $1006万
 $23,500/呎
-(22年-05月)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -72766,7 +72766,7 @@
           <t>E | 332呎 (1房)
 $852万
 $25,678/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -72774,7 +72774,7 @@
           <t>F | 445呎 (2房)
 $1062万
 $23,861/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -72782,7 +72782,7 @@
           <t>G | 482呎 (2房)
 $1144万
 $23,732/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -72790,7 +72790,7 @@
           <t>H | 774呎 (3房)
 $1905万
 $24,610/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -72805,7 +72805,7 @@
           <t>A | 763呎 (3房)
 $1807万
 $23,684/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -72813,7 +72813,7 @@
           <t>B | 766呎 (3房)
 $2089万
 $27,266/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -72821,7 +72821,7 @@
           <t>C | 439呎 (2房)
 $829万
 $18,891/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -72829,7 +72829,7 @@
           <t>D | 428呎 (2房)
 $1051万
 $24,556/呎
-(22年-01月)</t>
+(22年-01月-23日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -72837,7 +72837,7 @@
           <t>E | 333呎 (1房)
 $810万
 $24,315/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -72845,7 +72845,7 @@
           <t>F | 445呎 (2房)
 $1055万
 $23,703/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -72853,7 +72853,7 @@
           <t>G | 482呎 (2房)
 $847万
 $17,581/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -72861,7 +72861,7 @@
           <t>H | 774呎 (3房)
 $1899万
 $24,540/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -72876,7 +72876,7 @@
           <t>A | 763呎 (3房)
 $1801万
 $23,604/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -72884,7 +72884,7 @@
           <t>B | 766呎 (3房)
 $2028万
 $26,480/呎
-(22年-05月)</t>
+(22年-05月-04日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -72892,7 +72892,7 @@
           <t>C | 439呎 (2房)
 $827万
 $18,836/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -72900,7 +72900,7 @@
           <t>D | 427呎 (2房)
 $1008万
 $23,595/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -72908,7 +72908,7 @@
           <t>E | 333呎 (1房)
 $804万
 $24,159/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -72916,7 +72916,7 @@
           <t>F | 445呎 (2房)
 $1002万
 $22,508/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -72924,7 +72924,7 @@
           <t>G | 482呎 (2房)
 $1079万
 $22,382/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -72932,7 +72932,7 @@
           <t>H | 774呎 (3房)
 $1894万
 $24,470/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -72947,7 +72947,7 @@
           <t>A | 763呎 (3房)
 $1801万
 $23,604/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -72955,7 +72955,7 @@
           <t>B | 766呎 (3房)
 $1980万
 $25,854/呎
-(23年-05月)</t>
+(23年-05月-04日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -72963,7 +72963,7 @@
           <t>C | 439呎 (2房)
 $827万
 $18,836/呎
-(23年-12月)</t>
+(23年-12月-26日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -72971,7 +72971,7 @@
           <t>D | 427呎 (2房)
 $1002万
 $23,468/呎
-(22年-02月)</t>
+(22年-02月-17日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -72979,7 +72979,7 @@
           <t>E | 333呎 (1房)
 $804万
 $24,159/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -72987,7 +72987,7 @@
           <t>F | 445呎 (2房)
 $1002万
 $22,508/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -72995,7 +72995,7 @@
           <t>G | 482呎 (2房)
 $842万
 $17,465/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -73003,7 +73003,7 @@
           <t>H | 774呎 (3房)
 $1894万
 $24,470/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -73018,7 +73018,7 @@
           <t>A | 763呎 (3房)
 $1791万
 $23,471/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -73026,7 +73026,7 @@
           <t>B | 766呎 (3房)
 $2052万
 $26,789/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -73034,7 +73034,7 @@
           <t>C | 439呎 (2房)
 $834万
 $19,005/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -73042,7 +73042,7 @@
           <t>D | 427呎 (2房)
 $991万
 $23,204/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -73050,7 +73050,7 @@
           <t>E | 332呎 (1房)
 $831万
 $25,030/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -73058,7 +73058,7 @@
           <t>F | 445呎 (2房)
 $988万
 $22,207/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -73066,7 +73066,7 @@
           <t>G | 482呎 (2房)
 $1077万
 $22,338/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -73074,7 +73074,7 @@
           <t>H | 774呎 (3房)
 $1883万
 $24,332/呎
-(24年-04月)</t>
+(24年-04月-22日)</t>
         </is>
       </c>
     </row>
@@ -73089,7 +73089,7 @@
           <t>A | 763呎 (3房)
 $1785万
 $23,400/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -73097,7 +73097,7 @@
           <t>B | 766呎 (3房)
 $1829万
 $23,875/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -73105,7 +73105,7 @@
           <t>C | 439呎 (2房)
 $820万
 $18,667/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -73113,7 +73113,7 @@
           <t>D | 428呎 (2房)
 $982万
 $22,956/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -73121,7 +73121,7 @@
           <t>E | 332呎 (1房)
 $826万
 $24,867/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -73129,7 +73129,7 @@
           <t>F | 445呎 (2房)
 $1027万
 $23,076/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -73137,7 +73137,7 @@
           <t>G | 482呎 (2房)
 $1106万
 $22,946/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -73145,7 +73145,7 @@
           <t>H | 774呎 (3房)
 $1878万
 $24,264/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -73160,7 +73160,7 @@
           <t>A | 763呎 (3房)
 $1780万
 $23,333/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -73168,7 +73168,7 @@
           <t>B | 766呎 (3房)
 $1770万
 $23,108/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -73176,7 +73176,7 @@
           <t>C | 439呎 (2房)
 $817万
 $18,610/呎
-(24年-01月)</t>
+(24年-01月-23日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -73184,7 +73184,7 @@
           <t>D | 428呎 (2房)
 $1019万
 $23,815/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -73192,7 +73192,7 @@
           <t>E | 333呎 (1房)
 $820万
 $24,631/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -73200,7 +73200,7 @@
           <t>F | 445呎 (2房)
 $1020万
 $22,921/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -73208,7 +73208,7 @@
           <t>G | 482呎 (2房)
 $1062万
 $22,033/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -73216,7 +73216,7 @@
           <t>H | 774呎 (3房)
 $1873万
 $24,194/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
     </row>
@@ -73231,7 +73231,7 @@
           <t>A | 763呎 (3房)
 $1775万
 $23,266/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -73239,7 +73239,7 @@
           <t>B | 766呎 (3房)
 $1765万
 $23,039/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -73247,7 +73247,7 @@
           <t>C | 439呎 (2房)
 $815万
 $18,556/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -73255,7 +73255,7 @@
           <t>D | 427呎 (2房)
 $1000万
 $23,410/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -73263,7 +73263,7 @@
           <t>E | 332呎 (1房)
 $788万
 $23,732/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -73271,7 +73271,7 @@
           <t>F | 445呎 (2房)
 $1013万
 $22,764/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -73279,7 +73279,7 @@
           <t>G | 482呎 (2房)
 $1043万
 $21,633/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -73287,7 +73287,7 @@
           <t>H | 774呎 (3房)
 $1867万
 $24,124/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
     </row>
@@ -73302,7 +73302,7 @@
           <t>A | 763呎 (3房)
 $1770万
 $23,199/呎
-(24年-04月)</t>
+(24年-04月-10日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -73310,7 +73310,7 @@
           <t>B | 766呎 (3房)
 $1760万
 $22,970/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -73318,7 +73318,7 @@
           <t>C | 439呎 (2房)
 $812万
 $18,501/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -73326,7 +73326,7 @@
           <t>D | 428呎 (2房)
 $997万
 $23,285/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -73334,7 +73334,7 @@
           <t>E | 332呎 (1房)
 $774万
 $23,307/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -73342,7 +73342,7 @@
           <t>F | 445呎 (2房)
 $1006万
 $22,604/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -73350,7 +73350,7 @@
           <t>G | 482呎 (2房)
 $1083万
 $22,477/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -73358,7 +73358,7 @@
           <t>H | 774呎 (3房)
 $1862万
 $24,054/呎
-(24年-05月)</t>
+(24年-05月-06日)</t>
         </is>
       </c>
     </row>
@@ -73373,7 +73373,7 @@
           <t>A | 763呎 (3房)
 $1748万
 $22,904/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -73381,7 +73381,7 @@
           <t>B | 766呎 (3房)
 $1737万
 $22,676/呎
-(25年-11月)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -73389,7 +73389,7 @@
           <t>C | 439呎 (2房)
 $810万
 $18,446/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -73397,7 +73397,7 @@
           <t>D | 428呎 (2房)
 $976万
 $22,815/呎
-(22年-01月)</t>
+(22年-01月-02日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -73405,7 +73405,7 @@
           <t>E | 332呎 (1房)
 $786万
 $23,681/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -73413,7 +73413,7 @@
           <t>F | 445呎 (2房)
 $933万
 $20,957/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -73421,7 +73421,7 @@
           <t>G | 482呎 (2房)
 $824万
 $17,102/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -73429,7 +73429,7 @@
           <t>H | 774呎 (3房)
 $1856万
 $23,982/呎
-(25年-11月)</t>
+(25年-11月-16日)</t>
         </is>
       </c>
     </row>
@@ -73603,7 +73603,7 @@
           <t>A | 969呎 (3房)
 $3000万
 $30,956/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
@@ -73612,7 +73612,7 @@
           <t>C | 459呎 (2房)
 $1002万
 $21,834/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -73620,7 +73620,7 @@
           <t>D | 456呎 (2房)
 $970万
 $21,279/呎
-(24年-03月)</t>
+(24年-03月-13日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -73628,7 +73628,7 @@
           <t>E | 452呎 (2房)
 $932万
 $20,626/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="G5" s="20" t="inlineStr">
@@ -73636,7 +73636,7 @@
           <t>F | 1325呎 (4+房)
 $3600万
 $27,170/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="H5" s="21" t="inlineStr"/>
@@ -73646,7 +73646,7 @@
           <t>J | 357呎 (1房)
 $752万
 $21,050/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="K5" s="20" t="inlineStr">
@@ -73654,7 +73654,7 @@
           <t>K | 457呎 (2房)
 $987万
 $21,602/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -73669,7 +73669,7 @@
           <t>A | 657呎 (3房)
 $1499万
 $22,811/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -73677,7 +73677,7 @@
           <t>B | 329呎 (1房)
 $730万
 $22,182/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -73685,7 +73685,7 @@
           <t>C | 459呎 (2房)
 $999万
 $21,771/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -73693,7 +73693,7 @@
           <t>D | 456呎 (2房)
 $881万
 $19,320/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -73701,7 +73701,7 @@
           <t>E | 452呎 (2房)
 $927万
 $20,504/呎
-(25年-03月)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -73709,7 +73709,7 @@
           <t>F | 332呎 (1房)
 $693万
 $20,877/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="H6" s="20" t="inlineStr">
@@ -73717,7 +73717,7 @@
           <t>G | 536呎 (2房)
 $1323万
 $24,688/呎
-(22年-05月)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
       <c r="I6" s="20" t="inlineStr">
@@ -73725,7 +73725,7 @@
           <t>H | 349呎 (1房)
 $756万
 $21,676/呎
-(26年-04月)</t>
+(26年-04月-12日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -73733,7 +73733,7 @@
           <t>J | 451呎 (2房)
 $941万
 $20,869/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -73741,7 +73741,7 @@
           <t>K | 457呎 (2房)
 $982万
 $21,484/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
     </row>
@@ -73756,7 +73756,7 @@
           <t>A | 656呎 (3房)
 $1736万
 $26,466/呎
-(23年-02月)</t>
+(23年-02月-12日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -73764,7 +73764,7 @@
           <t>B | 329呎 (1房)
 $738万
 $22,447/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -73772,7 +73772,7 @@
           <t>C | 459呎 (2房)
 $1011万
 $22,033/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -73780,7 +73780,7 @@
           <t>D | 456呎 (2房)
 $876万
 $19,208/呎
-(26年-03月)</t>
+(26年-03月-29日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -73788,7 +73788,7 @@
           <t>E | 452呎 (2房)
 $921万
 $20,381/呎
-(24年-11月)</t>
+(24年-11月-24日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -73796,7 +73796,7 @@
           <t>F | 332呎 (1房)
 $691万
 $20,813/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="H7" s="20" t="inlineStr">
@@ -73804,7 +73804,7 @@
           <t>G | 536呎 (2房)
 $1383万
 $25,808/呎
-(22年-01月)</t>
+(22年-01月-09日)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -73812,7 +73812,7 @@
           <t>H | 349呎 (1房)
 $752万
 $21,539/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -73820,7 +73820,7 @@
           <t>J | 451呎 (2房)
 $951万
 $21,091/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -73828,7 +73828,7 @@
           <t>K | 457呎 (2房)
 $976万
 $21,365/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -73843,7 +73843,7 @@
           <t>A | 657呎 (3房)
 $1490万
 $22,674/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -73851,7 +73851,7 @@
           <t>B | 329呎 (1房)
 $725万
 $22,049/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -73859,7 +73859,7 @@
           <t>C | 459呎 (2房)
 $993万
 $21,641/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -73867,7 +73867,7 @@
           <t>D | 456呎 (2房)
 $871万
 $19,099/呎
-(26年-03月)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -73875,7 +73875,7 @@
           <t>E | 452呎 (2房)
 $916万
 $20,259/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -73883,7 +73883,7 @@
           <t>F | 332呎 (1房)
 $689万
 $20,750/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
@@ -73891,7 +73891,7 @@
           <t>G | 536呎 (2房)
 $1347万
 $25,136/呎
-(22年-07月)</t>
+(22年-07月-26日)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -73899,7 +73899,7 @@
           <t>H | 349呎 (1房)
 $887万
 $25,415/呎
-(23年-05月)</t>
+(23年-05月-30日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -73907,7 +73907,7 @@
           <t>J | 451呎 (2房)
 $931万
 $20,643/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -73915,7 +73915,7 @@
           <t>K | 457呎 (2房)
 $971万
 $21,247/呎
-(24年-04月)</t>
+(24年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -73930,7 +73930,7 @@
           <t>A | 657呎 (3房)
 $1485万
 $22,607/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -73938,7 +73938,7 @@
           <t>B | 329呎 (1房)
 $723万
 $21,985/呎
-(23年-12月)</t>
+(23年-12月-07日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -73946,7 +73946,7 @@
           <t>C | 459呎 (2房)
 $990万
 $21,573/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -73954,7 +73954,7 @@
           <t>D | 456呎 (2房)
 $934万
 $20,480/呎
-(26年-02月)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -73962,7 +73962,7 @@
           <t>E | 452呎 (2房)
 $910万
 $20,139/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -73970,7 +73970,7 @@
           <t>F | 332呎 (1房)
 $687万
 $20,684/呎
-(26年-04月)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -73978,7 +73978,7 @@
           <t>G | 536呎 (2房)
 $1423万
 $26,545/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -73986,7 +73986,7 @@
           <t>H | 348呎 (1房)
 $882万
 $25,333/呎
-(23年-04月)</t>
+(23年-04月-18日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -73994,7 +73994,7 @@
           <t>J | 451呎 (2房)
 $926万
 $20,530/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -74002,7 +74002,7 @@
           <t>K | 457呎 (2房)
 $980万
 $21,453/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -74017,7 +74017,7 @@
           <t>A | 657呎 (3房)
 $1481万
 $22,540/呎
-(24年-05月)</t>
+(24年-05月-12日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -74025,7 +74025,7 @@
           <t>B | 329呎 (1房)
 $721万
 $21,918/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -74033,7 +74033,7 @@
           <t>C | 459呎 (2房)
 $987万
 $21,508/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -74041,7 +74041,7 @@
           <t>D | 456呎 (2房)
 $928万
 $20,362/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -74049,7 +74049,7 @@
           <t>E | 452呎 (2房)
 $919万
 $20,323/呎
-(24年-04月)</t>
+(24年-04月-25日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -74057,7 +74057,7 @@
           <t>F | 332呎 (1房)
 $696万
 $20,949/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -74065,7 +74065,7 @@
           <t>G | 536呎 (2房)
 $1110万
 $20,700/呎
-(23年-12月)</t>
+(23年-12月-03日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -74073,7 +74073,7 @@
           <t>H | 348呎 (1房)
 $887万
 $25,486/呎
-(23年-06月)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -74081,7 +74081,7 @@
           <t>J | 451呎 (2房)
 $921万
 $20,417/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -74089,7 +74089,7 @@
           <t>K | 457呎 (2房)
 $960万
 $21,011/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -74104,7 +74104,7 @@
           <t>A | 657呎 (3房)
 $1476万
 $22,473/呎
-(24年-01月)</t>
+(24年-01月-03日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -74112,7 +74112,7 @@
           <t>B | 329呎 (1房)
 $719万
 $21,851/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -74120,7 +74120,7 @@
           <t>C | 459呎 (2房)
 $984万
 $21,442/呎
-(24年-01月)</t>
+(24年-01月-30日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -74128,7 +74128,7 @@
           <t>D | 456呎 (2房)
 $923万
 $20,243/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -74136,7 +74136,7 @@
           <t>E | 452呎 (2房)
 $899万
 $19,898/呎
-(24年-08月)</t>
+(24年-08月-13日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -74144,7 +74144,7 @@
           <t>F | 332呎 (1房)
 $683万
 $20,566/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -74152,7 +74152,7 @@
           <t>G | 536呎 (2房)
 $1106万
 $20,638/呎
-(23年-12月)</t>
+(23年-12月-26日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -74160,7 +74160,7 @@
           <t>H | 349呎 (1房)
 $871万
 $24,963/呎
-(23年-04月)</t>
+(23年-04月-17日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -74168,7 +74168,7 @@
           <t>J | 451呎 (2房)
 $930万
 $20,632/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -74176,7 +74176,7 @@
           <t>K | 457呎 (2房)
 $955万
 $20,893/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -74191,7 +74191,7 @@
           <t>A | 656呎 (3房)
 $1716万
 $26,152/呎
-(23年-03月)</t>
+(23年-03月-23日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -74199,7 +74199,7 @@
           <t>B | 329呎 (1房)
 $719万
 $21,851/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -74207,7 +74207,7 @@
           <t>C | 459呎 (2房)
 $984万
 $21,442/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -74215,7 +74215,7 @@
           <t>D | 457呎 (2房)
 $1243万
 $27,193/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -74223,7 +74223,7 @@
           <t>E | 452呎 (2房)
 $899万
 $19,898/呎
-(24年-04月)</t>
+(24年-04月-21日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -74231,7 +74231,7 @@
           <t>F | 332呎 (1房)
 $683万
 $20,566/呎
-(26年-05月)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -74239,7 +74239,7 @@
           <t>G | 536呎 (2房)
 $1335万
 $24,912/呎
-(22年-06月)</t>
+(22年-06月-26日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -74247,7 +74247,7 @@
           <t>H | 348呎 (1房)
 $892万
 $25,641/呎
-(22年-05月)</t>
+(22年-05月-29日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -74255,7 +74255,7 @@
           <t>J | 451呎 (2房)
 $916万
 $20,304/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -74263,7 +74263,7 @@
           <t>K | 457呎 (2房)
 $955万
 $20,893/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -74278,7 +74278,7 @@
           <t>A | 657呎 (3房)
 $1468万
 $22,339/呎
-(23年-12月)</t>
+(23年-12月-17日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -74286,7 +74286,7 @@
           <t>B | 329呎 (1房)
 $725万
 $22,049/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -74294,7 +74294,7 @@
           <t>C | 459呎 (2房)
 $978万
 $21,314/呎
-(24年-01月)</t>
+(24年-01月-14日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -74302,7 +74302,7 @@
           <t>D | 456呎 (2房)
 $1270万
 $27,855/呎
-(21年-10月)</t>
+(21年-10月-18日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -74310,7 +74310,7 @@
           <t>E | 452呎 (2房)
 $892万
 $19,741/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -74318,7 +74318,7 @@
           <t>F | 332呎 (1房)
 $679万
 $20,443/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -74326,7 +74326,7 @@
           <t>G | 536呎 (2房)
 $1115万
 $20,806/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -74334,7 +74334,7 @@
           <t>H | 348呎 (1房)
 $864万
 $24,836/呎
-(23年-03月)</t>
+(23年-03月-21日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -74342,7 +74342,7 @@
           <t>J | 451呎 (2房)
 $906万
 $20,078/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -74350,7 +74350,7 @@
           <t>K | 457呎 (2房)
 $958万
 $20,972/呎
-(24年-04月)</t>
+(24年-04月-11日)</t>
         </is>
       </c>
     </row>
@@ -74365,7 +74365,7 @@
           <t>A | 657呎 (3房)
 $1463万
 $22,272/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -74373,7 +74373,7 @@
           <t>B | 329呎 (1房)
 $710万
 $21,568/呎
-(24年-03月)</t>
+(24年-03月-04日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -74381,7 +74381,7 @@
           <t>C | 459呎 (2房)
 $975万
 $21,251/呎
-(24年-01月)</t>
+(24年-01月-09日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -74389,7 +74389,7 @@
           <t>D | 457呎 (2房)
 $1207万
 $26,409/呎
-(21年-07月)</t>
+(21年-07月-28日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -74397,7 +74397,7 @@
           <t>E | 452呎 (2房)
 $890万
 $19,681/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -74405,7 +74405,7 @@
           <t>F | 332呎 (1房)
 $677万
 $20,383/呎
-(26年-04月)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -74413,7 +74413,7 @@
           <t>G | 536呎 (2房)
 $1096万
 $20,451/呎
-(24年-01月)</t>
+(24年-01月-07日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -74421,7 +74421,7 @@
           <t>H | 349呎 (1房)
 $882万
 $25,287/呎
-(22年-05月)</t>
+(22年-05月-23日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -74429,7 +74429,7 @@
           <t>J | 451呎 (2房)
 $900万
 $19,965/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -74437,7 +74437,7 @@
           <t>K | 457呎 (2房)
 $953万
 $20,851/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -74452,7 +74452,7 @@
           <t>A | 657呎 (3房)
 $1480万
 $22,521/呎
-(24年-01月)</t>
+(24年-01月-11日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -74460,7 +74460,7 @@
           <t>B | 329呎 (1房)
 $710万
 $21,590/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -74468,7 +74468,7 @@
           <t>C | 459呎 (2房)
 $972万
 $21,187/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -74476,7 +74476,7 @@
           <t>D | 456呎 (2房)
 $902万
 $19,770/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -74484,7 +74484,7 @@
           <t>E | 452呎 (2房)
 $901万
 $19,925/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -74492,7 +74492,7 @@
           <t>F | 332呎 (1房)
 $675万
 $20,322/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -74500,7 +74500,7 @@
           <t>G | 536呎 (2房)
 $1093万
 $20,390/呎
-(24年-03月)</t>
+(24年-03月-21日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -74508,7 +74508,7 @@
           <t>H | 349呎 (1房)
 $890万
 $25,510/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -74516,7 +74516,7 @@
           <t>J | 451呎 (2房)
 $895万
 $19,851/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -74524,7 +74524,7 @@
           <t>K | 457呎 (2房)
 $933万
 $20,416/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -74539,7 +74539,7 @@
           <t>A | 657呎 (3房)
 $1455万
 $22,140/呎
-(23年-12月)</t>
+(23年-12月-27日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -74547,7 +74547,7 @@
           <t>B | 329呎 (1房)
 $708万
 $21,526/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -74555,7 +74555,7 @@
           <t>C | 459呎 (2房)
 $970万
 $21,124/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -74563,7 +74563,7 @@
           <t>D | 456呎 (2房)
 $1223万
 $26,814/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -74571,7 +74571,7 @@
           <t>E | 452呎 (2房)
 $884万
 $19,564/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -74579,7 +74579,7 @@
           <t>F | 332呎 (1房)
 $673万
 $20,262/呎
-(26年-05月)</t>
+(26年-05月-25日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -74587,7 +74587,7 @@
           <t>G | 536呎 (2房)
 $1090万
 $20,328/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -74595,7 +74595,7 @@
           <t>H | 348呎 (1房)
 $877万
 $25,207/呎
-(22年-05月)</t>
+(22年-05月-16日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -74603,7 +74603,7 @@
           <t>J | 451呎 (2房)
 $905万
 $20,058/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -74611,7 +74611,7 @@
           <t>K | 457呎 (2房)
 $928万
 $20,298/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -74626,7 +74626,7 @@
           <t>A | 657呎 (3房)
 $1450万
 $22,075/呎
-(23年-12月)</t>
+(23年-12月-11日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -74634,7 +74634,7 @@
           <t>B | 329呎 (1房)
 $706万
 $21,465/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -74642,7 +74642,7 @@
           <t>C | 459呎 (2房)
 $967万
 $21,061/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -74650,7 +74650,7 @@
           <t>D | 457呎 (2房)
 $1215万
 $26,593/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -74658,7 +74658,7 @@
           <t>E | 452呎 (2房)
 $895万
 $19,805/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -74666,7 +74666,7 @@
           <t>F | 332呎 (1房)
 $686万
 $20,675/呎
-(26年-05月)</t>
+(26年-05月-14日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -74674,7 +74674,7 @@
           <t>G | 536呎 (2房)
 $1118万
 $20,849/呎
-(24年-05月)</t>
+(24年-05月-05日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -74682,7 +74682,7 @@
           <t>H | 348呎 (1房)
 $926万
 $26,618/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -74690,7 +74690,7 @@
           <t>J | 451呎 (2房)
 $899万
 $19,942/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -74698,7 +74698,7 @@
           <t>K | 457呎 (2房)
 $922万
 $20,179/呎
-(24年-04月)</t>
+(24年-04月-16日)</t>
         </is>
       </c>
     </row>
@@ -74713,7 +74713,7 @@
           <t>A | 657呎 (3房)
 $1446万
 $22,008/呎
-(23年-12月)</t>
+(23年-12月-21日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -74721,7 +74721,7 @@
           <t>B | 329呎 (1房)
 $704万
 $21,398/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -74729,7 +74729,7 @@
           <t>C | 459呎 (2房)
 $964万
 $20,996/呎
-(24年-01月)</t>
+(24年-01月-28日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -74737,7 +74737,7 @@
           <t>D | 456呎 (2房)
 $1154万
 $25,318/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -74745,7 +74745,7 @@
           <t>E | 452呎 (2房)
 $892万
 $19,743/呎
-(24年-04月)</t>
+(24年-04月-18日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -74753,7 +74753,7 @@
           <t>F | 332呎 (1房)
 $669万
 $20,139/呎
-(25年-09月)</t>
+(25年-09月-14日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -74761,7 +74761,7 @@
           <t>G | 536呎 (2房)
 $1083万
 $20,207/呎
-(23年-12月)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -74769,7 +74769,7 @@
           <t>H | 349呎 (1房)
 $851万
 $24,395/呎
-(22年-05月)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -74777,7 +74777,7 @@
           <t>J | 451呎 (2房)
 $880万
 $19,512/呎
-(24年-03月)</t>
+(24年-03月-25日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -74785,7 +74785,7 @@
           <t>K | 457呎 (2房)
 $917万
 $20,061/呎
-(24年-04月)</t>
+(24年-04月-08日)</t>
         </is>
       </c>
     </row>
@@ -74800,7 +74800,7 @@
           <t>A | 656呎 (3房)
 $1675万
 $25,535/呎
-(23年-06月)</t>
+(23年-06月-15日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -74808,7 +74808,7 @@
           <t>B | 329呎 (1房)
 $702万
 $21,334/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -74816,7 +74816,7 @@
           <t>C | 459呎 (2房)
 $961万
 $20,932/呎
-(24年-02月)</t>
+(24年-02月-20日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -74824,7 +74824,7 @@
           <t>D | 456呎 (2房)
 $876万
 $19,200/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -74832,7 +74832,7 @@
           <t>E | 452呎 (2房)
 $876万
 $19,389/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -74840,7 +74840,7 @@
           <t>F | 332呎 (1房)
 $667万
 $20,078/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -74848,7 +74848,7 @@
           <t>G | 536呎 (2房)
 $1080万
 $20,147/呎
-(23年-12月)</t>
+(23年-12月-18日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -74856,7 +74856,7 @@
           <t>H | 348呎 (1房)
 $870万
 $24,986/呎
-(22年-05月)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -74864,7 +74864,7 @@
           <t>J | 451呎 (2房)
 $1291万
 $28,632/呎
-(21年-09月)</t>
+(21年-09月-28日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -74872,7 +74872,7 @@
           <t>K | 457呎 (2房)
 $911万
 $19,943/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
     </row>
@@ -74887,7 +74887,7 @@
           <t>A | 656呎 (3房)
 $1751万
 $26,692/呎
-(21年-12月)</t>
+(21年-12月-30日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -74895,7 +74895,7 @@
           <t>B | 329呎 (1房)
 $710万
 $21,593/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -74903,7 +74903,7 @@
           <t>C | 459呎 (2房)
 $958万
 $20,869/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -74911,7 +74911,7 @@
           <t>D | 457呎 (2房)
 $1140万
 $24,954/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -74935,7 +74935,7 @@
           <t>G | 536呎 (2房)
 $1269万
 $23,675/呎
-(23年-01月)</t>
+(23年-01月-18日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -74943,7 +74943,7 @@
           <t>H | 348呎 (1房)
 $867万
 $24,908/呎
-(22年-05月)</t>
+(22年-05月-09日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -74951,7 +74951,7 @@
           <t>J | 451呎 (2房)
 $870万
 $19,288/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -74959,7 +74959,7 @@
           <t>K | 457呎 (2房)
 $906万
 $19,825/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -74974,7 +74974,7 @@
           <t>A | 657呎 (3房)
 $1710万
 $26,035/呎
-(22年-06月)</t>
+(22年-06月-21日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -74982,7 +74982,7 @@
           <t>B | 329呎 (1房)
 $700万
 $21,274/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -74990,7 +74990,7 @@
           <t>C | 459呎 (2房)
 $958万
 $20,869/呎
-(23年-12月)</t>
+(23年-12月-04日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -74998,7 +74998,7 @@
           <t>D | 456呎 (2房)
 $1193万
 $26,164/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -75006,7 +75006,7 @@
           <t>E | 452呎 (2房)
 $1127万
 $24,938/呎
-(22年-06月)</t>
+(22年-06月-22日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -75014,7 +75014,7 @@
           <t>F | 331呎 (1房)
 $937万
 $28,305/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -75022,7 +75022,7 @@
           <t>G | 536呎 (2房)
 $1077万
 $20,088/呎
-(23年-12月)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -75030,7 +75030,7 @@
           <t>H | 349呎 (1房)
 $682万
 $19,544/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -75038,7 +75038,7 @@
           <t>J | 451呎 (2房)
 $1203万
 $26,676/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -75046,7 +75046,7 @@
           <t>K | 457呎 (2房)
 $1236万
 $27,053/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
     </row>
@@ -75061,7 +75061,7 @@
           <t>A | 656呎 (3房)
 $1660万
 $25,306/呎
-(22年-06月)</t>
+(22年-06月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -75069,7 +75069,7 @@
           <t>B | 329呎 (1房)
 $696万
 $21,146/呎
-(24年-03月)</t>
+(24年-03月-27日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -75077,7 +75077,7 @@
           <t>C | 459呎 (2房)
 $952万
 $20,745/呎
-(24年-03月)</t>
+(24年-03月-24日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -75085,7 +75085,7 @@
           <t>D | 456呎 (2房)
 $1126万
 $24,700/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -75093,7 +75093,7 @@
           <t>E | 452呎 (2房)
 $868万
 $19,215/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -75101,7 +75101,7 @@
           <t>F | 332呎 (1房)
 $926万
 $27,889/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -75109,7 +75109,7 @@
           <t>G | 536呎 (2房)
 $1277万
 $23,819/呎
-(23年-07月)</t>
+(23年-07月-02日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -75117,7 +75117,7 @@
           <t>H | 348呎 (1房)
 $913万
 $26,227/呎
-(22年-01月)</t>
+(22年-01月-12日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -75125,7 +75125,7 @@
           <t>J | 451呎 (2房)
 $1175万
 $26,062/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -75133,7 +75133,7 @@
           <t>K | 457呎 (2房)
 $1168万
 $25,547/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
     </row>
@@ -75148,7 +75148,7 @@
           <t>A | 657呎 (3房)
 $1655万
 $25,192/呎
-(22年-09月)</t>
+(22年-09月-22日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -75156,7 +75156,7 @@
           <t>B | 329呎 (1房)
 $694万
 $21,079/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -75164,7 +75164,7 @@
           <t>C | 459呎 (2房)
 $949万
 $20,684/呎
-(24年-01月)</t>
+(24年-01月-25日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -75172,7 +75172,7 @@
           <t>D | 456呎 (2房)
 $1136万
 $24,908/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -75180,7 +75180,7 @@
           <t>E | 452呎 (2房)
 $866万
 $19,157/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -75188,7 +75188,7 @@
           <t>F | 331呎 (1房)
 $920万
 $27,801/呎
-(21年-08月)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -75196,7 +75196,7 @@
           <t>G | 536呎 (2房)
 $1364万
 $25,453/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -75204,7 +75204,7 @@
           <t>H | 349呎 (1房)
 $676万
 $19,372/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -75212,7 +75212,7 @@
           <t>J | 451呎 (2房)
 $1222万
 $27,104/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -75220,7 +75220,7 @@
           <t>K | 457呎 (2房)
 $1214万
 $26,567/呎
-(21年-08月)</t>
+(21年-08月-30日)</t>
         </is>
       </c>
     </row>
@@ -75235,7 +75235,7 @@
           <t>A | 656呎 (3房)
 $1646万
 $25,096/呎
-(23年-03月)</t>
+(23年-03月-02日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -75243,7 +75243,7 @@
           <t>B | 329呎 (1房)
 $692万
 $21,018/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -75251,7 +75251,7 @@
           <t>C | 459呎 (2房)
 $946万
 $20,621/呎
-(23年-12月)</t>
+(23年-12月-20日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -75259,7 +75259,7 @@
           <t>D | 457呎 (2房)
 $1079万
 $23,606/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -75267,7 +75267,7 @@
           <t>E | 452呎 (2房)
 $863万
 $19,102/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -75275,7 +75275,7 @@
           <t>F | 332呎 (1房)
 $874万
 $26,337/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -75283,7 +75283,7 @@
           <t>G | 536呎 (2房)
 $1254万
 $23,394/呎
-(23年-07月)</t>
+(23年-07月-31日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -75291,7 +75291,7 @@
           <t>H | 349呎 (1房)
 $877万
 $25,123/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -75299,7 +75299,7 @@
           <t>J | 451呎 (2房)
 $1161万
 $25,752/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -75307,7 +75307,7 @@
           <t>K | 457呎 (2房)
 $1153万
 $25,239/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -75322,7 +75322,7 @@
           <t>A | 656呎 (3房)
 $1645万
 $25,079/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -75330,7 +75330,7 @@
           <t>B | 329呎 (1房)
 $689万
 $20,954/呎
-(26年-02月)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -75338,7 +75338,7 @@
           <t>C | 459呎 (2房)
 $944万
 $20,560/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -75346,7 +75346,7 @@
           <t>D | 457呎 (2房)
 $1121万
 $24,538/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -75354,7 +75354,7 @@
           <t>E | 452呎 (2房)
 $874万
 $19,336/呎
-(24年-04月)</t>
+(24年-04月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -75362,7 +75362,7 @@
           <t>F | 331呎 (1房)
 $909万
 $27,471/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -75370,7 +75370,7 @@
           <t>G | 536呎 (2房)
 $1061万
 $19,789/呎
-(23年-12月)</t>
+(23年-12月-12日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -75378,7 +75378,7 @@
           <t>H | 348呎 (1房)
 $900万
 $25,859/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -75386,7 +75386,7 @@
           <t>J | 451呎 (2房)
 $1208万
 $26,783/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -75394,7 +75394,7 @@
           <t>K | 457呎 (2房)
 $1199万
 $26,243/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -75409,7 +75409,7 @@
           <t>A | 656呎 (3房)
 $1640万
 $25,005/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -75417,7 +75417,7 @@
           <t>B | 329呎 (1房)
 $687万
 $20,891/呎
-(24年-04月)</t>
+(24年-04月-15日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -75425,7 +75425,7 @@
           <t>C | 459呎 (2房)
 $955万
 $20,810/呎
-(24年-01月)</t>
+(24年-01月-03日)</t>
         </is>
       </c>
       <c r="E26" s="20" t="inlineStr">
@@ -75433,7 +75433,7 @@
           <t>D | 456呎 (2房)
 $1114万
 $24,439/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F26" s="20" t="inlineStr">
@@ -75441,7 +75441,7 @@
           <t>E | 452呎 (2房)
 $858万
 $18,987/呎
-(24年-05月)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="G26" s="20" t="inlineStr">
@@ -75449,7 +75449,7 @@
           <t>F | 332呎 (1房)
 $914万
 $27,524/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H26" s="20" t="inlineStr">
@@ -75457,7 +75457,7 @@
           <t>G | 536呎 (2房)
 $1382万
 $25,791/呎
-(22年-01月)</t>
+(22年-01月-04日)</t>
         </is>
       </c>
       <c r="I26" s="20" t="inlineStr">
@@ -75465,7 +75465,7 @@
           <t>H | 348呎 (1房)
 $891万
 $25,595/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="J26" s="20" t="inlineStr">
@@ -75473,7 +75473,7 @@
           <t>J | 451呎 (2房)
 $1188万
 $26,350/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -75481,7 +75481,7 @@
           <t>K | 457呎 (2房)
 $1180万
 $25,812/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
     </row>
@@ -75496,7 +75496,7 @@
           <t>A | 656呎 (3房)
 $1635万
 $24,930/呎
-(23年-03月)</t>
+(23年-03月-09日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -75504,7 +75504,7 @@
           <t>B | 329呎 (1房)
 $685万
 $20,827/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="D27" s="20" t="inlineStr">
@@ -75512,7 +75512,7 @@
           <t>C | 459呎 (2房)
 $938万
 $20,438/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E27" s="20" t="inlineStr">
@@ -75520,7 +75520,7 @@
           <t>D | 457呎 (2房)
 $1058万
 $23,155/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F27" s="20" t="inlineStr">
@@ -75528,7 +75528,7 @@
           <t>E | 452呎 (2房)
 $856万
 $18,929/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="G27" s="20" t="inlineStr">
@@ -75536,7 +75536,7 @@
           <t>F | 331呎 (1房)
 $859万
 $25,940/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="H27" s="20" t="inlineStr">
@@ -75544,7 +75544,7 @@
           <t>G | 536呎 (2房)
 $1243万
 $23,185/呎
-(23年-05月)</t>
+(23年-05月-17日)</t>
         </is>
       </c>
       <c r="I27" s="20" t="inlineStr">
@@ -75552,7 +75552,7 @@
           <t>H | 348呎 (1房)
 $854万
 $24,526/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="J27" s="20" t="inlineStr">
@@ -75560,7 +75560,7 @@
           <t>J | 451呎 (2房)
 $828万
 $18,370/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -75568,7 +75568,7 @@
           <t>K | 457呎 (2房)
 $1052万
 $23,031/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -75583,7 +75583,7 @@
           <t>A | 656呎 (3房)
 $1631万
 $24,857/呎
-(22年-10月)</t>
+(22年-10月-11日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -75591,7 +75591,7 @@
           <t>B | 329呎 (1房)
 $680万
 $20,675/呎
-(24年-03月)</t>
+(24年-03月-07日)</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -75599,7 +75599,7 @@
           <t>C | 459呎 (2房)
 $935万
 $20,375/呎
-(24年-01月)</t>
+(24年-01月-21日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -75607,7 +75607,7 @@
           <t>D | 456呎 (2房)
 $1100万
 $24,123/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F28" s="20" t="inlineStr">
@@ -75615,7 +75615,7 @@
           <t>E | 452呎 (2房)
 $853万
 $18,874/呎
-(24年-04月)</t>
+(24年-04月-29日)</t>
         </is>
       </c>
       <c r="G28" s="20" t="inlineStr">
@@ -75623,7 +75623,7 @@
           <t>F | 331呎 (1房)
 $893万
 $26,970/呎
-(21年-08月)</t>
+(21年-08月-01日)</t>
         </is>
       </c>
       <c r="H28" s="20" t="inlineStr">
@@ -75631,7 +75631,7 @@
           <t>G | 536呎 (2房)
 $1239万
 $23,116/呎
-(22年-05月)</t>
+(22年-05月-05日)</t>
         </is>
       </c>
       <c r="I28" s="20" t="inlineStr">
@@ -75639,7 +75639,7 @@
           <t>H | 348呎 (1房)
 $821万
 $23,592/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="J28" s="20" t="inlineStr">
@@ -75647,7 +75647,7 @@
           <t>J | 451呎 (2房)
 $1088万
 $24,122/呎
-(21年-07月)</t>
+(21年-07月-21日)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -75655,7 +75655,7 @@
           <t>K | 457呎 (2房)
 $1034万
 $22,632/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -75670,7 +75670,7 @@
           <t>A | 656呎 (3房)
 $1631万
 $24,857/呎
-(23年-06月)</t>
+(23年-06月-11日)</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -75678,7 +75678,7 @@
           <t>B | 329呎 (1房)
 $683万
 $20,760/呎
-(24年-04月)</t>
+(24年-04月-01日)</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -75686,7 +75686,7 @@
           <t>C | 459呎 (2房)
 $935万
 $20,375/呎
-(23年-12月)</t>
+(23年-12月-19日)</t>
         </is>
       </c>
       <c r="E29" s="20" t="inlineStr">
@@ -75694,7 +75694,7 @@
           <t>D | 456呎 (2房)
 $839万
 $18,390/呎
-(24年-09月)</t>
+(24年-09月-02日)</t>
         </is>
       </c>
       <c r="F29" s="20" t="inlineStr">
@@ -75702,7 +75702,7 @@
           <t>E | 452呎 (2房)
 $853万
 $18,874/呎
-(24年-05月)</t>
+(24年-05月-07日)</t>
         </is>
       </c>
       <c r="G29" s="20" t="inlineStr">
@@ -75710,7 +75710,7 @@
           <t>F | 331呎 (1房)
 $853万
 $25,779/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H29" s="20" t="inlineStr">
@@ -75718,7 +75718,7 @@
           <t>G | 536呎 (2房)
 $1051万
 $19,614/呎
-(24年-02月)</t>
+(24年-02月-22日)</t>
         </is>
       </c>
       <c r="I29" s="20" t="inlineStr">
@@ -75726,7 +75726,7 @@
           <t>H | 349呎 (1房)
 $821万
 $23,524/呎
-(21年-12月)</t>
+(21年-12月-09日)</t>
         </is>
       </c>
       <c r="J29" s="20" t="inlineStr">
@@ -75734,7 +75734,7 @@
           <t>J | 451呎 (2房)
 $1076万
 $23,847/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="K29" s="20" t="inlineStr">
@@ -75742,7 +75742,7 @@
           <t>K | 457呎 (2房)
 $1082万
 $23,678/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -75757,7 +75757,7 @@
           <t>A | 657呎 (3房)
 $1395万
 $21,231/呎
-(23年-11月)</t>
+(23年-11月-28日)</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -75765,7 +75765,7 @@
           <t>B | 329呎 (1房)
 $679万
 $20,638/呎
-(24年-04月)</t>
+(24年-04月-04日)</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -75773,7 +75773,7 @@
           <t>C | 459呎 (2房)
 $930万
 $20,255/呎
-(24年-01月)</t>
+(24年-01月-03日)</t>
         </is>
       </c>
       <c r="E30" s="20" t="inlineStr">
@@ -75781,7 +75781,7 @@
           <t>D | 456呎 (2房)
 $1038万
 $22,757/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F30" s="20" t="inlineStr">
@@ -75789,7 +75789,7 @@
           <t>E | 452呎 (2房)
 $848万
 $18,761/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="G30" s="20" t="inlineStr">
@@ -75797,7 +75797,7 @@
           <t>F | 332呎 (1房)
 $882万
 $26,557/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="H30" s="20" t="inlineStr">
@@ -75805,7 +75805,7 @@
           <t>G | 536呎 (2房)
 $1041万
 $19,427/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="I30" s="20" t="inlineStr">
@@ -75813,7 +75813,7 @@
           <t>H | 348呎 (1房)
 $812万
 $23,328/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="J30" s="20" t="inlineStr">
@@ -75821,7 +75821,7 @@
           <t>J | 451呎 (2房)
 $1111万
 $24,627/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K30" s="20" t="inlineStr">
@@ -75829,7 +75829,7 @@
           <t>K | 457呎 (2房)
 $1021万
 $22,333/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -75844,7 +75844,7 @@
           <t>A | 657呎 (3房)
 $1391万
 $21,167/呎
-(23年-11月)</t>
+(23年-11月-29日)</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -75852,7 +75852,7 @@
           <t>B | 329呎 (1房)
 $677万
 $20,574/呎
-(24年-03月)</t>
+(24年-03月-26日)</t>
         </is>
       </c>
       <c r="D31" s="20" t="inlineStr">
@@ -75860,7 +75860,7 @@
           <t>C | 459呎 (2房)
 $927万
 $20,194/呎
-(23年-11月)</t>
+(23年-11月-30日)</t>
         </is>
       </c>
       <c r="E31" s="20" t="inlineStr">
@@ -75868,7 +75868,7 @@
           <t>D | 456呎 (2房)
 $1031万
 $22,605/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">
@@ -75876,7 +75876,7 @@
           <t>E | 452呎 (2房)
 $1065万
 $23,560/呎
-(22年-09月)</t>
+(22年-09月-29日)</t>
         </is>
       </c>
       <c r="G31" s="20" t="inlineStr">
@@ -75884,7 +75884,7 @@
           <t>F | 332呎 (1房)
 $838万
 $25,226/呎
-(21年-08月)</t>
+(21年-08月-03日)</t>
         </is>
       </c>
       <c r="H31" s="20" t="inlineStr">
@@ -75892,7 +75892,7 @@
           <t>G | 536呎 (2房)
 $1332万
 $24,854/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="I31" s="20" t="inlineStr">
@@ -75900,7 +75900,7 @@
           <t>H | 349呎 (1房)
 $805万
 $23,069/呎
-(22年-01月)</t>
+(22年-01月-03日)</t>
         </is>
       </c>
       <c r="J31" s="20" t="inlineStr">
@@ -75908,7 +75908,7 @@
           <t>J | 451呎 (2房)
 $1055万
 $23,384/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K31" s="20" t="inlineStr">
@@ -75916,7 +75916,7 @@
           <t>K | 457呎 (2房)
 $1014万
 $22,182/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -75931,7 +75931,7 @@
           <t>A | 657呎 (3房)
 $1386万
 $21,104/呎
-(23年-12月)</t>
+(23年-12月-17日)</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -75939,7 +75939,7 @@
           <t>B | 329呎 (1房)
 $675万
 $20,514/呎
-(24年-01月)</t>
+(24年-01月-24日)</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -75947,7 +75947,7 @@
           <t>C | 459呎 (2房)
 $924万
 $20,133/呎
-(23年-12月)</t>
+(23年-12月-10日)</t>
         </is>
       </c>
       <c r="E32" s="20" t="inlineStr">
@@ -75955,7 +75955,7 @@
           <t>D | 456呎 (2房)
 $1036万
 $22,717/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F32" s="20" t="inlineStr">
@@ -75963,7 +75963,7 @@
           <t>E | 452呎 (2房)
 $843万
 $18,650/呎
-(24年-04月)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="G32" s="20" t="inlineStr">
@@ -75971,7 +75971,7 @@
           <t>F | 331呎 (1房)
 $871万
 $26,305/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H32" s="20" t="inlineStr">
@@ -75979,7 +75979,7 @@
           <t>G | 536呎 (2房)
 $1035万
 $19,310/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="I32" s="20" t="inlineStr">
@@ -75987,7 +75987,7 @@
           <t>H | 348呎 (1房)
 $798万
 $22,945/呎
-(22年-01月)</t>
+(22年-01月-05日)</t>
         </is>
       </c>
       <c r="J32" s="20" t="inlineStr">
@@ -75995,7 +75995,7 @@
           <t>J | 451呎 (2房)
 $1048万
 $23,228/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K32" s="20" t="inlineStr">
@@ -76003,7 +76003,7 @@
           <t>K | 457呎 (2房)
 $1007万
 $22,033/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -76018,7 +76018,7 @@
           <t>A | 657呎 (3房)
 $1382万
 $21,040/呎
-(24年-03月)</t>
+(24年-03月-19日)</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -76026,7 +76026,7 @@
           <t>B | 329呎 (1房)
 $673万
 $20,453/呎
-(24年-04月)</t>
+(24年-04月-07日)</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -76034,7 +76034,7 @@
           <t>C | 459呎 (2房)
 $921万
 $20,072/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="E33" s="20" t="inlineStr">
@@ -76042,7 +76042,7 @@
           <t>D | 457呎 (2房)
 $1029万
 $22,514/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F33" s="20" t="inlineStr">
@@ -76050,7 +76050,7 @@
           <t>E | 452呎 (2房)
 $840万
 $18,595/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="G33" s="20" t="inlineStr">
@@ -76058,7 +76058,7 @@
           <t>F | 332呎 (1房)
 $865万
 $26,057/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H33" s="20" t="inlineStr">
@@ -76066,7 +76066,7 @@
           <t>G | 536呎 (2房)
 $1036万
 $19,323/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="I33" s="20" t="inlineStr">
@@ -76074,7 +76074,7 @@
           <t>H | 349呎 (1房)
 $591万
 $16,946/呎
-(24年-09月)</t>
+(24年-09月-25日)</t>
         </is>
       </c>
       <c r="J33" s="20" t="inlineStr">
@@ -76082,7 +76082,7 @@
           <t>J | 451呎 (2房)
 $1089万
 $24,142/呎
-(21年-07月)</t>
+(21年-07月-22日)</t>
         </is>
       </c>
       <c r="K33" s="20" t="inlineStr">
@@ -76090,7 +76090,7 @@
           <t>K | 457呎 (2房)
 $1000万
 $21,882/呎
-(21年-07月)</t>
+(21年-07月-29日)</t>
         </is>
       </c>
     </row>
@@ -76105,7 +76105,7 @@
           <t>A | 657呎 (3房)
 $1378万
 $20,977/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -76113,7 +76113,7 @@
           <t>B | 329呎 (1房)
 $671万
 $20,392/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -76121,7 +76121,7 @@
           <t>C | 459呎 (2房)
 $919万
 $20,013/呎
-(24年-01月)</t>
+(24年-01月-21日)</t>
         </is>
       </c>
       <c r="E34" s="20" t="inlineStr">
@@ -76129,7 +76129,7 @@
           <t>D | 456呎 (2房)
 $1057万
 $23,180/呎
-(21年-07月)</t>
+(21年-07月-26日)</t>
         </is>
       </c>
       <c r="F34" s="20" t="inlineStr">
@@ -76137,7 +76137,7 @@
           <t>E | 452呎 (2房)
 $838万
 $18,540/呎
-(24年-05月)</t>
+(24年-05月-01日)</t>
         </is>
       </c>
       <c r="G34" s="20" t="inlineStr">
@@ -76145,7 +76145,7 @@
           <t>F | 331呎 (1房)
 $860万
 $25,973/呎
-(21年-07月)</t>
+(21年-07月-27日)</t>
         </is>
       </c>
       <c r="H34" s="20" t="inlineStr">
@@ -76153,7 +76153,7 @@
           <t>G | 536呎 (2房)
 $1033万
 $19,265/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="I34" s="20" t="inlineStr">
@@ -76161,7 +76161,7 @@
           <t>H | 349呎 (1房)
 $590万
 $16,897/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="J34" s="20" t="inlineStr">
@@ -76169,7 +76169,7 @@
           <t>J | 451呎 (2房)
 $1082万
 $23,980/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
       <c r="K34" s="20" t="inlineStr">
@@ -76177,7 +76177,7 @@
           <t>K | 457呎 (2房)
 $1039万
 $22,740/呎
-(21年-07月)</t>
+(21年-07月-02日)</t>
         </is>
       </c>
     </row>
@@ -76192,7 +76192,7 @@
           <t>A | 657呎 (3房)
 $1356万
 $20,633/呎
-(24年-03月)</t>
+(24年-03月-18日)</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -76200,7 +76200,7 @@
           <t>B | 329呎 (1房)
 $669万
 $20,331/呎
-(26年-04月)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D35" s="20" t="inlineStr">
@@ -76208,7 +76208,7 @@
           <t>C | 459呎 (2房)
 $930万
 $20,255/呎
-(24年-03月)</t>
+(24年-03月-14日)</t>
         </is>
       </c>
       <c r="E35" s="20" t="inlineStr">
@@ -76216,7 +76216,7 @@
           <t>D | 456呎 (2房)
 $782万
 $17,154/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="F35" s="20" t="inlineStr">
@@ -76224,7 +76224,7 @@
           <t>E | 452呎 (2房)
 $1085万
 $24,004/呎
-(22年-01月)</t>
+(22年-01月-24日)</t>
         </is>
       </c>
       <c r="G35" s="20" t="inlineStr">
@@ -76232,7 +76232,7 @@
           <t>F | 331呎 (1房)
 $836万
 $25,248/呎
-(21年-07月)</t>
+(21年-07月-09日)</t>
         </is>
       </c>
       <c r="H35" s="20" t="inlineStr">
@@ -76240,7 +76240,7 @@
           <t>G | 536呎 (2房)
 $1015万
 $18,944/呎
-(24年-03月)</t>
+(24年-03月-20日)</t>
         </is>
       </c>
       <c r="I35" s="20" t="inlineStr">
@@ -76248,7 +76248,7 @@
           <t>H | 348呎 (1房)
 $779万
 $22,388/呎
-(22年-01月)</t>
+(22年-01月-20日)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -76264,7 +76264,7 @@
           <t>K | 457呎 (2房)
 $1020万
 $22,319/呎
-(21年-07月)</t>
+(21年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -76390,7 +76390,7 @@
           <t>A | 1793呎 (4+房)
 $6320万
 $35,250/呎
-(23年-03月)</t>
+(23年-03月-27日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -76398,7 +76398,7 @@
           <t>B | 1699呎 (4+房)
 $6380万
 $37,552/呎
-(23年-03月)</t>
+(23年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -76413,7 +76413,7 @@
           <t>A | 1687呎 (4+房)
 $4950万
 $29,342/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -76421,7 +76421,7 @@
           <t>B | 1687呎 (4+房)
 $4998万
 $29,627/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -76436,7 +76436,7 @@
           <t>A | 1687呎 (4+房)
 $4781万
 $28,342/呎
-(24年-04月)</t>
+(24年-04月-02日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -76444,7 +76444,7 @@
           <t>B | 1687呎 (4+房)
 $4930万
 $29,223/呎
-(24年-03月)</t>
+(24年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -76459,7 +76459,7 @@
           <t>A | 1687呎 (4+房)
 $4830万
 $28,631/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -76467,7 +76467,7 @@
           <t>B | 1687呎 (4+房)
 $4878万
 $28,917/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
@@ -76482,7 +76482,7 @@
           <t>A | 1687呎 (4+房)
 $4782万
 $28,345/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -76490,7 +76490,7 @@
           <t>B | 1687呎 (4+房)
 $4830万
 $28,628/呎
-(24年-04月)</t>
+(24年-04月-09日)</t>
         </is>
       </c>
     </row>
